--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="125">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,141 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>Indonesian Super League</t>
+  </si>
+  <si>
+    <t>Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Bosnian Premier League</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Bolivar</t>
+  </si>
+  <si>
+    <t>Arema Cronus</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Madura Utd</t>
+  </si>
+  <si>
+    <t>FC Zhetysu</t>
+  </si>
+  <si>
+    <t>FK Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>FK Aktobe</t>
+  </si>
+  <si>
+    <t>Harju JK Laagri</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
+    <t>Zeljeznicar</t>
+  </si>
+  <si>
+    <t>Yeovil</t>
+  </si>
+  <si>
+    <t>Espanyol</t>
+  </si>
+  <si>
+    <t>CD Gualberto Villarroel</t>
+  </si>
+  <si>
+    <t>Persik Kediri</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Psim Yogyakarta</t>
+  </si>
+  <si>
+    <t>FK Kaspyi Aktau</t>
+  </si>
+  <si>
+    <t>FK Kaisar</t>
+  </si>
+  <si>
+    <t>FK Ulytau Zhezkazgan</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Celik Zenica</t>
+  </si>
+  <si>
+    <t>Solihull Moors</t>
+  </si>
+  <si>
+    <t>Elche</t>
+  </si>
+  <si>
+    <t>2026-09-16 00:29:29</t>
   </si>
 </sst>
 </file>
@@ -585,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +963,2910 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2">
+        <v>1.1</v>
+      </c>
+      <c r="G2">
+        <v>600</v>
+      </c>
+      <c r="H2">
+        <v>1.1</v>
+      </c>
+      <c r="I2">
+        <v>870</v>
+      </c>
+      <c r="J2">
+        <v>1.12</v>
+      </c>
+      <c r="K2">
+        <v>950</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.24</v>
+      </c>
+      <c r="O2">
+        <v>1.01</v>
+      </c>
+      <c r="P2">
+        <v>1.24</v>
+      </c>
+      <c r="Q2">
+        <v>1.01</v>
+      </c>
+      <c r="R2">
+        <v>1.08</v>
+      </c>
+      <c r="S2">
+        <v>1.01</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.02</v>
+      </c>
+      <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2">
+        <v>1.03</v>
+      </c>
+      <c r="AR2">
+        <v>1.03</v>
+      </c>
+      <c r="AS2">
+        <v>1.03</v>
+      </c>
+      <c r="AT2">
+        <v>1.03</v>
+      </c>
+      <c r="AU2">
+        <v>1.03</v>
+      </c>
+      <c r="AV2">
+        <v>1.03</v>
+      </c>
+      <c r="AW2">
+        <v>1.03</v>
+      </c>
+      <c r="AX2">
+        <v>1.03</v>
+      </c>
+      <c r="AY2">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2">
+        <v>1.03</v>
+      </c>
+      <c r="BA2">
+        <v>1.03</v>
+      </c>
+      <c r="BB2">
+        <v>1.03</v>
+      </c>
+      <c r="BC2">
+        <v>1.03</v>
+      </c>
+      <c r="BD2">
+        <v>1.03</v>
+      </c>
+      <c r="BE2">
+        <v>1.03</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3">
+        <v>1.58</v>
+      </c>
+      <c r="G3">
+        <v>1.85</v>
+      </c>
+      <c r="H3">
+        <v>4.1</v>
+      </c>
+      <c r="I3">
+        <v>9.4</v>
+      </c>
+      <c r="J3">
+        <v>3.85</v>
+      </c>
+      <c r="K3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.91</v>
+      </c>
+      <c r="Q3">
+        <v>1.66</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>1.15</v>
+      </c>
+      <c r="G4">
+        <v>600</v>
+      </c>
+      <c r="H4">
+        <v>1.13</v>
+      </c>
+      <c r="I4">
+        <v>870</v>
+      </c>
+      <c r="J4">
+        <v>1.16</v>
+      </c>
+      <c r="K4">
+        <v>950</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.24</v>
+      </c>
+      <c r="Q4">
+        <v>1.01</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5">
+        <v>2.24</v>
+      </c>
+      <c r="G5">
+        <v>2.76</v>
+      </c>
+      <c r="H5">
+        <v>3.25</v>
+      </c>
+      <c r="I5">
+        <v>870</v>
+      </c>
+      <c r="J5">
+        <v>1.76</v>
+      </c>
+      <c r="K5">
+        <v>4.1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.81</v>
+      </c>
+      <c r="Q5">
+        <v>1.96</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>600</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>870</v>
+      </c>
+      <c r="J6">
+        <v>1.12</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.1</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8">
+        <v>1.15</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>1.13</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1.13</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.1</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.07</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>6.6</v>
+      </c>
+      <c r="H10">
+        <v>1.7</v>
+      </c>
+      <c r="I10">
+        <v>2.14</v>
+      </c>
+      <c r="J10">
+        <v>3.35</v>
+      </c>
+      <c r="K10">
+        <v>6.2</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.63</v>
+      </c>
+      <c r="Q10">
+        <v>1.92</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>1.74</v>
+      </c>
+      <c r="G11">
+        <v>2.34</v>
+      </c>
+      <c r="H11">
+        <v>3.35</v>
+      </c>
+      <c r="I11">
+        <v>8.6</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.62</v>
+      </c>
+      <c r="Q11">
+        <v>1.84</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>1.83</v>
+      </c>
+      <c r="G12">
+        <v>2.42</v>
+      </c>
+      <c r="H12">
+        <v>3.45</v>
+      </c>
+      <c r="I12">
+        <v>5.2</v>
+      </c>
+      <c r="J12">
+        <v>3.25</v>
+      </c>
+      <c r="K12">
+        <v>6.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.08</v>
+      </c>
+      <c r="Q12">
+        <v>1.5</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>1.9</v>
+      </c>
+      <c r="G13">
+        <v>1.91</v>
+      </c>
+      <c r="H13">
+        <v>4.8</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>3.7</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>3.85</v>
+      </c>
+      <c r="O13">
+        <v>1.33</v>
+      </c>
+      <c r="P13">
+        <v>1.96</v>
+      </c>
+      <c r="Q13">
+        <v>1.97</v>
+      </c>
+      <c r="R13">
+        <v>1.36</v>
+      </c>
+      <c r="S13">
+        <v>3.55</v>
+      </c>
+      <c r="T13">
+        <v>1.85</v>
+      </c>
+      <c r="U13">
+        <v>2.1</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>15</v>
+      </c>
+      <c r="Y13">
+        <v>17</v>
+      </c>
+      <c r="Z13">
+        <v>42</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>9</v>
+      </c>
+      <c r="AC13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13">
+        <v>19</v>
+      </c>
+      <c r="AE13">
+        <v>550</v>
+      </c>
+      <c r="AF13">
+        <v>11.5</v>
+      </c>
+      <c r="AG13">
+        <v>10.5</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>70</v>
+      </c>
+      <c r="AJ13">
+        <v>21</v>
+      </c>
+      <c r="AK13">
+        <v>20</v>
+      </c>
+      <c r="AL13">
+        <v>38</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>13.5</v>
+      </c>
+      <c r="AO13">
+        <v>80</v>
+      </c>
+      <c r="AP13">
+        <v>13</v>
+      </c>
+      <c r="AQ13">
+        <v>14.5</v>
+      </c>
+      <c r="AR13">
+        <v>30</v>
+      </c>
+      <c r="AS13">
+        <v>38</v>
+      </c>
+      <c r="AT13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU13">
+        <v>7.4</v>
+      </c>
+      <c r="AV13">
+        <v>17</v>
+      </c>
+      <c r="AW13">
+        <v>29</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13">
+        <v>17</v>
+      </c>
+      <c r="BA13">
+        <v>32</v>
+      </c>
+      <c r="BB13">
+        <v>18.5</v>
+      </c>
+      <c r="BC13">
+        <v>17.5</v>
+      </c>
+      <c r="BD13">
+        <v>23</v>
+      </c>
+      <c r="BE13">
+        <v>38</v>
+      </c>
+      <c r="BF13">
+        <v>11.5</v>
+      </c>
+      <c r="BG13">
+        <v>32</v>
+      </c>
+      <c r="BH13">
+        <v>3.35</v>
+      </c>
+      <c r="BI13">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13">
+        <v>12</v>
+      </c>
+      <c r="BK13">
+        <v>4.2</v>
+      </c>
+      <c r="BL13">
+        <v>160</v>
+      </c>
+      <c r="BM13">
+        <v>6.2</v>
+      </c>
+      <c r="BN13">
+        <v>5.3</v>
+      </c>
+      <c r="BO13">
+        <v>4.1</v>
+      </c>
+      <c r="BP13">
+        <v>16</v>
+      </c>
+      <c r="BQ13">
+        <v>4.6</v>
+      </c>
+      <c r="BR13">
+        <v>34</v>
+      </c>
+      <c r="BS13">
+        <v>5.4</v>
+      </c>
+      <c r="BT13">
+        <v>9.4</v>
+      </c>
+      <c r="BU13">
+        <v>7.2</v>
+      </c>
+      <c r="BV13">
+        <v>48</v>
+      </c>
+      <c r="BW13">
+        <v>5.7</v>
+      </c>
+      <c r="BX13">
+        <v>60</v>
+      </c>
+      <c r="BY13">
+        <v>5.8</v>
+      </c>
+      <c r="BZ13">
+        <v>30</v>
+      </c>
+      <c r="CA13">
+        <v>5.3</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
+    <t>Japanese J League 2</t>
+  </si>
+  <si>
     <t>Indonesian Super League</t>
   </si>
   <si>
@@ -286,6 +289,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>04:00:00</t>
+  </si>
+  <si>
     <t>08:30:00</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Bolivar</t>
   </si>
   <si>
+    <t>Vanraure Hachinohe</t>
+  </si>
+  <si>
     <t>Arema Cronus</t>
   </si>
   <si>
@@ -355,6 +364,9 @@
     <t>CD Gualberto Villarroel</t>
   </si>
   <si>
+    <t>Tegevajaro Miyazaki</t>
+  </si>
+  <si>
     <t>Persik Kediri</t>
   </si>
   <si>
@@ -388,7 +400,7 @@
     <t>Elche</t>
   </si>
   <si>
-    <t>2026-09-16 00:29:29</t>
+    <t>2026-09-16 02:44:11</t>
   </si>
 </sst>
 </file>
@@ -720,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -970,16 +982,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F2">
         <v>1.1</v>
@@ -1006,13 +1018,13 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O2">
         <v>1.01</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <v>1.01</v>
@@ -1021,7 +1033,7 @@
         <v>1.08</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1030,10 +1042,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1204,7 +1216,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1212,241 +1224,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F3">
-        <v>1.58</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="H3">
+        <v>2.14</v>
+      </c>
+      <c r="I3">
+        <v>2.24</v>
+      </c>
+      <c r="J3">
+        <v>3.25</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.43</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>2.82</v>
+      </c>
+      <c r="O3">
+        <v>1.42</v>
+      </c>
+      <c r="P3">
+        <v>1.63</v>
+      </c>
+      <c r="Q3">
+        <v>2.24</v>
+      </c>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
         <v>4.1</v>
       </c>
-      <c r="I3">
-        <v>9.4</v>
-      </c>
-      <c r="J3">
-        <v>3.85</v>
-      </c>
-      <c r="K3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>1.91</v>
-      </c>
-      <c r="Q3">
-        <v>1.66</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1454,34 +1466,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F4">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="G4">
-        <v>600</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
-        <v>1.13</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>870</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
-        <v>1.16</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1496,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1688,42 +1700,42 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F5">
-        <v>2.24</v>
+        <v>1.15</v>
       </c>
       <c r="G5">
-        <v>2.76</v>
+        <v>600</v>
       </c>
       <c r="H5">
-        <v>3.25</v>
+        <v>1.13</v>
       </c>
       <c r="I5">
         <v>870</v>
       </c>
       <c r="J5">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1738,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1930,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1938,34 +1950,34 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>2.5</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1980,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2172,39 +2184,39 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F7">
         <v>1.1</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H7">
         <v>1.1</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2222,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
         <v>1.01</v>
@@ -2414,39 +2426,39 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2656,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2664,31 +2676,31 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2706,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -2898,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2906,34 +2918,34 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2948,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="Q10">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3140,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3148,34 +3160,34 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F11">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="H11">
+        <v>1.7</v>
+      </c>
+      <c r="I11">
+        <v>2.14</v>
+      </c>
+      <c r="J11">
         <v>3.35</v>
       </c>
-      <c r="I11">
-        <v>8.6</v>
-      </c>
-      <c r="J11">
-        <v>3.25</v>
-      </c>
       <c r="K11">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3190,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3382,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3390,34 +3402,34 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F12">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H12">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I12">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>3.25</v>
       </c>
       <c r="K12">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3432,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3624,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3632,241 +3644,483 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13">
+        <v>1.83</v>
+      </c>
+      <c r="G13">
+        <v>2.42</v>
+      </c>
+      <c r="H13">
+        <v>3.45</v>
+      </c>
+      <c r="I13">
+        <v>5.2</v>
+      </c>
+      <c r="J13">
+        <v>3.25</v>
+      </c>
+      <c r="K13">
+        <v>6.2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.08</v>
+      </c>
+      <c r="Q13">
+        <v>1.5</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13">
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14">
         <v>1.9</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>1.91</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>4.8</v>
       </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13">
+      <c r="I14">
+        <v>4.9</v>
+      </c>
+      <c r="J14">
         <v>3.7</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>3.8</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>1.07</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>3.85</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>1.33</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>1.96</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>1.97</v>
       </c>
-      <c r="R13">
-        <v>1.36</v>
-      </c>
-      <c r="S13">
+      <c r="R14">
+        <v>1.37</v>
+      </c>
+      <c r="S14">
         <v>3.55</v>
       </c>
-      <c r="T13">
+      <c r="T14">
         <v>1.85</v>
       </c>
-      <c r="U13">
+      <c r="U14">
         <v>2.1</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
         <v>15</v>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <v>17</v>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <v>42</v>
       </c>
-      <c r="AA13">
-        <v>1000</v>
-      </c>
-      <c r="AB13">
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
         <v>9</v>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <v>19</v>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <v>550</v>
       </c>
-      <c r="AF13">
+      <c r="AF14">
         <v>11.5</v>
       </c>
-      <c r="AG13">
+      <c r="AG14">
         <v>10.5</v>
       </c>
-      <c r="AH13">
+      <c r="AH14">
         <v>20</v>
       </c>
-      <c r="AI13">
+      <c r="AI14">
         <v>70</v>
       </c>
-      <c r="AJ13">
+      <c r="AJ14">
         <v>21</v>
       </c>
-      <c r="AK13">
+      <c r="AK14">
         <v>20</v>
       </c>
-      <c r="AL13">
+      <c r="AL14">
         <v>38</v>
       </c>
-      <c r="AM13">
-        <v>1000</v>
-      </c>
-      <c r="AN13">
-        <v>13.5</v>
-      </c>
-      <c r="AO13">
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>13</v>
+      </c>
+      <c r="AO14">
         <v>80</v>
       </c>
-      <c r="AP13">
+      <c r="AP14">
         <v>13</v>
       </c>
-      <c r="AQ13">
+      <c r="AQ14">
         <v>14.5</v>
       </c>
-      <c r="AR13">
+      <c r="AR14">
         <v>30</v>
       </c>
-      <c r="AS13">
+      <c r="AS14">
         <v>38</v>
       </c>
-      <c r="AT13">
+      <c r="AT14">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU13">
+      <c r="AU14">
         <v>7.4</v>
       </c>
-      <c r="AV13">
+      <c r="AV14">
         <v>17</v>
       </c>
-      <c r="AW13">
+      <c r="AW14">
         <v>29</v>
       </c>
-      <c r="AX13">
+      <c r="AX14">
         <v>10</v>
       </c>
-      <c r="AY13">
+      <c r="AY14">
         <v>9.4</v>
       </c>
-      <c r="AZ13">
+      <c r="AZ14">
         <v>17</v>
       </c>
-      <c r="BA13">
+      <c r="BA14">
         <v>32</v>
       </c>
-      <c r="BB13">
+      <c r="BB14">
         <v>18.5</v>
       </c>
-      <c r="BC13">
+      <c r="BC14">
         <v>17.5</v>
       </c>
-      <c r="BD13">
+      <c r="BD14">
         <v>23</v>
       </c>
-      <c r="BE13">
+      <c r="BE14">
         <v>38</v>
       </c>
-      <c r="BF13">
+      <c r="BF14">
         <v>11.5</v>
       </c>
-      <c r="BG13">
+      <c r="BG14">
         <v>32</v>
       </c>
-      <c r="BH13">
-        <v>3.35</v>
-      </c>
-      <c r="BI13">
+      <c r="BH14">
+        <v>3.4</v>
+      </c>
+      <c r="BI14">
         <v>3.1</v>
       </c>
-      <c r="BJ13">
+      <c r="BJ14">
         <v>12</v>
       </c>
-      <c r="BK13">
+      <c r="BK14">
+        <v>4.1</v>
+      </c>
+      <c r="BL14">
+        <v>150</v>
+      </c>
+      <c r="BM14">
+        <v>6</v>
+      </c>
+      <c r="BN14">
+        <v>5.3</v>
+      </c>
+      <c r="BO14">
         <v>4.2</v>
       </c>
-      <c r="BL13">
-        <v>160</v>
-      </c>
-      <c r="BM13">
-        <v>6.2</v>
-      </c>
-      <c r="BN13">
+      <c r="BP14">
+        <v>16</v>
+      </c>
+      <c r="BQ14">
+        <v>4.5</v>
+      </c>
+      <c r="BR14">
+        <v>34</v>
+      </c>
+      <c r="BS14">
         <v>5.3</v>
       </c>
-      <c r="BO13">
-        <v>4.1</v>
-      </c>
-      <c r="BP13">
-        <v>16</v>
-      </c>
-      <c r="BQ13">
-        <v>4.6</v>
-      </c>
-      <c r="BR13">
-        <v>34</v>
-      </c>
-      <c r="BS13">
-        <v>5.4</v>
-      </c>
-      <c r="BT13">
+      <c r="BT14">
         <v>9.4</v>
       </c>
-      <c r="BU13">
-        <v>7.2</v>
-      </c>
-      <c r="BV13">
-        <v>48</v>
-      </c>
-      <c r="BW13">
+      <c r="BU14">
+        <v>7</v>
+      </c>
+      <c r="BV14">
+        <v>46</v>
+      </c>
+      <c r="BW14">
+        <v>5.6</v>
+      </c>
+      <c r="BX14">
+        <v>60</v>
+      </c>
+      <c r="BY14">
         <v>5.7</v>
       </c>
-      <c r="BX13">
-        <v>60</v>
-      </c>
-      <c r="BY13">
-        <v>5.8</v>
-      </c>
-      <c r="BZ13">
-        <v>30</v>
-      </c>
-      <c r="CA13">
-        <v>5.3</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>124</v>
+      <c r="BZ14">
+        <v>29</v>
+      </c>
+      <c r="CA14">
+        <v>5.2</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -400,7 +400,7 @@
     <t>Elche</t>
   </si>
   <si>
-    <t>2026-09-16 02:44:11</t>
+    <t>2026-09-16 04:59:18</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>600</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I2">
         <v>870</v>
@@ -1042,10 +1042,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1245,13 +1245,13 @@
         <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.43</v>
@@ -1260,16 +1260,16 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1278,16 +1278,16 @@
         <v>4.1</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U3">
         <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1478,22 +1478,22 @@
         <v>117</v>
       </c>
       <c r="F4">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="G4">
         <v>1.85</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>2.18</v>
       </c>
       <c r="I4">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>118</v>
       </c>
       <c r="F5">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G5">
         <v>600</v>
@@ -1732,7 +1732,7 @@
         <v>870</v>
       </c>
       <c r="J5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
         <v>1.01</v>
@@ -1965,7 +1965,7 @@
         <v>2.24</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
         <v>3.25</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
         <v>1.96</v>
@@ -2688,7 +2688,7 @@
         <v>122</v>
       </c>
       <c r="F9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G9">
         <v>11</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -3656,13 +3656,13 @@
         <v>126</v>
       </c>
       <c r="F13">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="G13">
         <v>2.42</v>
       </c>
       <c r="H13">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="I13">
         <v>5.2</v>
@@ -3671,7 +3671,7 @@
         <v>3.25</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3898,19 +3898,19 @@
         <v>127</v>
       </c>
       <c r="F14">
+        <v>1.89</v>
+      </c>
+      <c r="G14">
         <v>1.9</v>
-      </c>
-      <c r="G14">
-        <v>1.91</v>
       </c>
       <c r="H14">
         <v>4.8</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
         <v>3.8</v>
@@ -3925,13 +3925,13 @@
         <v>3.85</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P14">
         <v>1.96</v>
       </c>
       <c r="Q14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
         <v>1.37</v>
@@ -3940,7 +3940,7 @@
         <v>3.55</v>
       </c>
       <c r="T14">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
         <v>2.1</v>
@@ -3973,7 +3973,7 @@
         <v>19</v>
       </c>
       <c r="AE14">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="AF14">
         <v>11.5</v>
@@ -3982,7 +3982,7 @@
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
         <v>70</v>
@@ -4009,7 +4009,7 @@
         <v>13</v>
       </c>
       <c r="AQ14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR14">
         <v>30</v>
@@ -4075,16 +4075,16 @@
         <v>150</v>
       </c>
       <c r="BM14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BN14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ14">
         <v>4.5</v>
@@ -4093,7 +4093,7 @@
         <v>34</v>
       </c>
       <c r="BS14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT14">
         <v>9.4</v>
@@ -4105,19 +4105,19 @@
         <v>46</v>
       </c>
       <c r="BW14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX14">
         <v>60</v>
       </c>
       <c r="BY14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ14">
         <v>29</v>
       </c>
       <c r="CA14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB14" t="s">
         <v>128</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="136">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Indonesian Super League</t>
   </si>
   <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Kazakhstan Premier League</t>
   </si>
   <si>
@@ -295,12 +298,18 @@
     <t>08:30:00</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
     <t>11:00:00</t>
   </si>
   <si>
     <t>12:00:00</t>
   </si>
   <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -331,6 +340,9 @@
     <t>Arema Cronus</t>
   </si>
   <si>
+    <t>Chernomorets Odesa</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
@@ -340,6 +352,9 @@
     <t>FC Zhetysu</t>
   </si>
   <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
     <t>FK Kyzyl-Zhar</t>
   </si>
   <si>
@@ -370,6 +385,9 @@
     <t>Persik Kediri</t>
   </si>
   <si>
+    <t>Obolon-Brovar Kiev</t>
+  </si>
+  <si>
     <t>Zhenys</t>
   </si>
   <si>
@@ -379,6 +397,9 @@
     <t>FK Kaspyi Aktau</t>
   </si>
   <si>
+    <t>Kryvbas Krivyi Rih</t>
+  </si>
+  <si>
     <t>FK Kaisar</t>
   </si>
   <si>
@@ -400,7 +421,7 @@
     <t>Elche</t>
   </si>
   <si>
-    <t>2026-09-16 04:59:18</t>
+    <t>2026-09-16 07:13:15</t>
   </si>
 </sst>
 </file>
@@ -732,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -982,31 +1003,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F2">
+        <v>1.04</v>
+      </c>
+      <c r="G2">
+        <v>1.14</v>
+      </c>
+      <c r="H2">
         <v>1.1</v>
-      </c>
-      <c r="G2">
-        <v>600</v>
-      </c>
-      <c r="H2">
-        <v>1.12</v>
       </c>
       <c r="I2">
         <v>870</v>
       </c>
       <c r="J2">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -1042,10 +1063,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1216,7 +1237,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1224,46 +1245,46 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>3.8</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I3">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
         <v>1.66</v>
@@ -1272,19 +1293,19 @@
         <v>2.28</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W3">
         <v>1.32</v>
@@ -1458,7 +1479,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1466,241 +1487,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H4">
         <v>2.18</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>950</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1708,276 +1729,276 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="G5">
         <v>600</v>
       </c>
       <c r="H5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
         <v>870</v>
       </c>
       <c r="J5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
         <v>950</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>2.24</v>
+        <v>1.17</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>600</v>
       </c>
       <c r="H6">
-        <v>3.25</v>
+        <v>1.13</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>870</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>1.18</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1992,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2184,39 +2205,39 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="G7">
         <v>600</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="I7">
         <v>870</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2234,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
         <v>1.01</v>
@@ -2426,36 +2447,36 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J8">
         <v>1.1</v>
@@ -2476,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
         <v>1.01</v>
@@ -2668,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2676,31 +2697,31 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>600</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J9">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2718,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -2910,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2918,31 +2939,31 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
         <v>1000</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
         <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -2960,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q10">
         <v>1.01</v>
@@ -3152,42 +3173,42 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="G11">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="H11">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="I11">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>1.13</v>
       </c>
       <c r="K11">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3202,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.63</v>
+        <v>1.12</v>
       </c>
       <c r="Q11">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3394,39 +3415,39 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3444,10 +3465,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="Q12">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3636,39 +3657,39 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="G13">
-        <v>2.42</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>2.86</v>
+        <v>1.18</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>870</v>
       </c>
       <c r="J13">
-        <v>3.25</v>
+        <v>1.29</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3686,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3878,249 +3899,733 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14">
+        <v>1.76</v>
+      </c>
+      <c r="G14">
+        <v>2.46</v>
+      </c>
+      <c r="H14">
+        <v>1.1</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.01</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.07</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
         <v>88</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15">
+        <v>1.04</v>
+      </c>
+      <c r="G15">
+        <v>600</v>
+      </c>
+      <c r="H15">
+        <v>1.04</v>
+      </c>
+      <c r="I15">
+        <v>870</v>
+      </c>
+      <c r="J15">
+        <v>1.01</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>2.1</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>89</v>
       </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F14">
-        <v>1.89</v>
-      </c>
-      <c r="G14">
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16">
         <v>1.9</v>
       </c>
-      <c r="H14">
+      <c r="G16">
+        <v>1.91</v>
+      </c>
+      <c r="H16">
         <v>4.8</v>
       </c>
-      <c r="I14">
-        <v>5</v>
-      </c>
-      <c r="J14">
+      <c r="I16">
+        <v>4.9</v>
+      </c>
+      <c r="J16">
         <v>3.75</v>
       </c>
-      <c r="K14">
+      <c r="K16">
         <v>3.8</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>1.07</v>
       </c>
-      <c r="N14">
-        <v>3.85</v>
-      </c>
-      <c r="O14">
+      <c r="N16">
+        <v>3.9</v>
+      </c>
+      <c r="O16">
         <v>1.32</v>
       </c>
-      <c r="P14">
+      <c r="P16">
         <v>1.96</v>
       </c>
-      <c r="Q14">
+      <c r="Q16">
+        <v>1.97</v>
+      </c>
+      <c r="R16">
+        <v>1.37</v>
+      </c>
+      <c r="S16">
+        <v>3.45</v>
+      </c>
+      <c r="T16">
+        <v>1.86</v>
+      </c>
+      <c r="U16">
+        <v>2.1</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>15</v>
+      </c>
+      <c r="Y16">
+        <v>17</v>
+      </c>
+      <c r="Z16">
+        <v>42</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>9</v>
+      </c>
+      <c r="AC16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD16">
+        <v>19</v>
+      </c>
+      <c r="AE16">
+        <v>610</v>
+      </c>
+      <c r="AF16">
+        <v>11.5</v>
+      </c>
+      <c r="AG16">
+        <v>10.5</v>
+      </c>
+      <c r="AH16">
+        <v>19.5</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>21</v>
+      </c>
+      <c r="AK16">
+        <v>20</v>
+      </c>
+      <c r="AL16">
+        <v>38</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>13</v>
+      </c>
+      <c r="AO16">
+        <v>80</v>
+      </c>
+      <c r="AP16">
+        <v>13</v>
+      </c>
+      <c r="AQ16">
+        <v>15</v>
+      </c>
+      <c r="AR16">
+        <v>21</v>
+      </c>
+      <c r="AS16">
+        <v>38</v>
+      </c>
+      <c r="AT16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>17</v>
+      </c>
+      <c r="AW16">
+        <v>29</v>
+      </c>
+      <c r="AX16">
+        <v>10</v>
+      </c>
+      <c r="AY16">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16">
+        <v>17</v>
+      </c>
+      <c r="BA16">
+        <v>32</v>
+      </c>
+      <c r="BB16">
+        <v>18.5</v>
+      </c>
+      <c r="BC16">
+        <v>17.5</v>
+      </c>
+      <c r="BD16">
+        <v>23</v>
+      </c>
+      <c r="BE16">
+        <v>38</v>
+      </c>
+      <c r="BF16">
+        <v>11.5</v>
+      </c>
+      <c r="BG16">
+        <v>32</v>
+      </c>
+      <c r="BH16">
+        <v>3.45</v>
+      </c>
+      <c r="BI16">
+        <v>3.1</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
         <v>1.96</v>
       </c>
-      <c r="R14">
-        <v>1.37</v>
-      </c>
-      <c r="S14">
-        <v>3.55</v>
-      </c>
-      <c r="T14">
-        <v>1.84</v>
-      </c>
-      <c r="U14">
-        <v>2.1</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>15</v>
-      </c>
-      <c r="Y14">
-        <v>17</v>
-      </c>
-      <c r="Z14">
-        <v>42</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>9</v>
-      </c>
-      <c r="AC14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14">
-        <v>19</v>
-      </c>
-      <c r="AE14">
-        <v>610</v>
-      </c>
-      <c r="AF14">
-        <v>11.5</v>
-      </c>
-      <c r="AG14">
-        <v>10.5</v>
-      </c>
-      <c r="AH14">
-        <v>19.5</v>
-      </c>
-      <c r="AI14">
-        <v>70</v>
-      </c>
-      <c r="AJ14">
-        <v>21</v>
-      </c>
-      <c r="AK14">
-        <v>20</v>
-      </c>
-      <c r="AL14">
-        <v>38</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>13</v>
-      </c>
-      <c r="AO14">
-        <v>80</v>
-      </c>
-      <c r="AP14">
-        <v>13</v>
-      </c>
-      <c r="AQ14">
-        <v>15</v>
-      </c>
-      <c r="AR14">
-        <v>30</v>
-      </c>
-      <c r="AS14">
-        <v>38</v>
-      </c>
-      <c r="AT14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU14">
-        <v>7.4</v>
-      </c>
-      <c r="AV14">
-        <v>17</v>
-      </c>
-      <c r="AW14">
-        <v>29</v>
-      </c>
-      <c r="AX14">
-        <v>10</v>
-      </c>
-      <c r="AY14">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14">
-        <v>17</v>
-      </c>
-      <c r="BA14">
-        <v>32</v>
-      </c>
-      <c r="BB14">
-        <v>18.5</v>
-      </c>
-      <c r="BC14">
-        <v>17.5</v>
-      </c>
-      <c r="BD14">
-        <v>23</v>
-      </c>
-      <c r="BE14">
-        <v>38</v>
-      </c>
-      <c r="BF14">
-        <v>11.5</v>
-      </c>
-      <c r="BG14">
-        <v>32</v>
-      </c>
-      <c r="BH14">
-        <v>3.4</v>
-      </c>
-      <c r="BI14">
-        <v>3.1</v>
-      </c>
-      <c r="BJ14">
-        <v>12</v>
-      </c>
-      <c r="BK14">
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.96</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
         <v>4.1</v>
       </c>
-      <c r="BL14">
-        <v>150</v>
-      </c>
-      <c r="BM14">
-        <v>5.9</v>
-      </c>
-      <c r="BN14">
-        <v>5.4</v>
-      </c>
-      <c r="BO14">
-        <v>4.1</v>
-      </c>
-      <c r="BP14">
-        <v>16.5</v>
-      </c>
-      <c r="BQ14">
-        <v>4.5</v>
-      </c>
-      <c r="BR14">
-        <v>34</v>
-      </c>
-      <c r="BS14">
-        <v>5.2</v>
-      </c>
-      <c r="BT14">
-        <v>9.4</v>
-      </c>
-      <c r="BU14">
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.96</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.96</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
         <v>7</v>
       </c>
-      <c r="BV14">
-        <v>46</v>
-      </c>
-      <c r="BW14">
-        <v>5.4</v>
-      </c>
-      <c r="BX14">
-        <v>60</v>
-      </c>
-      <c r="BY14">
-        <v>5.6</v>
-      </c>
-      <c r="BZ14">
-        <v>29</v>
-      </c>
-      <c r="CA14">
-        <v>5.1</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>128</v>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.96</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.96</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.96</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -265,12 +265,18 @@
     <t>Indonesian Super League</t>
   </si>
   <si>
+    <t>Chinese League 1</t>
+  </si>
+  <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
     <t>Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>Estonian Premier League</t>
   </si>
   <si>
@@ -304,6 +310,12 @@
     <t>11:00:00</t>
   </si>
   <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
     <t>12:00:00</t>
   </si>
   <si>
@@ -340,18 +352,30 @@
     <t>Arema Cronus</t>
   </si>
   <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
     <t>Chernomorets Odesa</t>
   </si>
   <si>
+    <t>Dalian Kun City FC</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
+    <t>Nantong Zhiyun F.C</t>
+  </si>
+  <si>
+    <t>Zhejiang Greentown</t>
+  </si>
+  <si>
+    <t>FC Zhetysu</t>
+  </si>
+  <si>
     <t>Madura Utd</t>
   </si>
   <si>
-    <t>FC Zhetysu</t>
-  </si>
-  <si>
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
@@ -385,18 +409,30 @@
     <t>Persik Kediri</t>
   </si>
   <si>
+    <t>Guangdong GZ-Power FC</t>
+  </si>
+  <si>
     <t>Obolon-Brovar Kiev</t>
   </si>
   <si>
+    <t>Ningbo Professional</t>
+  </si>
+  <si>
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
+    <t>FK Kaspyi Aktau</t>
+  </si>
+  <si>
     <t>Psim Yogyakarta</t>
   </si>
   <si>
-    <t>FK Kaspyi Aktau</t>
-  </si>
-  <si>
     <t>Kryvbas Krivyi Rih</t>
   </si>
   <si>
@@ -421,7 +457,7 @@
     <t>Elche</t>
   </si>
   <si>
-    <t>2026-09-16 07:13:15</t>
+    <t>2026-09-16 09:27:27</t>
   </si>
 </sst>
 </file>
@@ -753,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1003,16 +1039,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F2">
         <v>1.04</v>
@@ -1021,7 +1057,7 @@
         <v>1.14</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I2">
         <v>870</v>
@@ -1237,7 +1273,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1245,16 +1281,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>3.8</v>
@@ -1263,7 +1299,7 @@
         <v>4.3</v>
       </c>
       <c r="H3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I3">
         <v>2.28</v>
@@ -1275,16 +1311,16 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
         <v>1.66</v>
@@ -1296,106 +1332,106 @@
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
         <v>1.97</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W3">
         <v>1.32</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
@@ -1416,7 +1452,7 @@
         <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1479,7 +1515,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1487,70 +1523,70 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>1.24</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>1.24</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1721,7 +1757,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1729,58 +1765,58 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F5">
+        <v>1.04</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.04</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.01</v>
+      </c>
+      <c r="K5">
+        <v>920</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
         <v>1.1</v>
       </c>
-      <c r="G5">
-        <v>600</v>
-      </c>
-      <c r="H5">
+      <c r="O5">
+        <v>1.01</v>
+      </c>
+      <c r="P5">
         <v>1.1</v>
       </c>
-      <c r="I5">
-        <v>870</v>
-      </c>
-      <c r="J5">
-        <v>1.1</v>
-      </c>
-      <c r="K5">
-        <v>950</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.24</v>
-      </c>
-      <c r="O5">
-        <v>1.01</v>
-      </c>
-      <c r="P5">
-        <v>1.24</v>
-      </c>
       <c r="Q5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R5">
         <v>1.06</v>
       </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1963,7 +1999,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1971,725 +2007,725 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F6">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="G6">
         <v>600</v>
       </c>
       <c r="H6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="I6">
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
         <v>950</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F7">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
         <v>870</v>
       </c>
-      <c r="J7">
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
         <v>1.1</v>
       </c>
-      <c r="K7">
-        <v>950</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Q7">
         <v>1.01</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="G8">
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I8">
         <v>870</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K8">
         <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2697,999 +2733,999 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F9">
         <v>1.04</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H9">
         <v>1.04</v>
       </c>
       <c r="I9">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J9">
+        <v>1.01</v>
+      </c>
+      <c r="K9">
+        <v>880</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
         <v>1.1</v>
       </c>
-      <c r="K9">
-        <v>950</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F11">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>11</v>
+        <v>600</v>
       </c>
       <c r="H11">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
         <v>950</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.07</v>
+        <v>1.84</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>7</v>
+        <v>600</v>
       </c>
       <c r="H13">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
         <v>870</v>
       </c>
       <c r="J13">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3707,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
         <v>1.01</v>
@@ -3899,30 +3935,30 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F14">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="G14">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H14">
         <v>1.1</v>
@@ -3931,7 +3967,7 @@
         <v>1000</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3949,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q14">
         <v>1.01</v>
@@ -4141,39 +4177,39 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="G15">
-        <v>600</v>
+        <v>11</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I15">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J15">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4191,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q15">
         <v>1.01</v>
@@ -4383,249 +4419,1217 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F16">
+        <v>1.1</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
+      </c>
+      <c r="H16">
+        <v>1.1</v>
+      </c>
+      <c r="I16">
+        <v>1000</v>
+      </c>
+      <c r="J16">
+        <v>1.1</v>
+      </c>
+      <c r="K16">
+        <v>950</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.07</v>
+      </c>
+      <c r="Q16">
+        <v>1.01</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>1.7</v>
+      </c>
+      <c r="I17">
+        <v>2.18</v>
+      </c>
+      <c r="J17">
+        <v>2.5</v>
+      </c>
+      <c r="K17">
+        <v>6.2</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.62</v>
+      </c>
+      <c r="Q17">
+        <v>2.06</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18">
+        <v>1.76</v>
+      </c>
+      <c r="G18">
+        <v>2.3</v>
+      </c>
+      <c r="H18">
+        <v>3.45</v>
+      </c>
+      <c r="I18">
+        <v>7.4</v>
+      </c>
+      <c r="J18">
+        <v>3.4</v>
+      </c>
+      <c r="K18">
+        <v>7.2</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.65</v>
+      </c>
+      <c r="Q18">
+        <v>1.87</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19">
+        <v>1.88</v>
+      </c>
+      <c r="G19">
+        <v>2.48</v>
+      </c>
+      <c r="H19">
+        <v>1.12</v>
+      </c>
+      <c r="I19">
+        <v>4.4</v>
+      </c>
+      <c r="J19">
+        <v>3.35</v>
+      </c>
+      <c r="K19">
+        <v>950</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2.22</v>
+      </c>
+      <c r="Q19">
+        <v>1.54</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20">
+        <v>1.88</v>
+      </c>
+      <c r="G20">
         <v>1.9</v>
       </c>
-      <c r="G16">
-        <v>1.91</v>
-      </c>
-      <c r="H16">
+      <c r="H20">
         <v>4.8</v>
       </c>
-      <c r="I16">
-        <v>4.9</v>
-      </c>
-      <c r="J16">
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
         <v>3.75</v>
       </c>
-      <c r="K16">
+      <c r="K20">
         <v>3.8</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>1.07</v>
       </c>
-      <c r="N16">
+      <c r="N20">
         <v>3.9</v>
       </c>
-      <c r="O16">
+      <c r="O20">
         <v>1.32</v>
       </c>
-      <c r="P16">
+      <c r="P20">
         <v>1.96</v>
       </c>
-      <c r="Q16">
+      <c r="Q20">
         <v>1.97</v>
       </c>
-      <c r="R16">
+      <c r="R20">
         <v>1.37</v>
       </c>
-      <c r="S16">
-        <v>3.45</v>
-      </c>
-      <c r="T16">
+      <c r="S20">
+        <v>3.5</v>
+      </c>
+      <c r="T20">
         <v>1.86</v>
       </c>
-      <c r="U16">
+      <c r="U20">
         <v>2.1</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
         <v>15</v>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <v>17</v>
       </c>
-      <c r="Z16">
+      <c r="Z20">
         <v>42</v>
       </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
         <v>9</v>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <v>19</v>
       </c>
-      <c r="AE16">
+      <c r="AE20">
         <v>610</v>
       </c>
-      <c r="AF16">
+      <c r="AF20">
         <v>11.5</v>
       </c>
-      <c r="AG16">
+      <c r="AG20">
         <v>10.5</v>
       </c>
-      <c r="AH16">
+      <c r="AH20">
         <v>19.5</v>
       </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
         <v>21</v>
       </c>
-      <c r="AK16">
+      <c r="AK20">
         <v>20</v>
       </c>
-      <c r="AL16">
+      <c r="AL20">
         <v>38</v>
       </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
         <v>13</v>
       </c>
-      <c r="AO16">
-        <v>80</v>
-      </c>
-      <c r="AP16">
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
         <v>13</v>
       </c>
-      <c r="AQ16">
+      <c r="AQ20">
         <v>15</v>
       </c>
-      <c r="AR16">
-        <v>21</v>
-      </c>
-      <c r="AS16">
+      <c r="AR20">
+        <v>30</v>
+      </c>
+      <c r="AS20">
         <v>38</v>
       </c>
-      <c r="AT16">
+      <c r="AT20">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU16">
+      <c r="AU20">
         <v>7.4</v>
       </c>
-      <c r="AV16">
+      <c r="AV20">
+        <v>16.5</v>
+      </c>
+      <c r="AW20">
+        <v>29</v>
+      </c>
+      <c r="AX20">
+        <v>10</v>
+      </c>
+      <c r="AY20">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20">
         <v>17</v>
       </c>
-      <c r="AW16">
+      <c r="BA20">
+        <v>32</v>
+      </c>
+      <c r="BB20">
+        <v>18.5</v>
+      </c>
+      <c r="BC20">
+        <v>17</v>
+      </c>
+      <c r="BD20">
+        <v>23</v>
+      </c>
+      <c r="BE20">
+        <v>38</v>
+      </c>
+      <c r="BF20">
+        <v>11.5</v>
+      </c>
+      <c r="BG20">
+        <v>32</v>
+      </c>
+      <c r="BH20">
+        <v>3.4</v>
+      </c>
+      <c r="BI20">
+        <v>3.1</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>4.1</v>
+      </c>
+      <c r="BL20">
+        <v>150</v>
+      </c>
+      <c r="BM20">
+        <v>5.9</v>
+      </c>
+      <c r="BN20">
+        <v>5.4</v>
+      </c>
+      <c r="BO20">
+        <v>4.2</v>
+      </c>
+      <c r="BP20">
+        <v>16.5</v>
+      </c>
+      <c r="BQ20">
+        <v>4.6</v>
+      </c>
+      <c r="BR20">
+        <v>34</v>
+      </c>
+      <c r="BS20">
+        <v>5.2</v>
+      </c>
+      <c r="BT20">
+        <v>9.4</v>
+      </c>
+      <c r="BU20">
+        <v>7</v>
+      </c>
+      <c r="BV20">
+        <v>46</v>
+      </c>
+      <c r="BW20">
+        <v>5.4</v>
+      </c>
+      <c r="BX20">
+        <v>60</v>
+      </c>
+      <c r="BY20">
+        <v>5.6</v>
+      </c>
+      <c r="BZ20">
         <v>29</v>
       </c>
-      <c r="AX16">
-        <v>10</v>
-      </c>
-      <c r="AY16">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16">
-        <v>17</v>
-      </c>
-      <c r="BA16">
-        <v>32</v>
-      </c>
-      <c r="BB16">
-        <v>18.5</v>
-      </c>
-      <c r="BC16">
-        <v>17.5</v>
-      </c>
-      <c r="BD16">
-        <v>23</v>
-      </c>
-      <c r="BE16">
-        <v>38</v>
-      </c>
-      <c r="BF16">
-        <v>11.5</v>
-      </c>
-      <c r="BG16">
-        <v>32</v>
-      </c>
-      <c r="BH16">
-        <v>3.45</v>
-      </c>
-      <c r="BI16">
-        <v>3.1</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.96</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.96</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>4.1</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.96</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.96</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>7</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.96</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.96</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
-      <c r="CA16">
-        <v>1.96</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>135</v>
+      <c r="CA20">
+        <v>5.1</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="165">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Japanese J League 2</t>
   </si>
   <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
     <t>Indonesian Super League</t>
   </si>
   <si>
@@ -277,6 +280,12 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Turkish 1 Lig</t>
+  </si>
+  <si>
     <t>Estonian Premier League</t>
   </si>
   <si>
@@ -301,9 +310,15 @@
     <t>04:00:00</t>
   </si>
   <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
     <t>08:30:00</t>
   </si>
   <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
@@ -322,6 +337,12 @@
     <t>12:30:00</t>
   </si>
   <si>
+    <t>12:45:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -349,9 +370,15 @@
     <t>Vanraure Hachinohe</t>
   </si>
   <si>
+    <t>Changchun Xidu</t>
+  </si>
+  <si>
     <t>Arema Cronus</t>
   </si>
   <si>
+    <t>Wuhan Three Towns II</t>
+  </si>
+  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
@@ -379,6 +406,12 @@
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Bandirmaspor</t>
+  </si>
+  <si>
     <t>FK Kyzyl-Zhar</t>
   </si>
   <si>
@@ -391,6 +424,9 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Muglaspor</t>
+  </si>
+  <si>
     <t>Zeljeznicar</t>
   </si>
   <si>
@@ -406,9 +442,15 @@
     <t>Tegevajaro Miyazaki</t>
   </si>
   <si>
+    <t>Guangdong Mingtu</t>
+  </si>
+  <si>
     <t>Persik Kediri</t>
   </si>
   <si>
+    <t>Haimen Codion</t>
+  </si>
+  <si>
     <t>Guangdong GZ-Power FC</t>
   </si>
   <si>
@@ -436,6 +478,12 @@
     <t>Kryvbas Krivyi Rih</t>
   </si>
   <si>
+    <t>Hapoel Petach Tikva</t>
+  </si>
+  <si>
+    <t>Umraniyespor</t>
+  </si>
+  <si>
     <t>FK Kaisar</t>
   </si>
   <si>
@@ -448,6 +496,9 @@
     <t>CSKA 1948 Sofia</t>
   </si>
   <si>
+    <t>76 Igdir Belediyespor</t>
+  </si>
+  <si>
     <t>Celik Zenica</t>
   </si>
   <si>
@@ -457,7 +508,7 @@
     <t>Elche</t>
   </si>
   <si>
-    <t>2026-09-16 09:27:27</t>
+    <t>2026-09-16 11:42:40</t>
   </si>
 </sst>
 </file>
@@ -789,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1039,16 +1090,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>1.04</v>
@@ -1273,7 +1324,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1281,28 +1332,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>3.8</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
         <v>2.14</v>
       </c>
       <c r="I3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J3">
         <v>3.3</v>
@@ -1311,7 +1362,7 @@
         <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1341,7 +1392,7 @@
         <v>1.9</v>
       </c>
       <c r="V3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W3">
         <v>1.32</v>
@@ -1350,7 +1401,7 @@
         <v>13</v>
       </c>
       <c r="Y3">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
         <v>16</v>
@@ -1362,7 +1413,7 @@
         <v>15</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD3">
         <v>13.5</v>
@@ -1404,7 +1455,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3">
         <v>11</v>
@@ -1416,10 +1467,10 @@
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3">
         <v>19.5</v>
@@ -1434,25 +1485,25 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1515,7 +1566,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1523,70 +1574,70 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F4">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="G4">
-        <v>1.85</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>1.06</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="Q4">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1757,7 +1808,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1765,70 +1816,70 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>920</v>
+        <v>6.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>2.78</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1999,42 +2050,42 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2043,22 +2094,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="Q6">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="S6">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2241,132 +2292,132 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
-        <v>870</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R7">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP7">
         <v>1.01</v>
@@ -2483,7 +2534,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2491,31 +2542,31 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>600</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>870</v>
       </c>
       <c r="J8">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2527,22 +2578,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="R8">
         <v>1.08</v>
       </c>
       <c r="S8">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2551,10 +2602,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2725,42 +2776,42 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2793,10 +2844,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2967,7 +3018,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2975,190 +3026,190 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F10">
-        <v>1.87</v>
+        <v>1.19</v>
       </c>
       <c r="G10">
-        <v>1.93</v>
+        <v>600</v>
       </c>
       <c r="H10">
-        <v>3.7</v>
+        <v>1.13</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>870</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L10">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="O10">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="R10">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>2.06</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
         <v>1000</v>
       </c>
       <c r="AA10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3167,10 +3218,10 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
@@ -3188,7 +3239,7 @@
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3209,78 +3260,78 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F11">
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>110</v>
       </c>
       <c r="J11">
+        <v>1.1</v>
+      </c>
+      <c r="K11">
+        <v>880</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
         <v>1.12</v>
       </c>
-      <c r="K11">
-        <v>950</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>1.24</v>
-      </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Q11">
+        <v>1.34</v>
+      </c>
+      <c r="R11">
+        <v>1.06</v>
+      </c>
+      <c r="S11">
+        <v>1.34</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
         <v>1.02</v>
       </c>
-      <c r="R11">
-        <v>1.08</v>
-      </c>
-      <c r="S11">
-        <v>1.31</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3451,192 +3502,192 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="G12">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H12">
+        <v>3.6</v>
+      </c>
+      <c r="I12">
+        <v>3.9</v>
+      </c>
+      <c r="J12">
+        <v>4.3</v>
+      </c>
+      <c r="K12">
+        <v>4.7</v>
+      </c>
+      <c r="L12">
+        <v>1.18</v>
+      </c>
+      <c r="M12">
+        <v>1.02</v>
+      </c>
+      <c r="N12">
+        <v>7.2</v>
+      </c>
+      <c r="O12">
+        <v>1.13</v>
+      </c>
+      <c r="P12">
         <v>3.15</v>
       </c>
-      <c r="I12">
-        <v>3.65</v>
-      </c>
-      <c r="J12">
-        <v>3.35</v>
-      </c>
-      <c r="K12">
-        <v>4.1</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>3.3</v>
-      </c>
-      <c r="O12">
-        <v>1.32</v>
-      </c>
-      <c r="P12">
-        <v>1.84</v>
-      </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="R12">
+        <v>1.88</v>
+      </c>
+      <c r="S12">
+        <v>2.02</v>
+      </c>
+      <c r="T12">
+        <v>1.45</v>
+      </c>
+      <c r="U12">
+        <v>2.94</v>
+      </c>
+      <c r="V12">
         <v>1.34</v>
       </c>
-      <c r="S12">
-        <v>2.78</v>
-      </c>
-      <c r="T12">
-        <v>1.01</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.38</v>
-      </c>
       <c r="W12">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI12">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
@@ -3651,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO12">
         <v>1.01</v>
@@ -3693,24 +3744,24 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F13">
         <v>1.1</v>
@@ -3731,453 +3782,453 @@
         <v>950</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
         <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P14">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4185,999 +4236,999 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
-        <v>11</v>
+        <v>600</v>
       </c>
       <c r="H15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
         <v>950</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>1.45</v>
       </c>
       <c r="H16">
-        <v>1.1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J16">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P16">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="G17">
+        <v>1.98</v>
+      </c>
+      <c r="H17">
+        <v>4.6</v>
+      </c>
+      <c r="I17">
+        <v>5.1</v>
+      </c>
+      <c r="J17">
+        <v>3.5</v>
+      </c>
+      <c r="K17">
+        <v>3.8</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>3.3</v>
+      </c>
+      <c r="O17">
+        <v>1.36</v>
+      </c>
+      <c r="P17">
+        <v>1.78</v>
+      </c>
+      <c r="Q17">
+        <v>2.1</v>
+      </c>
+      <c r="R17">
+        <v>1.26</v>
+      </c>
+      <c r="S17">
+        <v>3.4</v>
+      </c>
+      <c r="T17">
+        <v>1.86</v>
+      </c>
+      <c r="U17">
+        <v>1.86</v>
+      </c>
+      <c r="V17">
+        <v>1.25</v>
+      </c>
+      <c r="W17">
+        <v>2.02</v>
+      </c>
+      <c r="X17">
+        <v>12.5</v>
+      </c>
+      <c r="Y17">
+        <v>15.5</v>
+      </c>
+      <c r="Z17">
+        <v>42</v>
+      </c>
+      <c r="AA17">
+        <v>140</v>
+      </c>
+      <c r="AB17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC17">
+        <v>9.4</v>
+      </c>
+      <c r="AD17">
+        <v>20</v>
+      </c>
+      <c r="AE17">
+        <v>85</v>
+      </c>
+      <c r="AF17">
+        <v>11.5</v>
+      </c>
+      <c r="AG17">
+        <v>10.5</v>
+      </c>
+      <c r="AH17">
+        <v>21</v>
+      </c>
+      <c r="AI17">
+        <v>90</v>
+      </c>
+      <c r="AJ17">
+        <v>22</v>
+      </c>
+      <c r="AK17">
+        <v>22</v>
+      </c>
+      <c r="AL17">
+        <v>48</v>
+      </c>
+      <c r="AM17">
+        <v>150</v>
+      </c>
+      <c r="AN17">
+        <v>16.5</v>
+      </c>
+      <c r="AO17">
+        <v>110</v>
+      </c>
+      <c r="AP17">
+        <v>10.5</v>
+      </c>
+      <c r="AQ17">
+        <v>13</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
         <v>7</v>
       </c>
-      <c r="H17">
-        <v>1.7</v>
-      </c>
-      <c r="I17">
-        <v>2.18</v>
-      </c>
-      <c r="J17">
-        <v>2.5</v>
-      </c>
-      <c r="K17">
-        <v>6.2</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>1.62</v>
-      </c>
-      <c r="Q17">
-        <v>2.06</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
       <c r="AU17">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F18">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="G18">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H18">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="I18">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="K18">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.65</v>
+        <v>1.1</v>
       </c>
       <c r="Q18">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F19">
-        <v>1.88</v>
+        <v>1.19</v>
       </c>
       <c r="G19">
-        <v>2.48</v>
+        <v>11</v>
       </c>
       <c r="H19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I19">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>3.35</v>
+        <v>1.13</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5195,10 +5246,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.22</v>
+        <v>1.12</v>
       </c>
       <c r="Q19">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5387,249 +5438,1459 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20">
+        <v>1.1</v>
+      </c>
+      <c r="G20">
+        <v>1000</v>
+      </c>
+      <c r="H20">
+        <v>1.1</v>
+      </c>
+      <c r="I20">
+        <v>1000</v>
+      </c>
+      <c r="J20">
+        <v>1.1</v>
+      </c>
+      <c r="K20">
+        <v>950</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1.07</v>
+      </c>
+      <c r="Q20">
+        <v>1.01</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
         <v>91</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21">
+        <v>1.74</v>
+      </c>
+      <c r="I21">
+        <v>2.18</v>
+      </c>
+      <c r="J21">
+        <v>2.5</v>
+      </c>
+      <c r="K21">
+        <v>5.8</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.63</v>
+      </c>
+      <c r="Q21">
+        <v>1.92</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22">
+        <v>3.25</v>
+      </c>
+      <c r="G22">
+        <v>3.65</v>
+      </c>
+      <c r="H22">
+        <v>2.34</v>
+      </c>
+      <c r="I22">
+        <v>2.52</v>
+      </c>
+      <c r="J22">
+        <v>3.1</v>
+      </c>
+      <c r="K22">
+        <v>3.55</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.63</v>
+      </c>
+      <c r="Q22">
+        <v>1.9</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
         <v>92</v>
       </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20">
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23">
+        <v>1.76</v>
+      </c>
+      <c r="G23">
+        <v>2.3</v>
+      </c>
+      <c r="H23">
+        <v>3.55</v>
+      </c>
+      <c r="I23">
+        <v>7.2</v>
+      </c>
+      <c r="J23">
+        <v>1.76</v>
+      </c>
+      <c r="K23">
+        <v>6.8</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.64</v>
+      </c>
+      <c r="Q23">
+        <v>1.87</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24">
         <v>1.88</v>
       </c>
-      <c r="G20">
-        <v>1.9</v>
-      </c>
-      <c r="H20">
+      <c r="G24">
+        <v>2.36</v>
+      </c>
+      <c r="H24">
+        <v>1.12</v>
+      </c>
+      <c r="I24">
+        <v>4.6</v>
+      </c>
+      <c r="J24">
+        <v>3.35</v>
+      </c>
+      <c r="K24">
+        <v>950</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.06</v>
+      </c>
+      <c r="Q24">
+        <v>1.53</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25">
+        <v>1.88</v>
+      </c>
+      <c r="G25">
+        <v>1.89</v>
+      </c>
+      <c r="H25">
         <v>4.8</v>
       </c>
-      <c r="I20">
+      <c r="I25">
         <v>5</v>
       </c>
-      <c r="J20">
+      <c r="J25">
         <v>3.75</v>
       </c>
-      <c r="K20">
+      <c r="K25">
         <v>3.8</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>1.07</v>
       </c>
-      <c r="N20">
-        <v>3.9</v>
-      </c>
-      <c r="O20">
+      <c r="N25">
+        <v>3.85</v>
+      </c>
+      <c r="O25">
         <v>1.32</v>
       </c>
-      <c r="P20">
+      <c r="P25">
         <v>1.96</v>
       </c>
-      <c r="Q20">
-        <v>1.97</v>
-      </c>
-      <c r="R20">
+      <c r="Q25">
+        <v>1.98</v>
+      </c>
+      <c r="R25">
         <v>1.37</v>
       </c>
-      <c r="S20">
+      <c r="S25">
         <v>3.5</v>
       </c>
-      <c r="T20">
+      <c r="T25">
         <v>1.86</v>
       </c>
-      <c r="U20">
+      <c r="U25">
         <v>2.1</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
         <v>15</v>
       </c>
-      <c r="Y20">
+      <c r="Y25">
         <v>17</v>
       </c>
-      <c r="Z20">
+      <c r="Z25">
         <v>42</v>
       </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
         <v>9</v>
       </c>
-      <c r="AC20">
+      <c r="AC25">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD20">
+      <c r="AD25">
         <v>19</v>
       </c>
-      <c r="AE20">
-        <v>610</v>
-      </c>
-      <c r="AF20">
+      <c r="AE25">
+        <v>600</v>
+      </c>
+      <c r="AF25">
         <v>11.5</v>
       </c>
-      <c r="AG20">
+      <c r="AG25">
         <v>10.5</v>
       </c>
-      <c r="AH20">
+      <c r="AH25">
         <v>19.5</v>
       </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
         <v>21</v>
       </c>
-      <c r="AK20">
+      <c r="AK25">
         <v>20</v>
       </c>
-      <c r="AL20">
+      <c r="AL25">
         <v>38</v>
       </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
         <v>13</v>
       </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
         <v>13</v>
       </c>
-      <c r="AQ20">
+      <c r="AQ25">
         <v>15</v>
       </c>
-      <c r="AR20">
+      <c r="AR25">
         <v>30</v>
       </c>
-      <c r="AS20">
+      <c r="AS25">
         <v>38</v>
       </c>
-      <c r="AT20">
+      <c r="AT25">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU20">
+      <c r="AU25">
         <v>7.4</v>
       </c>
-      <c r="AV20">
+      <c r="AV25">
         <v>16.5</v>
       </c>
-      <c r="AW20">
+      <c r="AW25">
         <v>29</v>
       </c>
-      <c r="AX20">
+      <c r="AX25">
         <v>10</v>
       </c>
-      <c r="AY20">
+      <c r="AY25">
         <v>9.4</v>
       </c>
-      <c r="AZ20">
+      <c r="AZ25">
         <v>17</v>
       </c>
-      <c r="BA20">
+      <c r="BA25">
         <v>32</v>
       </c>
-      <c r="BB20">
+      <c r="BB25">
         <v>18.5</v>
       </c>
-      <c r="BC20">
+      <c r="BC25">
         <v>17</v>
       </c>
-      <c r="BD20">
+      <c r="BD25">
         <v>23</v>
       </c>
-      <c r="BE20">
+      <c r="BE25">
         <v>38</v>
       </c>
-      <c r="BF20">
+      <c r="BF25">
         <v>11.5</v>
       </c>
-      <c r="BG20">
+      <c r="BG25">
         <v>32</v>
       </c>
-      <c r="BH20">
+      <c r="BH25">
         <v>3.4</v>
       </c>
-      <c r="BI20">
+      <c r="BI25">
         <v>3.1</v>
       </c>
-      <c r="BJ20">
+      <c r="BJ25">
         <v>12</v>
       </c>
-      <c r="BK20">
+      <c r="BK25">
         <v>4.1</v>
       </c>
-      <c r="BL20">
+      <c r="BL25">
         <v>150</v>
       </c>
-      <c r="BM20">
+      <c r="BM25">
         <v>5.9</v>
       </c>
-      <c r="BN20">
+      <c r="BN25">
         <v>5.4</v>
       </c>
-      <c r="BO20">
+      <c r="BO25">
         <v>4.2</v>
       </c>
-      <c r="BP20">
+      <c r="BP25">
         <v>16.5</v>
       </c>
-      <c r="BQ20">
+      <c r="BQ25">
         <v>4.6</v>
       </c>
-      <c r="BR20">
+      <c r="BR25">
         <v>34</v>
       </c>
-      <c r="BS20">
+      <c r="BS25">
         <v>5.2</v>
       </c>
-      <c r="BT20">
+      <c r="BT25">
         <v>9.4</v>
       </c>
-      <c r="BU20">
+      <c r="BU25">
         <v>7</v>
       </c>
-      <c r="BV20">
+      <c r="BV25">
         <v>46</v>
       </c>
-      <c r="BW20">
+      <c r="BW25">
         <v>5.4</v>
       </c>
-      <c r="BX20">
+      <c r="BX25">
         <v>60</v>
       </c>
-      <c r="BY20">
+      <c r="BY25">
         <v>5.6</v>
       </c>
-      <c r="BZ20">
+      <c r="BZ25">
         <v>29</v>
       </c>
-      <c r="CA20">
+      <c r="CA25">
         <v>5.1</v>
       </c>
-      <c r="CB20" t="s">
-        <v>147</v>
+      <c r="CB25" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -1057,7 +1057,7 @@
     <t>Comerciantes Unidos</t>
   </si>
   <si>
-    <t>2026-09-16 18:32:21</t>
+    <t>2026-09-16 20:49:16</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1651,7 @@
         <v>251</v>
       </c>
       <c r="F2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
         <v>1.13</v>
@@ -1690,7 +1690,7 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1896,7 +1896,7 @@
         <v>3.8</v>
       </c>
       <c r="G3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
         <v>2.12</v>
@@ -1935,7 +1935,7 @@
         <v>4.4</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
         <v>1.9</v>
@@ -2159,13 +2159,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
         <v>1.02</v>
       </c>
       <c r="P4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q4">
         <v>1.55</v>
@@ -2174,7 +2174,7 @@
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -2183,10 +2183,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2416,7 +2416,7 @@
         <v>1.09</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2634,7 +2634,7 @@
         <v>3.75</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2646,7 +2646,7 @@
         <v>2.2</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
         <v>2.02</v>
@@ -2781,7 +2781,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
         <v>1.01</v>
@@ -2885,22 +2885,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.02</v>
       </c>
       <c r="P7">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Q7">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
         <v>1.08</v>
       </c>
       <c r="S7">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -3106,19 +3106,19 @@
         <v>4.3</v>
       </c>
       <c r="G8">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
         <v>1.79</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>1.36</v>
@@ -3136,7 +3136,7 @@
         <v>1.94</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
         <v>1.36</v>
@@ -3154,7 +3154,7 @@
         <v>2</v>
       </c>
       <c r="W8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X8">
         <v>18.5</v>
@@ -3587,19 +3587,19 @@
         <v>259</v>
       </c>
       <c r="F10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G10">
         <v>600</v>
       </c>
       <c r="H10">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3638,7 +3638,7 @@
         <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3856,7 +3856,7 @@
         <v>2.86</v>
       </c>
       <c r="O11">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="P11">
         <v>1.7</v>
@@ -4077,40 +4077,40 @@
         <v>2.22</v>
       </c>
       <c r="H12">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
         <v>4.8</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12">
         <v>4.2</v>
       </c>
       <c r="L12">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
         <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R12">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
         <v>1.81</v>
@@ -4337,13 +4337,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
         <v>1.02</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q13">
         <v>1.47</v>
@@ -4352,7 +4352,7 @@
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4361,10 +4361,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4555,19 +4555,19 @@
         <v>263</v>
       </c>
       <c r="F14">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>3.55</v>
       </c>
       <c r="I14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
         <v>4.7</v>
@@ -4582,7 +4582,7 @@
         <v>8.6</v>
       </c>
       <c r="O14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P14">
         <v>3.55</v>
@@ -4591,7 +4591,7 @@
         <v>1.36</v>
       </c>
       <c r="R14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S14">
         <v>1.86</v>
@@ -4600,19 +4600,19 @@
         <v>1.4</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z14">
         <v>42</v>
@@ -4621,13 +4621,13 @@
         <v>80</v>
       </c>
       <c r="AB14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE14">
         <v>34</v>
@@ -4636,10 +4636,10 @@
         <v>21</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI14">
         <v>34</v>
@@ -4648,7 +4648,7 @@
         <v>29</v>
       </c>
       <c r="AK14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL14">
         <v>22</v>
@@ -4663,16 +4663,16 @@
         <v>16.5</v>
       </c>
       <c r="AP14">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="AQ14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AR14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AS14">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AT14">
         <v>19</v>
@@ -4684,7 +4684,7 @@
         <v>16</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4696,10 +4696,10 @@
         <v>12</v>
       </c>
       <c r="BA14">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BB14">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BC14">
         <v>14.5</v>
@@ -4708,10 +4708,10 @@
         <v>18.5</v>
       </c>
       <c r="BE14">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BF14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG14">
         <v>14</v>
@@ -4803,10 +4803,10 @@
         <v>2.5</v>
       </c>
       <c r="H15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J15">
         <v>3.35</v>
@@ -4836,7 +4836,7 @@
         <v>1.28</v>
       </c>
       <c r="S15">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
         <v>1.72</v>
@@ -4845,7 +4845,7 @@
         <v>1.98</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.66</v>
@@ -5039,7 +5039,7 @@
         <v>265</v>
       </c>
       <c r="F16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G16">
         <v>600</v>
@@ -5305,22 +5305,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O17">
         <v>1.02</v>
       </c>
       <c r="P17">
+        <v>1.32</v>
+      </c>
+      <c r="Q17">
         <v>1.26</v>
-      </c>
-      <c r="Q17">
-        <v>1.25</v>
       </c>
       <c r="R17">
         <v>1.09</v>
       </c>
       <c r="S17">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -5526,7 +5526,7 @@
         <v>1.37</v>
       </c>
       <c r="G18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H18">
         <v>8.800000000000001</v>
@@ -5538,7 +5538,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5556,7 +5556,7 @@
         <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
         <v>1.45</v>
@@ -5765,82 +5765,82 @@
         <v>268</v>
       </c>
       <c r="F19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G19">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L19">
         <v>1.33</v>
       </c>
       <c r="M19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N19">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="O19">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P19">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q19">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="R19">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S19">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T19">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="U19">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V19">
         <v>1.25</v>
       </c>
       <c r="W19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X19">
         <v>15</v>
       </c>
       <c r="Y19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
         <v>38</v>
       </c>
       <c r="AA19">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB19">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>8.4</v>
       </c>
       <c r="AD19">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF19">
         <v>13</v>
@@ -5849,82 +5849,82 @@
         <v>10.5</v>
       </c>
       <c r="AH19">
+        <v>19</v>
+      </c>
+      <c r="AI19">
+        <v>75</v>
+      </c>
+      <c r="AJ19">
+        <v>23</v>
+      </c>
+      <c r="AK19">
         <v>20</v>
       </c>
-      <c r="AI19">
+      <c r="AL19">
+        <v>38</v>
+      </c>
+      <c r="AM19">
+        <v>130</v>
+      </c>
+      <c r="AN19">
+        <v>14.5</v>
+      </c>
+      <c r="AO19">
         <v>80</v>
       </c>
-      <c r="AJ19">
-        <v>22</v>
-      </c>
-      <c r="AK19">
-        <v>21</v>
-      </c>
-      <c r="AL19">
-        <v>40</v>
-      </c>
-      <c r="AM19">
-        <v>140</v>
-      </c>
-      <c r="AN19">
-        <v>15</v>
-      </c>
-      <c r="AO19">
-        <v>90</v>
-      </c>
       <c r="AP19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ19">
         <v>13.5</v>
       </c>
       <c r="AR19">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS19">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19">
+        <v>7.8</v>
+      </c>
+      <c r="AU19">
         <v>7.2</v>
       </c>
-      <c r="AU19">
-        <v>7.4</v>
-      </c>
       <c r="AV19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW19">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX19">
         <v>10</v>
       </c>
       <c r="AY19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA19">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB19">
         <v>19</v>
       </c>
       <c r="BC19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD19">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE19">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -6249,7 +6249,7 @@
         <v>270</v>
       </c>
       <c r="F21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G21">
         <v>110</v>
@@ -6258,10 +6258,10 @@
         <v>1.13</v>
       </c>
       <c r="I21">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="J21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K21">
         <v>950</v>
@@ -6494,10 +6494,10 @@
         <v>1.82</v>
       </c>
       <c r="G22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I22">
         <v>5.3</v>
@@ -6521,7 +6521,7 @@
         <v>1.34</v>
       </c>
       <c r="P22">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -6536,13 +6536,13 @@
         <v>1.86</v>
       </c>
       <c r="U22">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V22">
         <v>1.23</v>
       </c>
       <c r="W22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6754,13 +6754,13 @@
         <v>1.3</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P23">
         <v>2.22</v>
@@ -6769,10 +6769,10 @@
         <v>1.73</v>
       </c>
       <c r="R23">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S23">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T23">
         <v>1.77</v>
@@ -6975,22 +6975,22 @@
         <v>273</v>
       </c>
       <c r="F24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G24">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H24">
         <v>4.4</v>
       </c>
       <c r="I24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J24">
         <v>3.95</v>
       </c>
       <c r="K24">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6999,25 +6999,25 @@
         <v>1.02</v>
       </c>
       <c r="N24">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O24">
         <v>1.23</v>
       </c>
       <c r="P24">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
         <v>1.69</v>
       </c>
       <c r="R24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S24">
         <v>2.72</v>
       </c>
       <c r="T24">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U24">
         <v>2.3</v>
@@ -7026,7 +7026,7 @@
         <v>1.27</v>
       </c>
       <c r="W24">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X24">
         <v>21</v>
@@ -7044,7 +7044,7 @@
         <v>11</v>
       </c>
       <c r="AC24">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24">
         <v>19</v>
@@ -7068,7 +7068,7 @@
         <v>21</v>
       </c>
       <c r="AK24">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL24">
         <v>34</v>
@@ -7077,7 +7077,7 @@
         <v>90</v>
       </c>
       <c r="AN24">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24">
         <v>55</v>
@@ -7113,7 +7113,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA24">
         <v>1.01</v>
@@ -7217,19 +7217,19 @@
         <v>274</v>
       </c>
       <c r="F25">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>1.64</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="I25">
         <v>1000</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="K25">
         <v>870</v>
@@ -7241,22 +7241,22 @@
         <v>1.01</v>
       </c>
       <c r="N25">
+        <v>3.85</v>
+      </c>
+      <c r="O25">
         <v>1.08</v>
       </c>
-      <c r="O25">
-        <v>1.1</v>
-      </c>
       <c r="P25">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="Q25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R25">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -7268,7 +7268,7 @@
         <v>1.02</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7495,10 +7495,10 @@
         <v>1.35</v>
       </c>
       <c r="R26">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S26">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7749,7 +7749,7 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W27">
         <v>1.89</v>
@@ -7958,19 +7958,19 @@
         <v>3.2</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N28">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P28">
         <v>1.76</v>
@@ -8684,7 +8684,7 @@
         <v>4.1</v>
       </c>
       <c r="K31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8696,7 +8696,7 @@
         <v>5.5</v>
       </c>
       <c r="O31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P31">
         <v>2.48</v>
@@ -8705,10 +8705,10 @@
         <v>1.56</v>
       </c>
       <c r="R31">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S31">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="T31">
         <v>1.59</v>
@@ -8720,7 +8720,7 @@
         <v>2</v>
       </c>
       <c r="W31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X31">
         <v>29</v>
@@ -8774,7 +8774,7 @@
         <v>32</v>
       </c>
       <c r="AO31">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP31">
         <v>19</v>
@@ -8914,10 +8914,10 @@
         <v>4.5</v>
       </c>
       <c r="G32">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H32">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I32">
         <v>1.98</v>
@@ -8935,13 +8935,13 @@
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
         <v>1.36</v>
       </c>
       <c r="P32">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -8953,7 +8953,7 @@
         <v>3.75</v>
       </c>
       <c r="T32">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U32">
         <v>1.86</v>
@@ -9016,7 +9016,7 @@
         <v>1000</v>
       </c>
       <c r="AO32">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AP32">
         <v>8.6</v>
@@ -9109,7 +9109,7 @@
         <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>5.3</v>
+        <v>970</v>
       </c>
       <c r="BU32">
         <v>1.01</v>
@@ -9153,16 +9153,16 @@
         <v>282</v>
       </c>
       <c r="F33">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G33">
         <v>2.06</v>
       </c>
       <c r="H33">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -9177,7 +9177,7 @@
         <v>1.04</v>
       </c>
       <c r="N33">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O33">
         <v>1.22</v>
@@ -9201,7 +9201,7 @@
         <v>2.4</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.94</v>
@@ -9213,7 +9213,7 @@
         <v>22</v>
       </c>
       <c r="Z33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA33">
         <v>85</v>
@@ -9222,7 +9222,7 @@
         <v>14</v>
       </c>
       <c r="AC33">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD33">
         <v>19</v>
@@ -9237,7 +9237,7 @@
         <v>13</v>
       </c>
       <c r="AH33">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI33">
         <v>55</v>
@@ -9246,7 +9246,7 @@
         <v>28</v>
       </c>
       <c r="AK33">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL33">
         <v>34</v>
@@ -9255,7 +9255,7 @@
         <v>90</v>
       </c>
       <c r="AN33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO33">
         <v>38</v>
@@ -9267,10 +9267,10 @@
         <v>15</v>
       </c>
       <c r="AR33">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AS33">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT33">
         <v>10</v>
@@ -9300,19 +9300,19 @@
         <v>18.5</v>
       </c>
       <c r="BC33">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD33">
         <v>21</v>
       </c>
       <c r="BE33">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF33">
         <v>9.199999999999999</v>
       </c>
       <c r="BG33">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9667,10 +9667,10 @@
         <v>1.14</v>
       </c>
       <c r="P35">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R35">
         <v>1.73</v>
@@ -9879,7 +9879,7 @@
         <v>285</v>
       </c>
       <c r="F36">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G36">
         <v>3.1</v>
@@ -9909,7 +9909,7 @@
         <v>1.13</v>
       </c>
       <c r="P36">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q36">
         <v>1.47</v>
@@ -9975,7 +9975,7 @@
         <v>28</v>
       </c>
       <c r="AL36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM36">
         <v>70</v>
@@ -10127,7 +10127,7 @@
         <v>6.4</v>
       </c>
       <c r="H37">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I37">
         <v>2.02</v>
@@ -10157,7 +10157,7 @@
         <v>1.92</v>
       </c>
       <c r="R37">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S37">
         <v>3.2</v>
@@ -10390,7 +10390,7 @@
         <v>3.35</v>
       </c>
       <c r="O38">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P38">
         <v>1.99</v>
@@ -10608,10 +10608,10 @@
         <v>1.25</v>
       </c>
       <c r="G39">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H39">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>990</v>
@@ -10656,7 +10656,7 @@
         <v>1.02</v>
       </c>
       <c r="W39">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10874,7 +10874,7 @@
         <v>5.2</v>
       </c>
       <c r="O40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P40">
         <v>2.44</v>
@@ -11110,31 +11110,31 @@
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N41">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P41">
         <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R41">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S41">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="T41">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U41">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="V41">
         <v>1.32</v>
@@ -11340,10 +11340,10 @@
         <v>5</v>
       </c>
       <c r="I42">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J42">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K42">
         <v>4.7</v>
@@ -11355,7 +11355,7 @@
         <v>1.02</v>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O42">
         <v>1.16</v>
@@ -11370,13 +11370,13 @@
         <v>1.53</v>
       </c>
       <c r="S42">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="T42">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U42">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V42">
         <v>1.01</v>
@@ -11397,7 +11397,7 @@
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC42">
         <v>970</v>
@@ -11409,7 +11409,7 @@
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG42">
         <v>970</v>
@@ -11433,22 +11433,22 @@
         <v>1000</v>
       </c>
       <c r="AN42">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO42">
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AQ42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AS42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AT42">
         <v>9.6</v>
@@ -11457,13 +11457,13 @@
         <v>7.2</v>
       </c>
       <c r="AV42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AW42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AX42">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY42">
         <v>7.4</v>
@@ -11472,25 +11472,25 @@
         <v>11</v>
       </c>
       <c r="BA42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BB42">
-        <v>11</v>
+        <v>1.43</v>
       </c>
       <c r="BC42">
         <v>10</v>
       </c>
       <c r="BD42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BE42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF42">
         <v>5.2</v>
       </c>
       <c r="BG42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BH42">
         <v>970</v>
@@ -11576,7 +11576,7 @@
         <v>2.44</v>
       </c>
       <c r="G43">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H43">
         <v>3.05</v>
@@ -11585,10 +11585,10 @@
         <v>3.25</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K43">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11597,19 +11597,19 @@
         <v>1.07</v>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O43">
         <v>1.32</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q43">
         <v>1.94</v>
       </c>
       <c r="R43">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
         <v>3.4</v>
@@ -11621,10 +11621,10 @@
         <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X43">
         <v>17.5</v>
@@ -11693,7 +11693,7 @@
         <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU43">
         <v>7</v>
@@ -11824,7 +11824,7 @@
         <v>2.34</v>
       </c>
       <c r="I44">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J44">
         <v>3.1</v>
@@ -11842,7 +11842,7 @@
         <v>3.3</v>
       </c>
       <c r="O44">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P44">
         <v>1.68</v>
@@ -11980,7 +11980,7 @@
         <v>3.9</v>
       </c>
       <c r="BI44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BJ44">
         <v>1000</v>
@@ -12072,7 +12072,7 @@
         <v>3.35</v>
       </c>
       <c r="K45">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L45">
         <v>1.43</v>
@@ -12541,13 +12541,13 @@
         <v>296</v>
       </c>
       <c r="F47">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G47">
         <v>2.74</v>
       </c>
       <c r="H47">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="I47">
         <v>2.76</v>
@@ -12565,28 +12565,28 @@
         <v>1.02</v>
       </c>
       <c r="N47">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O47">
         <v>1.12</v>
       </c>
       <c r="P47">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q47">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R47">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S47">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="T47">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="U47">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="V47">
         <v>1.56</v>
@@ -12643,10 +12643,10 @@
         <v>1000</v>
       </c>
       <c r="AN47">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AO47">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AP47">
         <v>1.01</v>
@@ -13028,7 +13028,7 @@
         <v>2.24</v>
       </c>
       <c r="G49">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H49">
         <v>3.05</v>
@@ -13049,22 +13049,22 @@
         <v>1.02</v>
       </c>
       <c r="N49">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O49">
         <v>1.19</v>
       </c>
       <c r="P49">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q49">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R49">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S49">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T49">
         <v>1.53</v>
@@ -13076,7 +13076,7 @@
         <v>1.41</v>
       </c>
       <c r="W49">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X49">
         <v>1000</v>
@@ -13273,16 +13273,16 @@
         <v>1.43</v>
       </c>
       <c r="H50">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I50">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J50">
         <v>5.6</v>
       </c>
       <c r="K50">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L50">
         <v>1.2</v>
@@ -13297,10 +13297,10 @@
         <v>1.14</v>
       </c>
       <c r="P50">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R50">
         <v>1.8</v>
@@ -13357,7 +13357,7 @@
         <v>85</v>
       </c>
       <c r="AJ50">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK50">
         <v>14.5</v>
@@ -13405,7 +13405,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ50">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA50">
         <v>50</v>
@@ -13524,7 +13524,7 @@
         <v>3.6</v>
       </c>
       <c r="K51">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -13775,7 +13775,7 @@
         <v>1.06</v>
       </c>
       <c r="N52">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O52">
         <v>1.28</v>
@@ -13937,7 +13937,7 @@
         <v>3.8</v>
       </c>
       <c r="BP52">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ52">
         <v>3.05</v>
@@ -13952,10 +13952,10 @@
         <v>8.6</v>
       </c>
       <c r="BU52">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV52">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW52">
         <v>3.15</v>
@@ -13996,7 +13996,7 @@
         <v>2.3</v>
       </c>
       <c r="G53">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H53">
         <v>3.45</v>
@@ -14023,7 +14023,7 @@
         <v>1.39</v>
       </c>
       <c r="P53">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q53">
         <v>2.16</v>
@@ -14032,19 +14032,19 @@
         <v>1.25</v>
       </c>
       <c r="S53">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T53">
         <v>1.82</v>
       </c>
       <c r="U53">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V53">
         <v>1.37</v>
       </c>
       <c r="W53">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X53">
         <v>22</v>
@@ -14238,10 +14238,10 @@
         <v>2.34</v>
       </c>
       <c r="G54">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H54">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I54">
         <v>3.6</v>
@@ -14286,7 +14286,7 @@
         <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X54">
         <v>13.5</v>
@@ -14477,7 +14477,7 @@
         <v>304</v>
       </c>
       <c r="F55">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G55">
         <v>1.94</v>
@@ -14504,19 +14504,19 @@
         <v>4.1</v>
       </c>
       <c r="O55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P55">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q55">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R55">
         <v>1.43</v>
       </c>
       <c r="S55">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T55">
         <v>1.74</v>
@@ -14579,7 +14579,7 @@
         <v>110</v>
       </c>
       <c r="AN55">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AO55">
         <v>65</v>
@@ -14591,10 +14591,10 @@
         <v>15</v>
       </c>
       <c r="AR55">
+        <v>5.6</v>
+      </c>
+      <c r="AS55">
         <v>5.8</v>
-      </c>
-      <c r="AS55">
-        <v>6.2</v>
       </c>
       <c r="AT55">
         <v>8.6</v>
@@ -14606,7 +14606,7 @@
         <v>15.5</v>
       </c>
       <c r="AW55">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX55">
         <v>10.5</v>
@@ -14618,7 +14618,7 @@
         <v>15.5</v>
       </c>
       <c r="BA55">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BB55">
         <v>18</v>
@@ -14627,16 +14627,16 @@
         <v>16</v>
       </c>
       <c r="BD55">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE55">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF55">
         <v>10</v>
       </c>
       <c r="BG55">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14719,7 +14719,7 @@
         <v>305</v>
       </c>
       <c r="F56">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G56">
         <v>2.26</v>
@@ -14734,7 +14734,7 @@
         <v>3.55</v>
       </c>
       <c r="K56">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14752,13 +14752,13 @@
         <v>1.96</v>
       </c>
       <c r="Q56">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R56">
         <v>1.3</v>
       </c>
       <c r="S56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T56">
         <v>1.73</v>
@@ -14985,13 +14985,13 @@
         <v>1.03</v>
       </c>
       <c r="N57">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O57">
         <v>1.25</v>
       </c>
       <c r="P57">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q57">
         <v>1.76</v>
@@ -15000,10 +15000,10 @@
         <v>1.39</v>
       </c>
       <c r="S57">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T57">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U57">
         <v>2.16</v>
@@ -15233,7 +15233,7 @@
         <v>1.15</v>
       </c>
       <c r="P58">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q58">
         <v>1.47</v>
@@ -15245,7 +15245,7 @@
         <v>2.12</v>
       </c>
       <c r="T58">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U58">
         <v>2.66</v>
@@ -15257,7 +15257,7 @@
         <v>2.4</v>
       </c>
       <c r="X58">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y58">
         <v>36</v>
@@ -15293,7 +15293,7 @@
         <v>55</v>
       </c>
       <c r="AJ58">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK58">
         <v>16</v>
@@ -15308,19 +15308,19 @@
         <v>6</v>
       </c>
       <c r="AO58">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP58">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ58">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS58">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT58">
         <v>13</v>
@@ -15332,7 +15332,7 @@
         <v>18.5</v>
       </c>
       <c r="AW58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX58">
         <v>12.5</v>
@@ -15344,7 +15344,7 @@
         <v>14</v>
       </c>
       <c r="BA58">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB58">
         <v>16</v>
@@ -15356,10 +15356,10 @@
         <v>20</v>
       </c>
       <c r="BE58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF58">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG58">
         <v>6</v>
@@ -15481,7 +15481,7 @@
         <v>1.35</v>
       </c>
       <c r="R59">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S59">
         <v>1.83</v>
@@ -16204,13 +16204,13 @@
         <v>3.55</v>
       </c>
       <c r="Q62">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R62">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S62">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="T62">
         <v>1.38</v>
@@ -16413,7 +16413,7 @@
         <v>312</v>
       </c>
       <c r="F63">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G63">
         <v>2.6</v>
@@ -16422,7 +16422,7 @@
         <v>2.62</v>
       </c>
       <c r="I63">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="J63">
         <v>4</v>
@@ -16437,19 +16437,19 @@
         <v>1.02</v>
       </c>
       <c r="N63">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O63">
         <v>1.15</v>
       </c>
       <c r="P63">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="Q63">
         <v>1.48</v>
       </c>
       <c r="R63">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S63">
         <v>2.08</v>
@@ -16458,10 +16458,10 @@
         <v>1.4</v>
       </c>
       <c r="U63">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V63">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W63">
         <v>1.62</v>
@@ -16670,7 +16670,7 @@
         <v>4.3</v>
       </c>
       <c r="K64">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L64">
         <v>1.01</v>
@@ -16685,16 +16685,16 @@
         <v>1.11</v>
       </c>
       <c r="P64">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q64">
         <v>1.48</v>
       </c>
       <c r="R64">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S64">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T64">
         <v>1.5</v>
@@ -16799,7 +16799,7 @@
         <v>1.01</v>
       </c>
       <c r="BB64">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC64">
         <v>1.01</v>
@@ -16912,7 +16912,7 @@
         <v>3.2</v>
       </c>
       <c r="K65">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L65">
         <v>1.01</v>
@@ -16942,7 +16942,7 @@
         <v>1.52</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V65">
         <v>1.47</v>
@@ -17169,13 +17169,13 @@
         <v>1.24</v>
       </c>
       <c r="P66">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q66">
         <v>1.77</v>
       </c>
       <c r="R66">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="S66">
         <v>2.8</v>
@@ -17623,16 +17623,16 @@
         <v>317</v>
       </c>
       <c r="F68">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G68">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="H68">
         <v>2.14</v>
       </c>
       <c r="I68">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J68">
         <v>3.95</v>
@@ -17647,22 +17647,22 @@
         <v>1.02</v>
       </c>
       <c r="N68">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="O68">
         <v>1.14</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q68">
         <v>1.44</v>
       </c>
       <c r="R68">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S68">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T68">
         <v>1.43</v>
@@ -17671,10 +17671,10 @@
         <v>2.66</v>
       </c>
       <c r="V68">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W68">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17692,7 +17692,7 @@
         <v>1000</v>
       </c>
       <c r="AC68">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD68">
         <v>1000</v>
@@ -17889,7 +17889,7 @@
         <v>1.02</v>
       </c>
       <c r="N69">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="O69">
         <v>1.15</v>
@@ -18110,7 +18110,7 @@
         <v>2.44</v>
       </c>
       <c r="G70">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H70">
         <v>2.96</v>
@@ -18128,7 +18128,7 @@
         <v>1.35</v>
       </c>
       <c r="M70">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N70">
         <v>3.75</v>
@@ -18146,13 +18146,13 @@
         <v>1.39</v>
       </c>
       <c r="S70">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T70">
         <v>1.62</v>
       </c>
       <c r="U70">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V70">
         <v>1.47</v>
@@ -18227,13 +18227,13 @@
         <v>4.6</v>
       </c>
       <c r="AT70">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU70">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AV70">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AW70">
         <v>4.4</v>
@@ -18272,61 +18272,61 @@
         <v>970</v>
       </c>
       <c r="BI70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BJ70">
         <v>1000</v>
       </c>
       <c r="BK70">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BL70">
         <v>1000</v>
       </c>
       <c r="BM70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BN70">
         <v>970</v>
       </c>
       <c r="BO70">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP70">
         <v>1000</v>
       </c>
       <c r="BQ70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BR70">
         <v>1000</v>
       </c>
       <c r="BS70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT70">
         <v>1000</v>
       </c>
       <c r="BU70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BV70">
         <v>1000</v>
       </c>
       <c r="BW70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BX70">
         <v>1000</v>
       </c>
       <c r="BY70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BZ70">
         <v>1000</v>
       </c>
       <c r="CA70">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="CB70" t="s">
         <v>347</v>
@@ -18594,31 +18594,31 @@
         <v>1.08</v>
       </c>
       <c r="G72">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H72">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I72">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J72">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="K72">
+        <v>21</v>
+      </c>
+      <c r="L72">
+        <v>1.11</v>
+      </c>
+      <c r="M72">
+        <v>1.01</v>
+      </c>
+      <c r="N72">
         <v>19.5</v>
       </c>
-      <c r="L72">
-        <v>1.12</v>
-      </c>
-      <c r="M72">
-        <v>1.01</v>
-      </c>
-      <c r="N72">
-        <v>18.5</v>
-      </c>
       <c r="O72">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P72">
         <v>6.8</v>
@@ -18627,22 +18627,22 @@
         <v>1.15</v>
       </c>
       <c r="R72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S72">
         <v>1.42</v>
       </c>
       <c r="T72">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U72">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V72">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W72">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="X72">
         <v>140</v>
@@ -18687,13 +18687,13 @@
         <v>15.5</v>
       </c>
       <c r="AL72">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM72">
         <v>1000</v>
       </c>
       <c r="AN72">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AO72">
         <v>340</v>
@@ -18702,22 +18702,22 @@
         <v>95</v>
       </c>
       <c r="AQ72">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR72">
         <v>100</v>
       </c>
       <c r="AS72">
+        <v>60</v>
+      </c>
+      <c r="AT72">
         <v>21</v>
       </c>
-      <c r="AT72">
-        <v>26</v>
-      </c>
       <c r="AU72">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV72">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW72">
         <v>100</v>
@@ -18726,7 +18726,7 @@
         <v>14</v>
       </c>
       <c r="AY72">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ72">
         <v>32</v>
@@ -18735,10 +18735,10 @@
         <v>48</v>
       </c>
       <c r="BB72">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC72">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD72">
         <v>24</v>
@@ -18747,7 +18747,7 @@
         <v>46</v>
       </c>
       <c r="BF72">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="BG72">
         <v>100</v>
@@ -18756,13 +18756,13 @@
         <v>10.5</v>
       </c>
       <c r="BI72">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ72">
         <v>16.5</v>
       </c>
       <c r="BK72">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BL72">
         <v>120</v>
@@ -18771,13 +18771,13 @@
         <v>21</v>
       </c>
       <c r="BN72">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO72">
         <v>4.5</v>
       </c>
       <c r="BP72">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BQ72">
         <v>5.1</v>
@@ -18792,13 +18792,13 @@
         <v>30</v>
       </c>
       <c r="BU72">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV72">
         <v>170</v>
       </c>
       <c r="BW72">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BX72">
         <v>100</v>
@@ -18833,10 +18833,10 @@
         <v>322</v>
       </c>
       <c r="F73">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G73">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H73">
         <v>3.35</v>
@@ -18875,7 +18875,7 @@
         <v>3.6</v>
       </c>
       <c r="T73">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U73">
         <v>2.1</v>
@@ -18899,7 +18899,7 @@
         <v>65</v>
       </c>
       <c r="AB73">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC73">
         <v>8</v>
@@ -18950,13 +18950,13 @@
         <v>20</v>
       </c>
       <c r="AS73">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT73">
         <v>8.800000000000001</v>
       </c>
       <c r="AU73">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV73">
         <v>13</v>
@@ -18986,7 +18986,7 @@
         <v>34</v>
       </c>
       <c r="BE73">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF73">
         <v>18</v>
@@ -19010,49 +19010,49 @@
         <v>1000</v>
       </c>
       <c r="BM73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="BN73">
         <v>970</v>
       </c>
       <c r="BO73">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP73">
         <v>1000</v>
       </c>
       <c r="BQ73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="BR73">
         <v>1000</v>
       </c>
       <c r="BS73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="BT73">
         <v>1000</v>
       </c>
       <c r="BU73">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="BV73">
         <v>1000</v>
       </c>
       <c r="BW73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="BX73">
         <v>1000</v>
       </c>
       <c r="BY73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="BZ73">
         <v>1000</v>
       </c>
       <c r="CA73">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="CB73" t="s">
         <v>347</v>
@@ -19075,10 +19075,10 @@
         <v>323</v>
       </c>
       <c r="F74">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G74">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H74">
         <v>4.8</v>
@@ -19087,7 +19087,7 @@
         <v>5.6</v>
       </c>
       <c r="J74">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K74">
         <v>4.8</v>
@@ -19099,7 +19099,7 @@
         <v>1.02</v>
       </c>
       <c r="N74">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O74">
         <v>1.18</v>
@@ -19108,7 +19108,7 @@
         <v>2.52</v>
       </c>
       <c r="Q74">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R74">
         <v>1.55</v>
@@ -19117,7 +19117,7 @@
         <v>2.42</v>
       </c>
       <c r="T74">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U74">
         <v>2.28</v>
@@ -19126,7 +19126,7 @@
         <v>1.23</v>
       </c>
       <c r="W74">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X74">
         <v>1000</v>
@@ -19317,13 +19317,13 @@
         <v>324</v>
       </c>
       <c r="F75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G75">
         <v>110</v>
       </c>
       <c r="H75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I75">
         <v>110</v>
@@ -19592,7 +19592,7 @@
         <v>1.08</v>
       </c>
       <c r="Q76">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R76">
         <v>1.07</v>
@@ -19607,10 +19607,10 @@
         <v>1.01</v>
       </c>
       <c r="V76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
         <v>1000</v>
@@ -19813,7 +19813,7 @@
         <v>110</v>
       </c>
       <c r="J77">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K77">
         <v>890</v>
@@ -19831,7 +19831,7 @@
         <v>1.01</v>
       </c>
       <c r="P77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q77">
         <v>1.32</v>
@@ -19852,7 +19852,7 @@
         <v>1.11</v>
       </c>
       <c r="W77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -20043,19 +20043,19 @@
         <v>327</v>
       </c>
       <c r="F78">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G78">
         <v>1000</v>
       </c>
       <c r="H78">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="I78">
         <v>1000</v>
       </c>
       <c r="J78">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K78">
         <v>5</v>
@@ -20067,19 +20067,19 @@
         <v>1.01</v>
       </c>
       <c r="N78">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O78">
         <v>1.01</v>
       </c>
       <c r="P78">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Q78">
         <v>1.33</v>
       </c>
       <c r="R78">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S78">
         <v>1.34</v>
@@ -20091,10 +20091,10 @@
         <v>1.01</v>
       </c>
       <c r="V78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
         <v>1000</v>
@@ -20309,7 +20309,7 @@
         <v>1.01</v>
       </c>
       <c r="N79">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="O79">
         <v>1.22</v>
@@ -20539,7 +20539,7 @@
         <v>2.44</v>
       </c>
       <c r="J80">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K80">
         <v>3.6</v>
@@ -20551,7 +20551,7 @@
         <v>1.06</v>
       </c>
       <c r="N80">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O80">
         <v>1.29</v>
@@ -20560,13 +20560,13 @@
         <v>2.1</v>
       </c>
       <c r="Q80">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R80">
         <v>1.43</v>
       </c>
       <c r="S80">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T80">
         <v>1.7</v>
@@ -20581,7 +20581,7 @@
         <v>1.43</v>
       </c>
       <c r="X80">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y80">
         <v>11.5</v>
@@ -20614,7 +20614,7 @@
         <v>16</v>
       </c>
       <c r="AI80">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ80">
         <v>55</v>
@@ -20644,7 +20644,7 @@
         <v>15</v>
       </c>
       <c r="AS80">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT80">
         <v>12.5</v>
@@ -20692,7 +20692,7 @@
         <v>3.5</v>
       </c>
       <c r="BI80">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ80">
         <v>9.199999999999999</v>
@@ -20772,16 +20772,16 @@
         <v>2.36</v>
       </c>
       <c r="G81">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H81">
         <v>2.94</v>
       </c>
       <c r="I81">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J81">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K81">
         <v>4</v>
@@ -20790,7 +20790,7 @@
         <v>1.28</v>
       </c>
       <c r="M81">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N81">
         <v>4.4</v>
@@ -20808,10 +20808,10 @@
         <v>1.47</v>
       </c>
       <c r="S81">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T81">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U81">
         <v>2.32</v>
@@ -20871,7 +20871,7 @@
         <v>1000</v>
       </c>
       <c r="AN81">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO81">
         <v>1000</v>
@@ -21026,7 +21026,7 @@
         <v>3.45</v>
       </c>
       <c r="K82">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L82">
         <v>1.01</v>
@@ -21038,13 +21038,13 @@
         <v>4.1</v>
       </c>
       <c r="O82">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P82">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q82">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="R82">
         <v>1.41</v>
@@ -21053,7 +21053,7 @@
         <v>2.78</v>
       </c>
       <c r="T82">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U82">
         <v>2.16</v>
@@ -21068,10 +21068,10 @@
         <v>1000</v>
       </c>
       <c r="Y82">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z82">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA82">
         <v>1000</v>
@@ -21104,7 +21104,7 @@
         <v>1000</v>
       </c>
       <c r="AK82">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL82">
         <v>1000</v>
@@ -21143,7 +21143,7 @@
         <v>1.01</v>
       </c>
       <c r="AX82">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY82">
         <v>8</v>
@@ -21504,7 +21504,7 @@
         <v>3.15</v>
       </c>
       <c r="I84">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J84">
         <v>3.4</v>
@@ -21522,25 +21522,25 @@
         <v>3.5</v>
       </c>
       <c r="O84">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P84">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q84">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R84">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S84">
         <v>3.2</v>
       </c>
       <c r="T84">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U84">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V84">
         <v>1.37</v>
@@ -22230,7 +22230,7 @@
         <v>3.6</v>
       </c>
       <c r="I87">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J87">
         <v>3.9</v>
@@ -22260,7 +22260,7 @@
         <v>1.6</v>
       </c>
       <c r="S87">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T87">
         <v>1.54</v>
@@ -22284,7 +22284,7 @@
         <v>30</v>
       </c>
       <c r="AA87">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB87">
         <v>14.5</v>
@@ -22368,7 +22368,7 @@
         <v>24</v>
       </c>
       <c r="BC87">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD87">
         <v>11.5</v>
@@ -22466,10 +22466,10 @@
         <v>2.1</v>
       </c>
       <c r="G88">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H88">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I88">
         <v>3.7</v>
@@ -22496,25 +22496,25 @@
         <v>2.24</v>
       </c>
       <c r="Q88">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R88">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S88">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T88">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U88">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V88">
         <v>1.37</v>
       </c>
       <c r="W88">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X88">
         <v>1000</v>
@@ -22532,7 +22532,7 @@
         <v>1000</v>
       </c>
       <c r="AC88">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD88">
         <v>1000</v>
@@ -22544,7 +22544,7 @@
         <v>1000</v>
       </c>
       <c r="AG88">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH88">
         <v>1000</v>
@@ -22571,58 +22571,58 @@
         <v>1000</v>
       </c>
       <c r="AP88">
-        <v>12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ88">
-        <v>10.5</v>
+        <v>1.06</v>
       </c>
       <c r="AR88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AS88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AT88">
-        <v>8.800000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="AU88">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV88">
-        <v>9.6</v>
+        <v>1.06</v>
       </c>
       <c r="AW88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AX88">
-        <v>9.6</v>
+        <v>1.06</v>
       </c>
       <c r="AY88">
-        <v>7.8</v>
+        <v>1.06</v>
       </c>
       <c r="AZ88">
-        <v>10</v>
+        <v>1.06</v>
       </c>
       <c r="BA88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BB88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BC88">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="BD88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF88">
-        <v>8.4</v>
+        <v>1.06</v>
       </c>
       <c r="BG88">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BH88">
         <v>1000</v>
@@ -22705,16 +22705,16 @@
         <v>338</v>
       </c>
       <c r="F89">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G89">
         <v>2.02</v>
       </c>
       <c r="H89">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I89">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J89">
         <v>3.55</v>
@@ -22729,7 +22729,7 @@
         <v>1.08</v>
       </c>
       <c r="N89">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O89">
         <v>1.38</v>
@@ -22747,7 +22747,7 @@
         <v>3.95</v>
       </c>
       <c r="T89">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="U89">
         <v>1.96</v>
@@ -22774,13 +22774,13 @@
         <v>8.4</v>
       </c>
       <c r="AC89">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD89">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE89">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF89">
         <v>12</v>
@@ -22810,7 +22810,7 @@
         <v>16.5</v>
       </c>
       <c r="AO89">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP89">
         <v>11</v>
@@ -22822,10 +22822,10 @@
         <v>8</v>
       </c>
       <c r="AS89">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT89">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU89">
         <v>7.2</v>
@@ -22840,13 +22840,13 @@
         <v>10</v>
       </c>
       <c r="AY89">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ89">
         <v>17.5</v>
       </c>
       <c r="BA89">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB89">
         <v>7.2</v>
@@ -22858,25 +22858,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE89">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF89">
         <v>14.5</v>
       </c>
       <c r="BG89">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH89">
-        <v>3.5</v>
+        <v>970</v>
       </c>
       <c r="BI89">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ89">
         <v>1000</v>
       </c>
       <c r="BK89">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL89">
         <v>1000</v>
@@ -22885,10 +22885,10 @@
         <v>1.01</v>
       </c>
       <c r="BN89">
-        <v>5.4</v>
+        <v>970</v>
       </c>
       <c r="BO89">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP89">
         <v>1000</v>
@@ -22906,7 +22906,7 @@
         <v>1000</v>
       </c>
       <c r="BU89">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV89">
         <v>1000</v>
@@ -23431,10 +23431,10 @@
         <v>341</v>
       </c>
       <c r="F92">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G92">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H92">
         <v>7.6</v>
@@ -23443,10 +23443,10 @@
         <v>8.4</v>
       </c>
       <c r="J92">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K92">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L92">
         <v>1.29</v>
@@ -23458,7 +23458,7 @@
         <v>4.8</v>
       </c>
       <c r="O92">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P92">
         <v>2.36</v>
@@ -23467,22 +23467,22 @@
         <v>1.63</v>
       </c>
       <c r="R92">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S92">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T92">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U92">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="V92">
         <v>1.13</v>
       </c>
       <c r="W92">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X92">
         <v>28</v>
@@ -23491,7 +23491,7 @@
         <v>27</v>
       </c>
       <c r="Z92">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA92">
         <v>310</v>
@@ -23500,25 +23500,25 @@
         <v>10</v>
       </c>
       <c r="AC92">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD92">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE92">
         <v>130</v>
       </c>
       <c r="AF92">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG92">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH92">
         <v>28</v>
       </c>
       <c r="AI92">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ92">
         <v>13</v>
@@ -23536,43 +23536,43 @@
         <v>6.4</v>
       </c>
       <c r="AO92">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP92">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ92">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR92">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS92">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT92">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU92">
         <v>10.5</v>
       </c>
       <c r="AV92">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AW92">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX92">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY92">
         <v>9.4</v>
       </c>
       <c r="AZ92">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA92">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB92">
         <v>11</v>
@@ -23581,16 +23581,16 @@
         <v>13</v>
       </c>
       <c r="BD92">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE92">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF92">
         <v>5.2</v>
       </c>
       <c r="BG92">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH92">
         <v>970</v>
@@ -23673,16 +23673,16 @@
         <v>342</v>
       </c>
       <c r="F93">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G93">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H93">
+        <v>4.7</v>
+      </c>
+      <c r="I93">
         <v>4.8</v>
-      </c>
-      <c r="I93">
-        <v>4.9</v>
       </c>
       <c r="J93">
         <v>3.8</v>
@@ -23691,13 +23691,13 @@
         <v>3.85</v>
       </c>
       <c r="L93">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M93">
         <v>1.07</v>
       </c>
       <c r="N93">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O93">
         <v>1.3</v>
@@ -23706,13 +23706,13 @@
         <v>2.1</v>
       </c>
       <c r="Q93">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R93">
         <v>1.41</v>
       </c>
       <c r="S93">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T93">
         <v>1.79</v>
@@ -23721,7 +23721,7 @@
         <v>2.22</v>
       </c>
       <c r="V93">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W93">
         <v>2.12</v>
@@ -23766,7 +23766,7 @@
         <v>21</v>
       </c>
       <c r="AK93">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL93">
         <v>34</v>
@@ -23790,13 +23790,13 @@
         <v>32</v>
       </c>
       <c r="AS93">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT93">
         <v>9.199999999999999</v>
       </c>
       <c r="AU93">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV93">
         <v>16</v>
@@ -23832,7 +23832,7 @@
         <v>10.5</v>
       </c>
       <c r="BG93">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BH93">
         <v>3.55</v>
@@ -23844,7 +23844,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK93">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL93">
         <v>140</v>
@@ -23868,7 +23868,7 @@
         <v>32</v>
       </c>
       <c r="BS93">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT93">
         <v>8</v>
@@ -23915,22 +23915,22 @@
         <v>343</v>
       </c>
       <c r="F94">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G94">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H94">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I94">
         <v>4.5</v>
       </c>
       <c r="J94">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K94">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L94">
         <v>1.38</v>
@@ -23951,7 +23951,7 @@
         <v>1.89</v>
       </c>
       <c r="R94">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S94">
         <v>3.25</v>
@@ -23966,7 +23966,7 @@
         <v>1.28</v>
       </c>
       <c r="W94">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X94">
         <v>15.5</v>
@@ -23975,7 +23975,7 @@
         <v>17</v>
       </c>
       <c r="Z94">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA94">
         <v>95</v>
@@ -23999,10 +23999,10 @@
         <v>10.5</v>
       </c>
       <c r="AH94">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI94">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ94">
         <v>22</v>
@@ -24017,10 +24017,10 @@
         <v>100</v>
       </c>
       <c r="AN94">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO94">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AP94">
         <v>14</v>
@@ -24029,7 +24029,7 @@
         <v>15</v>
       </c>
       <c r="AR94">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS94">
         <v>36</v>
@@ -24041,7 +24041,7 @@
         <v>7.8</v>
       </c>
       <c r="AV94">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW94">
         <v>42</v>
@@ -24050,7 +24050,7 @@
         <v>11</v>
       </c>
       <c r="AY94">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ94">
         <v>16.5</v>
@@ -24074,7 +24074,7 @@
         <v>11</v>
       </c>
       <c r="BG94">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BH94">
         <v>970</v>
@@ -24157,13 +24157,13 @@
         <v>344</v>
       </c>
       <c r="F95">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G95">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H95">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I95">
         <v>2.48</v>
@@ -24184,16 +24184,16 @@
         <v>6.6</v>
       </c>
       <c r="O95">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P95">
         <v>2.88</v>
       </c>
       <c r="Q95">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R95">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S95">
         <v>2.26</v>
@@ -24202,7 +24202,7 @@
         <v>1.46</v>
       </c>
       <c r="U95">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V95">
         <v>1.67</v>
@@ -24244,7 +24244,7 @@
         <v>13</v>
       </c>
       <c r="AI95">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ95">
         <v>46</v>
@@ -24301,7 +24301,7 @@
         <v>23</v>
       </c>
       <c r="BB95">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC95">
         <v>23</v>
@@ -24334,7 +24334,7 @@
         <v>65</v>
       </c>
       <c r="BM95">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BN95">
         <v>6.4</v>
@@ -24343,16 +24343,16 @@
         <v>5.9</v>
       </c>
       <c r="BP95">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ95">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR95">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS95">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT95">
         <v>5.9</v>
@@ -24361,22 +24361,22 @@
         <v>5.4</v>
       </c>
       <c r="BV95">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW95">
+        <v>10.5</v>
+      </c>
+      <c r="BX95">
+        <v>22</v>
+      </c>
+      <c r="BY95">
+        <v>11</v>
+      </c>
+      <c r="BZ95">
+        <v>14</v>
+      </c>
+      <c r="CA95">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX95">
-        <v>23</v>
-      </c>
-      <c r="BY95">
-        <v>10.5</v>
-      </c>
-      <c r="BZ95">
-        <v>14.5</v>
-      </c>
-      <c r="CA95">
-        <v>8.199999999999999</v>
       </c>
       <c r="CB95" t="s">
         <v>347</v>
@@ -24408,7 +24408,7 @@
         <v>6.6</v>
       </c>
       <c r="I96">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J96">
         <v>4.6</v>
@@ -24444,7 +24444,7 @@
         <v>1.75</v>
       </c>
       <c r="U96">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V96">
         <v>1.16</v>
@@ -24543,10 +24543,10 @@
         <v>1.01</v>
       </c>
       <c r="BB96">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC96">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD96">
         <v>1.01</v>
@@ -24555,7 +24555,7 @@
         <v>1.01</v>
       </c>
       <c r="BF96">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG96">
         <v>1.01</v>
@@ -24641,19 +24641,19 @@
         <v>346</v>
       </c>
       <c r="F97">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G97">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H97">
         <v>5.1</v>
       </c>
       <c r="I97">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J97">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K97">
         <v>6.4</v>
@@ -24689,10 +24689,10 @@
         <v>1.01</v>
       </c>
       <c r="V97">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W97">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="X97">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -1183,7 +1183,7 @@
     <t>New York Red Bulls</t>
   </si>
   <si>
-    <t>2026-09-17 01:25:34</t>
+    <t>2026-09-17 03:45:33</t>
   </si>
 </sst>
 </file>
@@ -1777,7 +1777,7 @@
         <v>280</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -1807,22 +1807,22 @@
         <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -1831,124 +1831,124 @@
         <v>1.71</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>30</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>27</v>
+      </c>
+      <c r="AO2">
+        <v>65</v>
+      </c>
+      <c r="AP2">
+        <v>9.6</v>
+      </c>
+      <c r="AQ2">
+        <v>10</v>
+      </c>
+      <c r="AR2">
+        <v>21</v>
+      </c>
+      <c r="AS2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>7.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>13.5</v>
+      </c>
+      <c r="AW2">
+        <v>29</v>
+      </c>
+      <c r="AX2">
+        <v>12</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
         <v>17</v>
       </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>55</v>
-      </c>
-      <c r="AK2">
-        <v>48</v>
-      </c>
-      <c r="AL2">
-        <v>85</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>2.3</v>
-      </c>
-      <c r="AQ2">
+      <c r="BA2">
         <v>9</v>
       </c>
-      <c r="AR2">
-        <v>17</v>
-      </c>
-      <c r="AS2">
-        <v>2.64</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
-      </c>
-      <c r="AU2">
-        <v>6</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>2.56</v>
-      </c>
-      <c r="AX2">
-        <v>10.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>2.64</v>
-      </c>
       <c r="BB2">
-        <v>2.52</v>
+        <v>24</v>
       </c>
       <c r="BC2">
         <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>2.56</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>2.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>2.64</v>
+        <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>2.64</v>
+        <v>36</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1957,43 +1957,43 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -2031,7 +2031,7 @@
         <v>29</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="K3">
         <v>14</v>
@@ -2043,28 +2043,28 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q3">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="R3">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="S3">
         <v>1.41</v>
       </c>
       <c r="T3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V3">
         <v>1.04</v>
@@ -2085,7 +2085,7 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AC3">
         <v>38</v>
@@ -2097,7 +2097,7 @@
         <v>300</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>20</v>
@@ -2109,7 +2109,7 @@
         <v>170</v>
       </c>
       <c r="AJ3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AK3">
         <v>18</v>
@@ -2121,64 +2121,64 @@
         <v>140</v>
       </c>
       <c r="AN3">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AO3">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AP3">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
+        <v>7.2</v>
+      </c>
+      <c r="AR3">
+        <v>7.4</v>
+      </c>
+      <c r="AS3">
+        <v>7.6</v>
+      </c>
+      <c r="AT3">
         <v>5.9</v>
       </c>
-      <c r="AR3">
-        <v>1.63</v>
-      </c>
-      <c r="AS3">
-        <v>1.64</v>
-      </c>
-      <c r="AT3">
-        <v>5.1</v>
-      </c>
       <c r="AU3">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>1.61</v>
+        <v>7</v>
       </c>
       <c r="AW3">
-        <v>1.96</v>
+        <v>7.4</v>
       </c>
       <c r="AX3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY3">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ3">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>1.63</v>
+        <v>7.2</v>
       </c>
       <c r="BB3">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BC3">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="BG3">
-        <v>1.63</v>
+        <v>7.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2264,13 +2264,13 @@
         <v>3.8</v>
       </c>
       <c r="G4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H4">
         <v>2.14</v>
       </c>
       <c r="I4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J4">
         <v>3.3</v>
@@ -2285,7 +2285,7 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O4">
         <v>1.43</v>
@@ -2309,7 +2309,7 @@
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W4">
         <v>1.32</v>
@@ -2321,13 +2321,13 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA4">
         <v>36</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -2336,13 +2336,13 @@
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF4">
         <v>34</v>
       </c>
       <c r="AG4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH4">
         <v>25</v>
@@ -2366,7 +2366,7 @@
         <v>90</v>
       </c>
       <c r="AO4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP4">
         <v>7.8</v>
@@ -2378,7 +2378,7 @@
         <v>11</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
@@ -2387,13 +2387,13 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY4">
         <v>12</v>
@@ -2402,22 +2402,22 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC4">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BD4">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG4">
         <v>20</v>
@@ -2503,19 +2503,19 @@
         <v>283</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
         <v>110</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
         <v>110</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2745,19 +2745,19 @@
         <v>284</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
         <v>920</v>
@@ -2793,10 +2793,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2996,13 +2996,13 @@
         <v>4.5</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -3011,7 +3011,7 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
         <v>1.26</v>
@@ -3029,7 +3029,7 @@
         <v>2.78</v>
       </c>
       <c r="T7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
         <v>2.02</v>
@@ -3229,19 +3229,19 @@
         <v>286</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>900</v>
@@ -3277,10 +3277,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3713,19 +3713,19 @@
         <v>288</v>
       </c>
       <c r="F10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
         <v>600</v>
       </c>
       <c r="H10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3761,10 +3761,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3955,7 +3955,7 @@
         <v>289</v>
       </c>
       <c r="F11">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G11">
         <v>2.08</v>
@@ -3964,13 +3964,13 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3979,34 +3979,34 @@
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P11">
         <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
+        <v>1.22</v>
+      </c>
+      <c r="S11">
+        <v>2.5</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
         <v>1.23</v>
       </c>
-      <c r="S11">
-        <v>1.01</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.22</v>
-      </c>
       <c r="W11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -4200,10 +4200,10 @@
         <v>1.27</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H12">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="I12">
         <v>870</v>
@@ -4221,7 +4221,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O12">
         <v>1.01</v>
@@ -4233,7 +4233,7 @@
         <v>1.27</v>
       </c>
       <c r="R12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S12">
         <v>1.28</v>
@@ -4245,10 +4245,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4448,7 +4448,7 @@
         <v>3.75</v>
       </c>
       <c r="I13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J13">
         <v>3.35</v>
@@ -4469,7 +4469,7 @@
         <v>1.35</v>
       </c>
       <c r="P13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -4478,7 +4478,7 @@
         <v>1.31</v>
       </c>
       <c r="S13">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T13">
         <v>1.82</v>
@@ -4681,19 +4681,19 @@
         <v>292</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G14">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I14">
         <v>110</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>1000</v>
@@ -4729,10 +4729,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4926,19 +4926,19 @@
         <v>1.93</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J15">
         <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>1.16</v>
@@ -4956,25 +4956,25 @@
         <v>3.55</v>
       </c>
       <c r="Q15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="T15">
         <v>1.4</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X15">
         <v>44</v>
@@ -4986,7 +4986,7 @@
         <v>42</v>
       </c>
       <c r="AA15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
         <v>24</v>
@@ -5022,13 +5022,13 @@
         <v>22</v>
       </c>
       <c r="AM15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AN15">
         <v>6.2</v>
       </c>
       <c r="AO15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP15">
         <v>26</v>
@@ -5177,7 +5177,7 @@
         <v>870</v>
       </c>
       <c r="J16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -5198,13 +5198,13 @@
         <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>1.31</v>
       </c>
       <c r="R16">
         <v>1.08</v>
       </c>
       <c r="S16">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -5213,10 +5213,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5431,7 +5431,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
         <v>1.32</v>
@@ -5455,7 +5455,7 @@
         <v>2</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
         <v>1.66</v>
@@ -5661,7 +5661,7 @@
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5676,13 +5676,13 @@
         <v>1.32</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18">
         <v>1.32</v>
       </c>
       <c r="Q18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R18">
         <v>1.09</v>
@@ -5697,10 +5697,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5918,7 +5918,7 @@
         <v>4.4</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P19">
         <v>2.18</v>
@@ -5936,7 +5936,7 @@
         <v>2.08</v>
       </c>
       <c r="U19">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V19">
         <v>1.1</v>
@@ -5981,7 +5981,7 @@
         <v>150</v>
       </c>
       <c r="AJ19">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AK19">
         <v>16</v>
@@ -6136,13 +6136,13 @@
         <v>1.86</v>
       </c>
       <c r="G20">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H20">
         <v>4.5</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>3.55</v>
@@ -6157,28 +6157,28 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O20">
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q20">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
         <v>1.25</v>
@@ -6217,7 +6217,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI20">
         <v>75</v>
@@ -6235,7 +6235,7 @@
         <v>120</v>
       </c>
       <c r="AN20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO20">
         <v>80</v>
@@ -6247,10 +6247,10 @@
         <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS20">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT20">
         <v>7.8</v>
@@ -6262,19 +6262,19 @@
         <v>16</v>
       </c>
       <c r="AW20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20">
         <v>10</v>
       </c>
       <c r="AY20">
+        <v>9</v>
+      </c>
+      <c r="AZ20">
+        <v>16</v>
+      </c>
+      <c r="BA20">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20">
-        <v>6.4</v>
-      </c>
-      <c r="BA20">
-        <v>8.4</v>
       </c>
       <c r="BB20">
         <v>19</v>
@@ -6283,16 +6283,16 @@
         <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20">
         <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6375,22 +6375,22 @@
         <v>299</v>
       </c>
       <c r="F21">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="H21">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="I21">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="J21">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="K21">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="L21">
         <v>1.31</v>
@@ -6399,22 +6399,22 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
         <v>1.83</v>
       </c>
       <c r="Q21">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R21">
         <v>1.27</v>
       </c>
       <c r="S21">
-        <v>1.34</v>
+        <v>2.78</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6423,10 +6423,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6629,7 +6629,7 @@
         <v>110</v>
       </c>
       <c r="J22">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K22">
         <v>950</v>
@@ -6644,10 +6644,10 @@
         <v>1.13</v>
       </c>
       <c r="O22">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q22">
         <v>1.37</v>
@@ -6656,7 +6656,7 @@
         <v>1.08</v>
       </c>
       <c r="S22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6665,10 +6665,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6859,10 +6859,10 @@
         <v>301</v>
       </c>
       <c r="F23">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G23">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H23">
         <v>4.4</v>
@@ -6883,28 +6883,28 @@
         <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P23">
         <v>2.3</v>
       </c>
       <c r="Q23">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S23">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
         <v>1.27</v>
@@ -6913,16 +6913,16 @@
         <v>2.12</v>
       </c>
       <c r="X23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y23">
         <v>20</v>
       </c>
       <c r="Z23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
         <v>11</v>
@@ -6934,7 +6934,7 @@
         <v>18.5</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF23">
         <v>12.5</v>
@@ -6949,7 +6949,7 @@
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23">
         <v>18</v>
@@ -6958,7 +6958,7 @@
         <v>30</v>
       </c>
       <c r="AM23">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
         <v>9.4</v>
@@ -6967,7 +6967,7 @@
         <v>55</v>
       </c>
       <c r="AP23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ23">
         <v>17.5</v>
@@ -6976,7 +6976,7 @@
         <v>23</v>
       </c>
       <c r="AS23">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT23">
         <v>10.5</v>
@@ -6988,19 +6988,19 @@
         <v>16</v>
       </c>
       <c r="AW23">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AX23">
         <v>11</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
         <v>15</v>
       </c>
       <c r="BA23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB23">
         <v>17</v>
@@ -7012,7 +7012,7 @@
         <v>23</v>
       </c>
       <c r="BE23">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF23">
         <v>8.4</v>
@@ -7113,7 +7113,7 @@
         <v>4.5</v>
       </c>
       <c r="J24">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="K24">
         <v>4.2</v>
@@ -7128,7 +7128,7 @@
         <v>2.58</v>
       </c>
       <c r="O24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P24">
         <v>1.57</v>
@@ -7349,7 +7349,7 @@
         <v>1.64</v>
       </c>
       <c r="H25">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I25">
         <v>6.4</v>
@@ -7358,43 +7358,43 @@
         <v>4.4</v>
       </c>
       <c r="K25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L25">
         <v>1.3</v>
       </c>
       <c r="M25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P25">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q25">
         <v>1.74</v>
       </c>
       <c r="R25">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T25">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W25">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X25">
         <v>23</v>
@@ -7403,7 +7403,7 @@
         <v>26</v>
       </c>
       <c r="Z25">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA25">
         <v>1000</v>
@@ -7412,10 +7412,10 @@
         <v>9.6</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE25">
         <v>1000</v>
@@ -7427,7 +7427,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI25">
         <v>1000</v>
@@ -7436,16 +7436,16 @@
         <v>16</v>
       </c>
       <c r="AK25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM25">
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO25">
         <v>1000</v>
@@ -7457,7 +7457,7 @@
         <v>17</v>
       </c>
       <c r="AR25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS25">
         <v>44</v>
@@ -7469,19 +7469,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW25">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AX25">
         <v>9.199999999999999</v>
       </c>
       <c r="AY25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ25">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA25">
         <v>42</v>
@@ -7493,13 +7493,13 @@
         <v>14</v>
       </c>
       <c r="BD25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE25">
         <v>40</v>
       </c>
       <c r="BF25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG25">
         <v>36</v>
@@ -7591,13 +7591,13 @@
         <v>110</v>
       </c>
       <c r="H26">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="I26">
         <v>110</v>
       </c>
       <c r="J26">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -7633,10 +7633,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7827,22 +7827,22 @@
         <v>305</v>
       </c>
       <c r="F27">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G27">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I27">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7851,7 +7851,7 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O27">
         <v>1.34</v>
@@ -7869,16 +7869,16 @@
         <v>3.5</v>
       </c>
       <c r="T27">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U27">
         <v>1.9</v>
       </c>
       <c r="V27">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W27">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7905,10 +7905,10 @@
         <v>1000</v>
       </c>
       <c r="AF27">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH27">
         <v>1000</v>
@@ -7929,64 +7929,64 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO27">
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AQ27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AR27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AS27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AT27">
-        <v>1.14</v>
+        <v>6.2</v>
       </c>
       <c r="AU27">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AV27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AW27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AX27">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AY27">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AZ27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BA27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BB27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BC27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BD27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BE27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BF27">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="BG27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -8072,16 +8072,16 @@
         <v>1.1</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>1.34</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I28">
         <v>1000</v>
       </c>
       <c r="J28">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="K28">
         <v>1000</v>
@@ -8093,22 +8093,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="O28">
         <v>1.09</v>
       </c>
       <c r="P28">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="Q28">
         <v>1.09</v>
       </c>
       <c r="R28">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
       <c r="S28">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -8120,7 +8120,7 @@
         <v>1.01</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -8311,13 +8311,13 @@
         <v>307</v>
       </c>
       <c r="F29">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G29">
         <v>4.8</v>
       </c>
       <c r="H29">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I29">
         <v>1.98</v>
@@ -8335,7 +8335,7 @@
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O29">
         <v>1.36</v>
@@ -8365,13 +8365,13 @@
         <v>1.27</v>
       </c>
       <c r="X29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y29">
         <v>12</v>
       </c>
       <c r="Z29">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA29">
         <v>110</v>
@@ -8383,7 +8383,7 @@
         <v>11.5</v>
       </c>
       <c r="AD29">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE29">
         <v>110</v>
@@ -8392,10 +8392,10 @@
         <v>90</v>
       </c>
       <c r="AG29">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AH29">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AI29">
         <v>1000</v>
@@ -8422,7 +8422,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ29">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR29">
         <v>8.4</v>
@@ -8431,7 +8431,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT29">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU29">
         <v>6.6</v>
@@ -8449,7 +8449,7 @@
         <v>13</v>
       </c>
       <c r="AZ29">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA29">
         <v>12</v>
@@ -8458,7 +8458,7 @@
         <v>30</v>
       </c>
       <c r="BC29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD29">
         <v>15</v>
@@ -8467,7 +8467,7 @@
         <v>32</v>
       </c>
       <c r="BF29">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="BG29">
         <v>9.800000000000001</v>
@@ -8553,7 +8553,7 @@
         <v>308</v>
       </c>
       <c r="F30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G30">
         <v>4.1</v>
@@ -8568,37 +8568,37 @@
         <v>4.1</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O30">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P30">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q30">
         <v>1.57</v>
       </c>
       <c r="R30">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S30">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T30">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U30">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V30">
         <v>2</v>
@@ -8685,7 +8685,7 @@
         <v>15.5</v>
       </c>
       <c r="AX30">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="AY30">
         <v>13.5</v>
@@ -8697,16 +8697,16 @@
         <v>20</v>
       </c>
       <c r="BB30">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC30">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BD30">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BF30">
         <v>21</v>
@@ -8798,7 +8798,7 @@
         <v>2.1</v>
       </c>
       <c r="G31">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H31">
         <v>3.25</v>
@@ -8810,7 +8810,7 @@
         <v>3.65</v>
       </c>
       <c r="K31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L31">
         <v>1.28</v>
@@ -8834,7 +8834,7 @@
         <v>1.42</v>
       </c>
       <c r="S31">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T31">
         <v>1.67</v>
@@ -8846,7 +8846,7 @@
         <v>1.37</v>
       </c>
       <c r="W31">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X31">
         <v>20</v>
@@ -9037,16 +9037,16 @@
         <v>310</v>
       </c>
       <c r="F32">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G32">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H32">
         <v>3.7</v>
       </c>
       <c r="I32">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J32">
         <v>4.1</v>
@@ -9058,13 +9058,13 @@
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N32">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P32">
         <v>2.46</v>
@@ -9076,19 +9076,19 @@
         <v>1.58</v>
       </c>
       <c r="S32">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T32">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U32">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V32">
         <v>1.34</v>
       </c>
       <c r="W32">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X32">
         <v>25</v>
@@ -9327,7 +9327,7 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.74</v>
@@ -9521,7 +9521,7 @@
         <v>312</v>
       </c>
       <c r="F34">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G34">
         <v>4.2</v>
@@ -9533,7 +9533,7 @@
         <v>2.24</v>
       </c>
       <c r="J34">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K34">
         <v>3.95</v>
@@ -9551,7 +9551,7 @@
         <v>1.04</v>
       </c>
       <c r="P34">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="Q34">
         <v>1.84</v>
@@ -9766,7 +9766,7 @@
         <v>1.64</v>
       </c>
       <c r="G35">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H35">
         <v>3.55</v>
@@ -9814,7 +9814,7 @@
         <v>1.2</v>
       </c>
       <c r="W35">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -10008,7 +10008,7 @@
         <v>1.25</v>
       </c>
       <c r="G36">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H36">
         <v>6.8</v>
@@ -10017,7 +10017,7 @@
         <v>1000</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K36">
         <v>18.5</v>
@@ -10029,13 +10029,13 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P36">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q36">
         <v>1.35</v>
@@ -10056,7 +10056,7 @@
         <v>1.01</v>
       </c>
       <c r="W36">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -10259,7 +10259,7 @@
         <v>110</v>
       </c>
       <c r="J37">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K37">
         <v>870</v>
@@ -10731,19 +10731,19 @@
         <v>317</v>
       </c>
       <c r="F39">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G39">
         <v>3.1</v>
       </c>
       <c r="H39">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I39">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K39">
         <v>4.3</v>
@@ -10755,37 +10755,37 @@
         <v>1.03</v>
       </c>
       <c r="N39">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="O39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P39">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="Q39">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="R39">
         <v>1.76</v>
       </c>
       <c r="S39">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T39">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U39">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="V39">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W39">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X39">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y39">
         <v>18</v>
@@ -10794,7 +10794,7 @@
         <v>21</v>
       </c>
       <c r="AA39">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB39">
         <v>21</v>
@@ -10806,7 +10806,7 @@
         <v>12.5</v>
       </c>
       <c r="AE39">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AF39">
         <v>27</v>
@@ -10821,37 +10821,37 @@
         <v>27</v>
       </c>
       <c r="AJ39">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AK39">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AL39">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AM39">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AN39">
         <v>15</v>
       </c>
       <c r="AO39">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP39">
         <v>11</v>
       </c>
       <c r="AQ39">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR39">
         <v>18</v>
       </c>
       <c r="AS39">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU39">
         <v>9.6</v>
@@ -10860,7 +10860,7 @@
         <v>10.5</v>
       </c>
       <c r="AW39">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX39">
         <v>10</v>
@@ -10872,16 +10872,16 @@
         <v>12.5</v>
       </c>
       <c r="BA39">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BB39">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC39">
         <v>20</v>
       </c>
       <c r="BD39">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BE39">
         <v>34</v>
@@ -11009,7 +11009,7 @@
         <v>1.44</v>
       </c>
       <c r="R40">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S40">
         <v>2.22</v>
@@ -11099,7 +11099,7 @@
         <v>10</v>
       </c>
       <c r="AV40">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW40">
         <v>8.199999999999999</v>
@@ -11108,7 +11108,7 @@
         <v>11.5</v>
       </c>
       <c r="AY40">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ40">
         <v>15</v>
@@ -11215,58 +11215,58 @@
         <v>319</v>
       </c>
       <c r="F41">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G41">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H41">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I41">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J41">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K41">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L41">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N41">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O41">
         <v>1.34</v>
       </c>
       <c r="P41">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Q41">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S41">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T41">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="U41">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X41">
         <v>14.5</v>
@@ -11278,73 +11278,73 @@
         <v>26</v>
       </c>
       <c r="AA41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB41">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC41">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD41">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE41">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AF41">
         <v>17</v>
       </c>
       <c r="AG41">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH41">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI41">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ41">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL41">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM41">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN41">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AO41">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AP41">
+        <v>12.5</v>
+      </c>
+      <c r="AQ41">
         <v>11</v>
-      </c>
-      <c r="AQ41">
-        <v>10.5</v>
       </c>
       <c r="AR41">
         <v>19.5</v>
       </c>
       <c r="AS41">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AT41">
         <v>8.6</v>
       </c>
       <c r="AU41">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV41">
         <v>12.5</v>
       </c>
       <c r="AW41">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AX41">
         <v>13</v>
@@ -11353,28 +11353,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ41">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA41">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BB41">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BC41">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD41">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BE41">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF41">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH41">
         <v>970</v>
@@ -11460,16 +11460,16 @@
         <v>3.3</v>
       </c>
       <c r="G42">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H42">
         <v>2.38</v>
       </c>
       <c r="I42">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J42">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K42">
         <v>3.5</v>
@@ -11484,13 +11484,13 @@
         <v>3.3</v>
       </c>
       <c r="O42">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P42">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q42">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R42">
         <v>1.3</v>
@@ -11499,13 +11499,13 @@
         <v>3.75</v>
       </c>
       <c r="T42">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V42">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W42">
         <v>1.38</v>
@@ -11556,13 +11556,13 @@
         <v>75</v>
       </c>
       <c r="AM42">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN42">
         <v>55</v>
       </c>
       <c r="AO42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP42">
         <v>10</v>
@@ -11598,25 +11598,25 @@
         <v>15</v>
       </c>
       <c r="BA42">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB42">
+        <v>7.4</v>
+      </c>
+      <c r="BC42">
+        <v>7</v>
+      </c>
+      <c r="BD42">
         <v>7.2</v>
       </c>
-      <c r="BC42">
-        <v>6.8</v>
-      </c>
-      <c r="BD42">
-        <v>7</v>
-      </c>
       <c r="BE42">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF42">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BG42">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH42">
         <v>3.9</v>
@@ -11699,118 +11699,118 @@
         <v>321</v>
       </c>
       <c r="F43">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G43">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H43">
         <v>3.05</v>
       </c>
       <c r="I43">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J43">
         <v>3.35</v>
       </c>
       <c r="K43">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L43">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M43">
         <v>1.07</v>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O43">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P43">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q43">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R43">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S43">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T43">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U43">
         <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
         <v>1.61</v>
       </c>
       <c r="X43">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y43">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z43">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA43">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB43">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC43">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE43">
+        <v>44</v>
+      </c>
+      <c r="AF43">
+        <v>22</v>
+      </c>
+      <c r="AG43">
+        <v>970</v>
+      </c>
+      <c r="AH43">
+        <v>22</v>
+      </c>
+      <c r="AI43">
+        <v>1000</v>
+      </c>
+      <c r="AJ43">
+        <v>44</v>
+      </c>
+      <c r="AK43">
         <v>36</v>
       </c>
-      <c r="AF43">
-        <v>21</v>
-      </c>
-      <c r="AG43">
-        <v>14.5</v>
-      </c>
-      <c r="AH43">
-        <v>17.5</v>
-      </c>
-      <c r="AI43">
-        <v>55</v>
-      </c>
-      <c r="AJ43">
-        <v>36</v>
-      </c>
-      <c r="AK43">
-        <v>28</v>
-      </c>
       <c r="AL43">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM43">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN43">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO43">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP43">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
         <v>1.01</v>
@@ -11819,25 +11819,25 @@
         <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU43">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AV43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
         <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
         <v>1.01</v>
@@ -11846,7 +11846,7 @@
         <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD43">
         <v>1.01</v>
@@ -11855,13 +11855,13 @@
         <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG43">
         <v>1.01</v>
       </c>
       <c r="BH43">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI43">
         <v>1.01</v>
@@ -11870,7 +11870,7 @@
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL43">
         <v>1000</v>
@@ -11879,7 +11879,7 @@
         <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO43">
         <v>1.01</v>
@@ -11974,13 +11974,13 @@
         <v>2.6</v>
       </c>
       <c r="Q44">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R44">
         <v>1.62</v>
       </c>
       <c r="S44">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T44">
         <v>1.52</v>
@@ -12013,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="AD44">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE44">
         <v>48</v>
@@ -12043,16 +12043,16 @@
         <v>70</v>
       </c>
       <c r="AN44">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO44">
         <v>29</v>
       </c>
       <c r="AP44">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ44">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR44">
         <v>6.8</v>
@@ -12070,7 +12070,7 @@
         <v>14</v>
       </c>
       <c r="AW44">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -12082,7 +12082,7 @@
         <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB44">
         <v>19.5</v>
@@ -12094,7 +12094,7 @@
         <v>21</v>
       </c>
       <c r="BE44">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF44">
         <v>7.4</v>
@@ -12183,16 +12183,16 @@
         <v>323</v>
       </c>
       <c r="F45">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G45">
         <v>1.66</v>
       </c>
       <c r="H45">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I45">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J45">
         <v>4.1</v>
@@ -12237,49 +12237,49 @@
         <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y45">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z45">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA45">
         <v>1000</v>
       </c>
       <c r="AB45">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC45">
+        <v>12.5</v>
+      </c>
+      <c r="AD45">
+        <v>85</v>
+      </c>
+      <c r="AE45">
+        <v>1000</v>
+      </c>
+      <c r="AF45">
+        <v>16</v>
+      </c>
+      <c r="AG45">
+        <v>12</v>
+      </c>
+      <c r="AH45">
+        <v>80</v>
+      </c>
+      <c r="AI45">
+        <v>1000</v>
+      </c>
+      <c r="AJ45">
+        <v>80</v>
+      </c>
+      <c r="AK45">
         <v>970</v>
       </c>
-      <c r="AD45">
-        <v>1000</v>
-      </c>
-      <c r="AE45">
-        <v>1000</v>
-      </c>
-      <c r="AF45">
-        <v>26</v>
-      </c>
-      <c r="AG45">
-        <v>970</v>
-      </c>
-      <c r="AH45">
-        <v>1000</v>
-      </c>
-      <c r="AI45">
-        <v>1000</v>
-      </c>
-      <c r="AJ45">
-        <v>1000</v>
-      </c>
-      <c r="AK45">
-        <v>1000</v>
-      </c>
       <c r="AL45">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM45">
         <v>1000</v>
@@ -12291,58 +12291,58 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.44</v>
+        <v>6.8</v>
       </c>
       <c r="AQ45">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="AR45">
-        <v>1.44</v>
+        <v>10.5</v>
       </c>
       <c r="AS45">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AT45">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU45">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV45">
-        <v>1.44</v>
+        <v>15.5</v>
       </c>
       <c r="AW45">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AX45">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY45">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ45">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BA45">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="BB45">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC45">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD45">
-        <v>1.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE45">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="BF45">
         <v>5.2</v>
       </c>
       <c r="BG45">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="BH45">
         <v>970</v>
@@ -12425,22 +12425,22 @@
         <v>324</v>
       </c>
       <c r="F46">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="G46">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="I46">
         <v>990</v>
       </c>
       <c r="J46">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K46">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12449,22 +12449,22 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O46">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P46">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Q46">
         <v>1.58</v>
       </c>
       <c r="R46">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="S46">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="T46">
         <v>1.11</v>
@@ -12473,10 +12473,10 @@
         <v>1.59</v>
       </c>
       <c r="V46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W46">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12667,22 +12667,22 @@
         <v>325</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="G47">
-        <v>25</v>
+        <v>990</v>
       </c>
       <c r="H47">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="I47">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="J47">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="K47">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="L47">
         <v>1.29</v>
@@ -12691,22 +12691,22 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
         <v>1.26</v>
       </c>
       <c r="P47">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="Q47">
         <v>1.75</v>
       </c>
       <c r="R47">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S47">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="T47">
         <v>1.11</v>
@@ -12715,10 +12715,10 @@
         <v>1.11</v>
       </c>
       <c r="V47">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="W47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
         <v>1000</v>
@@ -12924,7 +12924,7 @@
         <v>3.05</v>
       </c>
       <c r="K48">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="L48">
         <v>1.35</v>
@@ -13157,16 +13157,16 @@
         <v>2.12</v>
       </c>
       <c r="H49">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I49">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J49">
         <v>4.1</v>
       </c>
       <c r="K49">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13199,7 +13199,7 @@
         <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
         <v>1.89</v>
@@ -13223,7 +13223,7 @@
         <v>10</v>
       </c>
       <c r="AD49">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE49">
         <v>44</v>
@@ -13402,13 +13402,13 @@
         <v>7.8</v>
       </c>
       <c r="I50">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J50">
         <v>5.6</v>
       </c>
       <c r="K50">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L50">
         <v>1.2</v>
@@ -13426,7 +13426,7 @@
         <v>3</v>
       </c>
       <c r="Q50">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R50">
         <v>1.8</v>
@@ -13435,16 +13435,16 @@
         <v>2.08</v>
       </c>
       <c r="T50">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U50">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V50">
         <v>1.13</v>
       </c>
       <c r="W50">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X50">
         <v>42</v>
@@ -13531,7 +13531,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ50">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA50">
         <v>50</v>
@@ -13549,7 +13549,7 @@
         <v>60</v>
       </c>
       <c r="BF50">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BG50">
         <v>55</v>
@@ -13638,19 +13638,19 @@
         <v>2.24</v>
       </c>
       <c r="G51">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H51">
         <v>3.05</v>
       </c>
       <c r="I51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J51">
         <v>3.65</v>
       </c>
       <c r="K51">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13659,7 +13659,7 @@
         <v>1.05</v>
       </c>
       <c r="N51">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O51">
         <v>1.2</v>
@@ -13674,7 +13674,7 @@
         <v>1.51</v>
       </c>
       <c r="S51">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T51">
         <v>1.53</v>
@@ -13683,7 +13683,7 @@
         <v>2.34</v>
       </c>
       <c r="V51">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.71</v>
@@ -13877,7 +13877,7 @@
         <v>330</v>
       </c>
       <c r="F52">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G52">
         <v>2.74</v>
@@ -13892,7 +13892,7 @@
         <v>3.85</v>
       </c>
       <c r="K52">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13904,7 +13904,7 @@
         <v>6.4</v>
       </c>
       <c r="O52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P52">
         <v>2.92</v>
@@ -13919,10 +13919,10 @@
         <v>2.02</v>
       </c>
       <c r="T52">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="U52">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
         <v>1.56</v>
@@ -14119,7 +14119,7 @@
         <v>331</v>
       </c>
       <c r="F53">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G53">
         <v>2.08</v>
@@ -14131,7 +14131,7 @@
         <v>4.3</v>
       </c>
       <c r="J53">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K53">
         <v>5.1</v>
@@ -14143,13 +14143,13 @@
         <v>1.01</v>
       </c>
       <c r="N53">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O53">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P53">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q53">
         <v>1.38</v>
@@ -14376,7 +14376,7 @@
         <v>3.9</v>
       </c>
       <c r="K54">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -14385,22 +14385,22 @@
         <v>1.02</v>
       </c>
       <c r="N54">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O54">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P54">
         <v>2.3</v>
       </c>
       <c r="Q54">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R54">
         <v>1.52</v>
       </c>
       <c r="S54">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T54">
         <v>1.57</v>
@@ -14609,13 +14609,13 @@
         <v>2.26</v>
       </c>
       <c r="H55">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I55">
         <v>3.7</v>
       </c>
       <c r="J55">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K55">
         <v>3.8</v>
@@ -14651,13 +14651,13 @@
         <v>1.99</v>
       </c>
       <c r="V55">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W55">
         <v>1.79</v>
       </c>
       <c r="X55">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y55">
         <v>16.5</v>
@@ -14675,13 +14675,13 @@
         <v>9.6</v>
       </c>
       <c r="AD55">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE55">
         <v>60</v>
       </c>
       <c r="AF55">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG55">
         <v>13</v>
@@ -14720,19 +14720,19 @@
         <v>16</v>
       </c>
       <c r="AS55">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AT55">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="AU55">
-        <v>2.42</v>
+        <v>6.6</v>
       </c>
       <c r="AV55">
         <v>9.6</v>
       </c>
       <c r="AW55">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="AX55">
         <v>9.199999999999999</v>
@@ -14744,7 +14744,7 @@
         <v>11.5</v>
       </c>
       <c r="BA55">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="BB55">
         <v>18</v>
@@ -14753,10 +14753,10 @@
         <v>15</v>
       </c>
       <c r="BD55">
-        <v>3.05</v>
+        <v>14.5</v>
       </c>
       <c r="BE55">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BF55">
         <v>11.5</v>
@@ -14845,7 +14845,7 @@
         <v>334</v>
       </c>
       <c r="F56">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G56">
         <v>2.4</v>
@@ -14860,7 +14860,7 @@
         <v>3.55</v>
       </c>
       <c r="K56">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14869,19 +14869,19 @@
         <v>1.03</v>
       </c>
       <c r="N56">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O56">
         <v>1.25</v>
       </c>
       <c r="P56">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q56">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R56">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S56">
         <v>2.88</v>
@@ -14899,37 +14899,37 @@
         <v>1.71</v>
       </c>
       <c r="X56">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Y56">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z56">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA56">
         <v>1000</v>
       </c>
       <c r="AB56">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC56">
+        <v>10.5</v>
+      </c>
+      <c r="AD56">
         <v>970</v>
       </c>
-      <c r="AD56">
-        <v>1000</v>
-      </c>
       <c r="AE56">
         <v>1000</v>
       </c>
       <c r="AF56">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG56">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH56">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI56">
         <v>1000</v>
@@ -14953,58 +14953,58 @@
         <v>1000</v>
       </c>
       <c r="AP56">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AR56">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS56">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT56">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU56">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV56">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AW56">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX56">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AY56">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AZ56">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BA56">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB56">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC56">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD56">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BE56">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BF56">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BG56">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -15090,7 +15090,7 @@
         <v>1.84</v>
       </c>
       <c r="G57">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H57">
         <v>4.3</v>
@@ -15099,7 +15099,7 @@
         <v>4.8</v>
       </c>
       <c r="J57">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K57">
         <v>4.2</v>
@@ -15111,16 +15111,16 @@
         <v>1.06</v>
       </c>
       <c r="N57">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O57">
         <v>1.29</v>
       </c>
       <c r="P57">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q57">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="R57">
         <v>1.41</v>
@@ -15129,7 +15129,7 @@
         <v>3.1</v>
       </c>
       <c r="T57">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U57">
         <v>2.12</v>
@@ -15144,7 +15144,7 @@
         <v>20</v>
       </c>
       <c r="Y57">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z57">
         <v>42</v>
@@ -15153,10 +15153,10 @@
         <v>110</v>
       </c>
       <c r="AB57">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC57">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD57">
         <v>18.5</v>
@@ -15165,7 +15165,7 @@
         <v>65</v>
       </c>
       <c r="AF57">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG57">
         <v>10.5</v>
@@ -15180,7 +15180,7 @@
         <v>23</v>
       </c>
       <c r="AK57">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL57">
         <v>40</v>
@@ -15201,10 +15201,10 @@
         <v>14.5</v>
       </c>
       <c r="AR57">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS57">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT57">
         <v>8.4</v>
@@ -15216,37 +15216,37 @@
         <v>15.5</v>
       </c>
       <c r="AW57">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX57">
         <v>10.5</v>
       </c>
       <c r="AY57">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ57">
         <v>15.5</v>
       </c>
       <c r="BA57">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB57">
         <v>18</v>
       </c>
       <c r="BC57">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE57">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF57">
         <v>10</v>
       </c>
       <c r="BG57">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH57">
         <v>1000</v>
@@ -15338,7 +15338,7 @@
         <v>5</v>
       </c>
       <c r="I58">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J58">
         <v>4.5</v>
@@ -15386,7 +15386,7 @@
         <v>32</v>
       </c>
       <c r="Y58">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z58">
         <v>65</v>
@@ -15398,10 +15398,10 @@
         <v>15.5</v>
       </c>
       <c r="AC58">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD58">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE58">
         <v>70</v>
@@ -15419,7 +15419,7 @@
         <v>55</v>
       </c>
       <c r="AJ58">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK58">
         <v>16</v>
@@ -15437,16 +15437,16 @@
         <v>38</v>
       </c>
       <c r="AP58">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ58">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR58">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS58">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT58">
         <v>13</v>
@@ -15458,7 +15458,7 @@
         <v>18.5</v>
       </c>
       <c r="AW58">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX58">
         <v>12.5</v>
@@ -15470,7 +15470,7 @@
         <v>14</v>
       </c>
       <c r="BA58">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB58">
         <v>16</v>
@@ -15482,13 +15482,13 @@
         <v>20</v>
       </c>
       <c r="BE58">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF58">
         <v>5.2</v>
       </c>
       <c r="BG58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -15571,13 +15571,13 @@
         <v>337</v>
       </c>
       <c r="F59">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G59">
         <v>2.42</v>
       </c>
       <c r="H59">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I59">
         <v>3.65</v>
@@ -15604,13 +15604,13 @@
         <v>1.67</v>
       </c>
       <c r="Q59">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R59">
         <v>1.25</v>
       </c>
       <c r="S59">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T59">
         <v>1.82</v>
@@ -15625,10 +15625,10 @@
         <v>1.7</v>
       </c>
       <c r="X59">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y59">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z59">
         <v>29</v>
@@ -15637,10 +15637,10 @@
         <v>90</v>
       </c>
       <c r="AB59">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC59">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD59">
         <v>18.5</v>
@@ -15649,7 +15649,7 @@
         <v>60</v>
       </c>
       <c r="AF59">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG59">
         <v>13.5</v>
@@ -15667,7 +15667,7 @@
         <v>36</v>
       </c>
       <c r="AL59">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM59">
         <v>1000</v>
@@ -15679,58 +15679,58 @@
         <v>65</v>
       </c>
       <c r="AP59">
+        <v>8.4</v>
+      </c>
+      <c r="AQ59">
+        <v>9.4</v>
+      </c>
+      <c r="AR59">
+        <v>5</v>
+      </c>
+      <c r="AS59">
+        <v>18.5</v>
+      </c>
+      <c r="AT59">
         <v>8</v>
       </c>
-      <c r="AQ59">
-        <v>8.6</v>
-      </c>
-      <c r="AR59">
-        <v>3.75</v>
-      </c>
-      <c r="AS59">
-        <v>4.1</v>
-      </c>
-      <c r="AT59">
-        <v>6.8</v>
-      </c>
       <c r="AU59">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV59">
         <v>11</v>
       </c>
       <c r="AW59">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AX59">
         <v>10.5</v>
       </c>
       <c r="AY59">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ59">
         <v>13.5</v>
       </c>
       <c r="BA59">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="BB59">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="BC59">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BD59">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BE59">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BF59">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BG59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH59">
         <v>970</v>
@@ -15816,13 +15816,13 @@
         <v>2.36</v>
       </c>
       <c r="G60">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H60">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I60">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J60">
         <v>3.5</v>
@@ -15840,7 +15840,7 @@
         <v>3.9</v>
       </c>
       <c r="O60">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P60">
         <v>2.06</v>
@@ -15861,19 +15861,19 @@
         <v>2.16</v>
       </c>
       <c r="V60">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W60">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X60">
         <v>18.5</v>
       </c>
       <c r="Y60">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z60">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA60">
         <v>70</v>
@@ -15885,16 +15885,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD60">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE60">
         <v>48</v>
       </c>
       <c r="AF60">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG60">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH60">
         <v>17.5</v>
@@ -15906,7 +15906,7 @@
         <v>44</v>
       </c>
       <c r="AK60">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL60">
         <v>50</v>
@@ -15915,19 +15915,19 @@
         <v>100</v>
       </c>
       <c r="AN60">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO60">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP60">
         <v>14</v>
       </c>
       <c r="AQ60">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR60">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AS60">
         <v>32</v>
@@ -15951,25 +15951,25 @@
         <v>10</v>
       </c>
       <c r="AZ60">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA60">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB60">
         <v>23</v>
       </c>
       <c r="BC60">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BD60">
         <v>25</v>
       </c>
       <c r="BE60">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF60">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BG60">
         <v>18.5</v>
@@ -15984,55 +15984,55 @@
         <v>12.5</v>
       </c>
       <c r="BK60">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BL60">
         <v>1000</v>
       </c>
       <c r="BM60">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BN60">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO60">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP60">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ60">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BR60">
         <v>40</v>
       </c>
       <c r="BS60">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BT60">
         <v>8.6</v>
       </c>
       <c r="BU60">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV60">
         <v>34</v>
       </c>
       <c r="BW60">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BX60">
         <v>48</v>
       </c>
       <c r="BY60">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BZ60">
         <v>34</v>
       </c>
       <c r="CA60">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="CB60" t="s">
         <v>389</v>
@@ -16055,7 +16055,7 @@
         <v>339</v>
       </c>
       <c r="F61">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G61">
         <v>1.78</v>
@@ -16321,10 +16321,10 @@
         <v>1.09</v>
       </c>
       <c r="N62">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O62">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P62">
         <v>1.7</v>
@@ -16333,7 +16333,7 @@
         <v>2.22</v>
       </c>
       <c r="R62">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S62">
         <v>4</v>
@@ -16357,7 +16357,7 @@
         <v>11.5</v>
       </c>
       <c r="Z62">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA62">
         <v>80</v>
@@ -16366,7 +16366,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC62">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD62">
         <v>16.5</v>
@@ -16417,7 +16417,7 @@
         <v>6.6</v>
       </c>
       <c r="AT62">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU62">
         <v>6.6</v>
@@ -16426,16 +16426,16 @@
         <v>13</v>
       </c>
       <c r="AW62">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX62">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY62">
         <v>10</v>
       </c>
       <c r="AZ62">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA62">
         <v>6.6</v>
@@ -16450,13 +16450,13 @@
         <v>36</v>
       </c>
       <c r="BE62">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF62">
         <v>20</v>
       </c>
       <c r="BG62">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16563,13 +16563,13 @@
         <v>1.02</v>
       </c>
       <c r="N63">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="O63">
         <v>1.09</v>
       </c>
       <c r="P63">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q63">
         <v>1.35</v>
@@ -16578,7 +16578,7 @@
         <v>1.9</v>
       </c>
       <c r="S63">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T63">
         <v>1.33</v>
@@ -16695,7 +16695,7 @@
         <v>1.01</v>
       </c>
       <c r="BF63">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG63">
         <v>6.2</v>
@@ -16781,52 +16781,52 @@
         <v>342</v>
       </c>
       <c r="F64">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G64">
         <v>4.2</v>
       </c>
       <c r="H64">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="I64">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J64">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L64">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M64">
         <v>1.02</v>
       </c>
       <c r="N64">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O64">
         <v>1.25</v>
       </c>
       <c r="P64">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q64">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="R64">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S64">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="T64">
         <v>1.64</v>
       </c>
       <c r="U64">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V64">
         <v>1.84</v>
@@ -17044,10 +17044,10 @@
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N65">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="O65">
         <v>1.14</v>
@@ -17265,22 +17265,22 @@
         <v>344</v>
       </c>
       <c r="F66">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="G66">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H66">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J66">
         <v>3.45</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -17289,34 +17289,34 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="O66">
         <v>1.01</v>
       </c>
       <c r="P66">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q66">
+        <v>1.93</v>
+      </c>
+      <c r="R66">
+        <v>1.19</v>
+      </c>
+      <c r="S66">
+        <v>1.01</v>
+      </c>
+      <c r="T66">
+        <v>1.01</v>
+      </c>
+      <c r="U66">
+        <v>1.01</v>
+      </c>
+      <c r="V66">
+        <v>1.22</v>
+      </c>
+      <c r="W66">
         <v>1.87</v>
-      </c>
-      <c r="R66">
-        <v>1.18</v>
-      </c>
-      <c r="S66">
-        <v>2.56</v>
-      </c>
-      <c r="T66">
-        <v>1.01</v>
-      </c>
-      <c r="U66">
-        <v>1.01</v>
-      </c>
-      <c r="V66">
-        <v>1.21</v>
-      </c>
-      <c r="W66">
-        <v>1.81</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17507,16 +17507,16 @@
         <v>345</v>
       </c>
       <c r="F67">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G67">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="H67">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I67">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J67">
         <v>3.75</v>
@@ -17528,124 +17528,124 @@
         <v>1.01</v>
       </c>
       <c r="M67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N67">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O67">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P67">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q67">
+        <v>1.63</v>
+      </c>
+      <c r="R67">
         <v>1.57</v>
       </c>
-      <c r="R67">
-        <v>1.48</v>
-      </c>
       <c r="S67">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T67">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="U67">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W67">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X67">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y67">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z67">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA67">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB67">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC67">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD67">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE67">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF67">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG67">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH67">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI67">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ67">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK67">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL67">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM67">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN67">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO67">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP67">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ67">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR67">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS67">
         <v>1.01</v>
       </c>
       <c r="AT67">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU67">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV67">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW67">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX67">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY67">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ67">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA67">
         <v>1.01</v>
@@ -17654,7 +17654,7 @@
         <v>1.01</v>
       </c>
       <c r="BC67">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD67">
         <v>1.01</v>
@@ -17663,10 +17663,10 @@
         <v>1.01</v>
       </c>
       <c r="BF67">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG67">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -17752,10 +17752,10 @@
         <v>1.73</v>
       </c>
       <c r="G68">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H68">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I68">
         <v>4.7</v>
@@ -17764,28 +17764,28 @@
         <v>4.4</v>
       </c>
       <c r="K68">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L68">
         <v>1.01</v>
       </c>
       <c r="M68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="O68">
         <v>1.11</v>
       </c>
       <c r="P68">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q68">
         <v>1.39</v>
       </c>
       <c r="R68">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S68">
         <v>1.99</v>
@@ -17800,7 +17800,7 @@
         <v>1.27</v>
       </c>
       <c r="W68">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -18021,16 +18021,16 @@
         <v>1.14</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R69">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S69">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T69">
         <v>1.43</v>
@@ -18236,7 +18236,7 @@
         <v>3.15</v>
       </c>
       <c r="G70">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H70">
         <v>2.02</v>
@@ -18257,25 +18257,25 @@
         <v>1.02</v>
       </c>
       <c r="N70">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O70">
         <v>1.11</v>
       </c>
       <c r="P70">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q70">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R70">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S70">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T70">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U70">
         <v>3.2</v>
@@ -18284,22 +18284,22 @@
         <v>1.86</v>
       </c>
       <c r="W70">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X70">
         <v>55</v>
       </c>
       <c r="Y70">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z70">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA70">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB70">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC70">
         <v>14</v>
@@ -18314,7 +18314,7 @@
         <v>44</v>
       </c>
       <c r="AG70">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH70">
         <v>15</v>
@@ -18341,7 +18341,7 @@
         <v>7</v>
       </c>
       <c r="AP70">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ70">
         <v>19</v>
@@ -18350,10 +18350,10 @@
         <v>18.5</v>
       </c>
       <c r="AS70">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT70">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU70">
         <v>11</v>
@@ -18377,16 +18377,16 @@
         <v>18</v>
       </c>
       <c r="BB70">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC70">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD70">
         <v>21</v>
       </c>
       <c r="BE70">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF70">
         <v>11</v>
@@ -18475,55 +18475,55 @@
         <v>349</v>
       </c>
       <c r="F71">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G71">
         <v>1.8</v>
       </c>
       <c r="H71">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J71">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K71">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L71">
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N71">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P71">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="Q71">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="R71">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S71">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T71">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U71">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V71">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W71">
         <v>2.24</v>
@@ -18553,7 +18553,7 @@
         <v>1000</v>
       </c>
       <c r="AF71">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG71">
         <v>1000</v>
@@ -18568,16 +18568,16 @@
         <v>1000</v>
       </c>
       <c r="AK71">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL71">
         <v>1000</v>
       </c>
       <c r="AM71">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN71">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AO71">
         <v>1000</v>
@@ -18586,7 +18586,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ71">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR71">
         <v>1.01</v>
@@ -18598,7 +18598,7 @@
         <v>1.01</v>
       </c>
       <c r="AU71">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV71">
         <v>1.01</v>
@@ -18607,10 +18607,10 @@
         <v>1.01</v>
       </c>
       <c r="AX71">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY71">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ71">
         <v>1.01</v>
@@ -18625,7 +18625,7 @@
         <v>1.01</v>
       </c>
       <c r="BD71">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE71">
         <v>1.01</v>
@@ -18720,7 +18720,7 @@
         <v>2.44</v>
       </c>
       <c r="G72">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H72">
         <v>2.62</v>
@@ -18732,43 +18732,43 @@
         <v>4</v>
       </c>
       <c r="K72">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L72">
         <v>1.01</v>
       </c>
       <c r="M72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N72">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O72">
         <v>1.15</v>
       </c>
       <c r="P72">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
         <v>1.48</v>
       </c>
       <c r="R72">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="S72">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T72">
         <v>1.41</v>
       </c>
       <c r="U72">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V72">
         <v>1.54</v>
       </c>
       <c r="W72">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X72">
         <v>1000</v>
@@ -18849,7 +18849,7 @@
         <v>16</v>
       </c>
       <c r="AX72">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY72">
         <v>9.199999999999999</v>
@@ -19207,13 +19207,13 @@
         <v>1.09</v>
       </c>
       <c r="H74">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I74">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J74">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="K74">
         <v>21</v>
@@ -19225,34 +19225,34 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O74">
         <v>1.04</v>
       </c>
       <c r="P74">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Q74">
         <v>1.15</v>
       </c>
       <c r="R74">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T74">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V74">
         <v>1.02</v>
       </c>
       <c r="W74">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="X74">
         <v>140</v>
@@ -19261,7 +19261,7 @@
         <v>1000</v>
       </c>
       <c r="Z74">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="AA74">
         <v>1000</v>
@@ -19270,28 +19270,28 @@
         <v>32</v>
       </c>
       <c r="AC74">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AD74">
         <v>1000</v>
       </c>
       <c r="AE74">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AF74">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG74">
         <v>21</v>
       </c>
       <c r="AH74">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI74">
         <v>1000</v>
       </c>
       <c r="AJ74">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK74">
         <v>15.5</v>
@@ -19303,13 +19303,13 @@
         <v>1000</v>
       </c>
       <c r="AN74">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO74">
         <v>340</v>
       </c>
       <c r="AP74">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AQ74">
         <v>46</v>
@@ -19318,13 +19318,13 @@
         <v>100</v>
       </c>
       <c r="AS74">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="AT74">
         <v>21</v>
       </c>
       <c r="AU74">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV74">
         <v>40</v>
@@ -19333,10 +19333,10 @@
         <v>100</v>
       </c>
       <c r="AX74">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY74">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ74">
         <v>32</v>
@@ -19345,19 +19345,19 @@
         <v>48</v>
       </c>
       <c r="BB74">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC74">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD74">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE74">
         <v>46</v>
       </c>
       <c r="BF74">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BG74">
         <v>100</v>
@@ -19372,22 +19372,22 @@
         <v>16.5</v>
       </c>
       <c r="BK74">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL74">
         <v>110</v>
       </c>
       <c r="BM74">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BN74">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO74">
         <v>4.5</v>
       </c>
       <c r="BP74">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BQ74">
         <v>5.1</v>
@@ -19402,19 +19402,19 @@
         <v>30</v>
       </c>
       <c r="BU74">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV74">
         <v>170</v>
       </c>
       <c r="BW74">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BX74">
         <v>100</v>
       </c>
       <c r="BY74">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BZ74">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>353</v>
       </c>
       <c r="F75">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G75">
         <v>1.74</v>
@@ -19452,13 +19452,13 @@
         <v>4.9</v>
       </c>
       <c r="I75">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J75">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K75">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -19467,28 +19467,28 @@
         <v>1.02</v>
       </c>
       <c r="N75">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="O75">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P75">
         <v>2.52</v>
       </c>
       <c r="Q75">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R75">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S75">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T75">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V75">
         <v>1.23</v>
@@ -19497,64 +19497,64 @@
         <v>2.34</v>
       </c>
       <c r="X75">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y75">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z75">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA75">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB75">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC75">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD75">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE75">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF75">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG75">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH75">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI75">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ75">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK75">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL75">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM75">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN75">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AO75">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP75">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ75">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR75">
         <v>1.01</v>
@@ -19563,43 +19563,43 @@
         <v>1.01</v>
       </c>
       <c r="AT75">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU75">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV75">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW75">
         <v>1.01</v>
       </c>
       <c r="AX75">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY75">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ75">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA75">
         <v>1.01</v>
       </c>
       <c r="BB75">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC75">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD75">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE75">
         <v>1.01</v>
       </c>
       <c r="BF75">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG75">
         <v>1.01</v>
@@ -19691,13 +19691,13 @@
         <v>4.2</v>
       </c>
       <c r="H76">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I76">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J76">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K76">
         <v>3.55</v>
@@ -19706,37 +19706,37 @@
         <v>1.34</v>
       </c>
       <c r="M76">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N76">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O76">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P76">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q76">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R76">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S76">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="T76">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U76">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V76">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W76">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X76">
         <v>1000</v>
@@ -19927,19 +19927,19 @@
         <v>355</v>
       </c>
       <c r="F77">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G77">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H77">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="I77">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J77">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K77">
         <v>3.85</v>
@@ -19951,10 +19951,10 @@
         <v>1.06</v>
       </c>
       <c r="N77">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O77">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P77">
         <v>2.1</v>
@@ -19963,25 +19963,25 @@
         <v>1.83</v>
       </c>
       <c r="R77">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S77">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="T77">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="U77">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V77">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W77">
         <v>1.62</v>
       </c>
       <c r="X77">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y77">
         <v>14</v>
@@ -19996,7 +19996,7 @@
         <v>12.5</v>
       </c>
       <c r="AC77">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD77">
         <v>14</v>
@@ -20005,22 +20005,22 @@
         <v>34</v>
       </c>
       <c r="AF77">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG77">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH77">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI77">
         <v>42</v>
       </c>
       <c r="AJ77">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK77">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL77">
         <v>38</v>
@@ -20029,7 +20029,7 @@
         <v>95</v>
       </c>
       <c r="AN77">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO77">
         <v>27</v>
@@ -20038,13 +20038,13 @@
         <v>15</v>
       </c>
       <c r="AQ77">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR77">
         <v>18.5</v>
       </c>
       <c r="AS77">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT77">
         <v>10.5</v>
@@ -20053,13 +20053,13 @@
         <v>7.6</v>
       </c>
       <c r="AV77">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW77">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AX77">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY77">
         <v>10.5</v>
@@ -20068,25 +20068,25 @@
         <v>14.5</v>
       </c>
       <c r="BA77">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BB77">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BC77">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD77">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BE77">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF77">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG77">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BH77">
         <v>970</v>
@@ -20169,10 +20169,10 @@
         <v>356</v>
       </c>
       <c r="F78">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G78">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H78">
         <v>3.35</v>
@@ -20184,7 +20184,7 @@
         <v>3.4</v>
       </c>
       <c r="K78">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L78">
         <v>1.38</v>
@@ -20199,10 +20199,10 @@
         <v>1.35</v>
       </c>
       <c r="P78">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q78">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R78">
         <v>1.32</v>
@@ -20220,10 +20220,10 @@
         <v>1.39</v>
       </c>
       <c r="W78">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X78">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y78">
         <v>13</v>
@@ -20256,7 +20256,7 @@
         <v>18.5</v>
       </c>
       <c r="AI78">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ78">
         <v>32</v>
@@ -20298,7 +20298,7 @@
         <v>13</v>
       </c>
       <c r="AW78">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX78">
         <v>13</v>
@@ -20310,16 +20310,16 @@
         <v>16.5</v>
       </c>
       <c r="BA78">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB78">
         <v>27</v>
       </c>
       <c r="BC78">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD78">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE78">
         <v>12</v>
@@ -20328,7 +20328,7 @@
         <v>18</v>
       </c>
       <c r="BG78">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="BH78">
         <v>970</v>
@@ -20653,7 +20653,7 @@
         <v>358</v>
       </c>
       <c r="F80">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G80">
         <v>2.52</v>
@@ -20665,7 +20665,7 @@
         <v>3.2</v>
       </c>
       <c r="J80">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K80">
         <v>4.5</v>
@@ -20704,7 +20704,7 @@
         <v>1.46</v>
       </c>
       <c r="W80">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X80">
         <v>1000</v>
@@ -20895,19 +20895,19 @@
         <v>359</v>
       </c>
       <c r="F81">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="G81">
         <v>110</v>
       </c>
       <c r="H81">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="I81">
         <v>110</v>
       </c>
       <c r="J81">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K81">
         <v>900</v>
@@ -20919,7 +20919,7 @@
         <v>1.01</v>
       </c>
       <c r="N81">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O81">
         <v>1.01</v>
@@ -20928,13 +20928,13 @@
         <v>1.08</v>
       </c>
       <c r="Q81">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R81">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S81">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
         <v>1.01</v>
@@ -20943,10 +20943,10 @@
         <v>1.01</v>
       </c>
       <c r="V81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
         <v>1000</v>
@@ -21137,10 +21137,10 @@
         <v>360</v>
       </c>
       <c r="F82">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G82">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H82">
         <v>1.12</v>
@@ -21149,7 +21149,7 @@
         <v>110</v>
       </c>
       <c r="J82">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K82">
         <v>890</v>
@@ -21167,13 +21167,13 @@
         <v>1.01</v>
       </c>
       <c r="P82">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q82">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R82">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S82">
         <v>1.33</v>
@@ -21185,10 +21185,10 @@
         <v>1.01</v>
       </c>
       <c r="V82">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W82">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
         <v>1000</v>
@@ -21379,13 +21379,13 @@
         <v>361</v>
       </c>
       <c r="F83">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G83">
         <v>110</v>
       </c>
       <c r="H83">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="I83">
         <v>110</v>
@@ -21427,10 +21427,10 @@
         <v>1.01</v>
       </c>
       <c r="V83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
         <v>1000</v>
@@ -21869,7 +21869,7 @@
         <v>3.3</v>
       </c>
       <c r="H85">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I85">
         <v>2.44</v>
@@ -21893,7 +21893,7 @@
         <v>1.29</v>
       </c>
       <c r="P85">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q85">
         <v>1.87</v>
@@ -21905,7 +21905,7 @@
         <v>3.2</v>
       </c>
       <c r="T85">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U85">
         <v>2.34</v>
@@ -21917,7 +21917,7 @@
         <v>1.43</v>
       </c>
       <c r="X85">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y85">
         <v>11.5</v>
@@ -21950,7 +21950,7 @@
         <v>16</v>
       </c>
       <c r="AI85">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ85">
         <v>55</v>
@@ -21974,7 +21974,7 @@
         <v>14</v>
       </c>
       <c r="AQ85">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR85">
         <v>15</v>
@@ -22040,7 +22040,7 @@
         <v>120</v>
       </c>
       <c r="BM85">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BN85">
         <v>6.4</v>
@@ -22162,7 +22162,7 @@
         <v>1000</v>
       </c>
       <c r="Y86">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z86">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>970</v>
       </c>
       <c r="AD86">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE86">
         <v>1000</v>
@@ -22228,7 +22228,7 @@
         <v>1.01</v>
       </c>
       <c r="AU86">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV86">
         <v>1.01</v>
@@ -22237,10 +22237,10 @@
         <v>1.01</v>
       </c>
       <c r="AX86">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY86">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ86">
         <v>1.01</v>
@@ -22347,22 +22347,22 @@
         <v>365</v>
       </c>
       <c r="F87">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G87">
         <v>1.54</v>
       </c>
       <c r="H87">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I87">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J87">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K87">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L87">
         <v>1.01</v>
@@ -22377,25 +22377,25 @@
         <v>1.17</v>
       </c>
       <c r="P87">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="Q87">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R87">
         <v>1.52</v>
       </c>
       <c r="S87">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="T87">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U87">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V87">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W87">
         <v>2.86</v>
@@ -22449,7 +22449,7 @@
         <v>1000</v>
       </c>
       <c r="AN87">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO87">
         <v>1000</v>
@@ -22613,10 +22613,10 @@
         <v>1.07</v>
       </c>
       <c r="N88">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O88">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P88">
         <v>1.92</v>
@@ -23073,13 +23073,13 @@
         <v>368</v>
       </c>
       <c r="F90">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G90">
         <v>4.8</v>
       </c>
       <c r="H90">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I90">
         <v>2</v>
@@ -23088,7 +23088,7 @@
         <v>3.75</v>
       </c>
       <c r="K90">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L90">
         <v>1.28</v>
@@ -23097,7 +23097,7 @@
         <v>1.01</v>
       </c>
       <c r="N90">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O90">
         <v>1.25</v>
@@ -23106,7 +23106,7 @@
         <v>2.04</v>
       </c>
       <c r="Q90">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R90">
         <v>1.37</v>
@@ -23342,7 +23342,7 @@
         <v>5.5</v>
       </c>
       <c r="O91">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P91">
         <v>2.56</v>
@@ -23402,7 +23402,7 @@
         <v>14.5</v>
       </c>
       <c r="AI91">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ91">
         <v>27</v>
@@ -23414,13 +23414,13 @@
         <v>26</v>
       </c>
       <c r="AM91">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN91">
         <v>10.5</v>
       </c>
       <c r="AO91">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP91">
         <v>21</v>
@@ -23465,7 +23465,7 @@
         <v>17</v>
       </c>
       <c r="BD91">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BE91">
         <v>48</v>
@@ -23492,7 +23492,7 @@
         <v>1000</v>
       </c>
       <c r="BM91">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BN91">
         <v>7.4</v>
@@ -23510,7 +23510,7 @@
         <v>1000</v>
       </c>
       <c r="BS91">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT91">
         <v>970</v>
@@ -23522,19 +23522,19 @@
         <v>1000</v>
       </c>
       <c r="BW91">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX91">
         <v>1000</v>
       </c>
       <c r="BY91">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ91">
         <v>1000</v>
       </c>
       <c r="CA91">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB91" t="s">
         <v>389</v>
@@ -23593,13 +23593,13 @@
         <v>1.64</v>
       </c>
       <c r="R92">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S92">
         <v>2.62</v>
       </c>
       <c r="T92">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="U92">
         <v>2.28</v>
@@ -23799,22 +23799,22 @@
         <v>371</v>
       </c>
       <c r="F93">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="G93">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="H93">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I93">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J93">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K93">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L93">
         <v>1.4</v>
@@ -23823,22 +23823,22 @@
         <v>1.08</v>
       </c>
       <c r="N93">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O93">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P93">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q93">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R93">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S93">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T93">
         <v>1.94</v>
@@ -23847,28 +23847,28 @@
         <v>1.96</v>
       </c>
       <c r="V93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W93">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="X93">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Y93">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z93">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA93">
         <v>130</v>
       </c>
       <c r="AB93">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC93">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD93">
         <v>22</v>
@@ -23877,10 +23877,10 @@
         <v>75</v>
       </c>
       <c r="AF93">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG93">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH93">
         <v>21</v>
@@ -23889,19 +23889,19 @@
         <v>100</v>
       </c>
       <c r="AJ93">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK93">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL93">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM93">
         <v>150</v>
       </c>
       <c r="AN93">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO93">
         <v>95</v>
@@ -23913,10 +23913,10 @@
         <v>12.5</v>
       </c>
       <c r="AR93">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AS93">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT93">
         <v>7.4</v>
@@ -23925,40 +23925,40 @@
         <v>7.2</v>
       </c>
       <c r="AV93">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW93">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX93">
+        <v>9.6</v>
+      </c>
+      <c r="AY93">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX93">
-        <v>10</v>
-      </c>
-      <c r="AY93">
-        <v>9.6</v>
-      </c>
       <c r="AZ93">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA93">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB93">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BC93">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BD93">
+        <v>7.8</v>
+      </c>
+      <c r="BE93">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE93">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF93">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BG93">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH93">
         <v>970</v>
@@ -24044,7 +24044,7 @@
         <v>2.2</v>
       </c>
       <c r="G94">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H94">
         <v>3.15</v>
@@ -24056,25 +24056,25 @@
         <v>3.3</v>
       </c>
       <c r="K94">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L94">
         <v>1.01</v>
       </c>
       <c r="M94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N94">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O94">
         <v>1.26</v>
       </c>
       <c r="P94">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q94">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R94">
         <v>1.37</v>
@@ -24083,16 +24083,16 @@
         <v>2.88</v>
       </c>
       <c r="T94">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U94">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V94">
         <v>1.35</v>
       </c>
       <c r="W94">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X94">
         <v>1000</v>
@@ -24212,55 +24212,55 @@
         <v>1000</v>
       </c>
       <c r="BK94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BL94">
         <v>1000</v>
       </c>
       <c r="BM94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BN94">
         <v>1000</v>
       </c>
       <c r="BO94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BP94">
         <v>1000</v>
       </c>
       <c r="BQ94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BR94">
         <v>1000</v>
       </c>
       <c r="BS94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BT94">
         <v>1000</v>
       </c>
       <c r="BU94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BV94">
         <v>1000</v>
       </c>
       <c r="BW94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BX94">
         <v>1000</v>
       </c>
       <c r="BY94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BZ94">
         <v>1000</v>
       </c>
       <c r="CA94">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="CB94" t="s">
         <v>389</v>
@@ -24295,7 +24295,7 @@
         <v>4.8</v>
       </c>
       <c r="J95">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K95">
         <v>3.85</v>
@@ -24319,10 +24319,10 @@
         <v>1.89</v>
       </c>
       <c r="R95">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S95">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T95">
         <v>1.78</v>
@@ -24346,13 +24346,13 @@
         <v>36</v>
       </c>
       <c r="AA95">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB95">
         <v>9.800000000000001</v>
       </c>
       <c r="AC95">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD95">
         <v>18</v>
@@ -24370,13 +24370,13 @@
         <v>18.5</v>
       </c>
       <c r="AI95">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ95">
         <v>21</v>
       </c>
       <c r="AK95">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL95">
         <v>34</v>
@@ -24400,10 +24400,10 @@
         <v>32</v>
       </c>
       <c r="AS95">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT95">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU95">
         <v>8</v>
@@ -24460,7 +24460,7 @@
         <v>140</v>
       </c>
       <c r="BM95">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BN95">
         <v>4.6</v>
@@ -24552,7 +24552,7 @@
         <v>1.09</v>
       </c>
       <c r="O96">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="P96">
         <v>1.09</v>
@@ -24770,19 +24770,19 @@
         <v>1.44</v>
       </c>
       <c r="G97">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="H97">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I97">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K97">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L97">
         <v>1.29</v>
@@ -24794,34 +24794,34 @@
         <v>4.8</v>
       </c>
       <c r="O97">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P97">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q97">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R97">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S97">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="T97">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="U97">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V97">
         <v>1.14</v>
       </c>
       <c r="W97">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="X97">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y97">
         <v>29</v>
@@ -24830,13 +24830,13 @@
         <v>65</v>
       </c>
       <c r="AA97">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB97">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC97">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD97">
         <v>32</v>
@@ -24845,10 +24845,10 @@
         <v>120</v>
       </c>
       <c r="AF97">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG97">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH97">
         <v>26</v>
@@ -24857,7 +24857,7 @@
         <v>100</v>
       </c>
       <c r="AJ97">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK97">
         <v>15</v>
@@ -24872,7 +24872,7 @@
         <v>6.2</v>
       </c>
       <c r="AO97">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP97">
         <v>18.5</v>
@@ -24881,10 +24881,10 @@
         <v>19.5</v>
       </c>
       <c r="AR97">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS97">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT97">
         <v>9</v>
@@ -24893,40 +24893,40 @@
         <v>10.5</v>
       </c>
       <c r="AV97">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AW97">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AX97">
         <v>8.4</v>
       </c>
       <c r="AY97">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ97">
         <v>18</v>
       </c>
       <c r="BA97">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB97">
         <v>11</v>
       </c>
       <c r="BC97">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD97">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE97">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF97">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG97">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH97">
         <v>970</v>
@@ -25009,16 +25009,16 @@
         <v>376</v>
       </c>
       <c r="F98">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G98">
         <v>1.93</v>
       </c>
       <c r="H98">
+        <v>4.3</v>
+      </c>
+      <c r="I98">
         <v>4.4</v>
-      </c>
-      <c r="I98">
-        <v>4.5</v>
       </c>
       <c r="J98">
         <v>3.9</v>
@@ -25039,10 +25039,10 @@
         <v>1.3</v>
       </c>
       <c r="P98">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q98">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R98">
         <v>1.41</v>
@@ -25051,13 +25051,13 @@
         <v>3.25</v>
       </c>
       <c r="T98">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U98">
         <v>2.16</v>
       </c>
       <c r="V98">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W98">
         <v>2.06</v>
@@ -25069,7 +25069,7 @@
         <v>17</v>
       </c>
       <c r="Z98">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA98">
         <v>95</v>
@@ -25081,7 +25081,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD98">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE98">
         <v>55</v>
@@ -25096,7 +25096,7 @@
         <v>19</v>
       </c>
       <c r="AI98">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ98">
         <v>22</v>
@@ -25114,7 +25114,7 @@
         <v>12.5</v>
       </c>
       <c r="AO98">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="AP98">
         <v>14</v>
@@ -25123,7 +25123,7 @@
         <v>15</v>
       </c>
       <c r="AR98">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AS98">
         <v>36</v>
@@ -25168,7 +25168,7 @@
         <v>11</v>
       </c>
       <c r="BG98">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH98">
         <v>970</v>
@@ -25186,7 +25186,7 @@
         <v>1000</v>
       </c>
       <c r="BM98">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BN98">
         <v>6.2</v>
@@ -25204,7 +25204,7 @@
         <v>1000</v>
       </c>
       <c r="BS98">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT98">
         <v>970</v>
@@ -25216,19 +25216,19 @@
         <v>1000</v>
       </c>
       <c r="BW98">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX98">
         <v>1000</v>
       </c>
       <c r="BY98">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BZ98">
         <v>1000</v>
       </c>
       <c r="CA98">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB98" t="s">
         <v>389</v>
@@ -25257,7 +25257,7 @@
         <v>2.94</v>
       </c>
       <c r="H99">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I99">
         <v>2.48</v>
@@ -25284,10 +25284,10 @@
         <v>2.88</v>
       </c>
       <c r="Q99">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R99">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S99">
         <v>2.26</v>
@@ -25296,7 +25296,7 @@
         <v>1.46</v>
       </c>
       <c r="U99">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V99">
         <v>1.67</v>
@@ -25317,7 +25317,7 @@
         <v>36</v>
       </c>
       <c r="AB99">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC99">
         <v>9.800000000000001</v>
@@ -25347,10 +25347,10 @@
         <v>26</v>
       </c>
       <c r="AL99">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM99">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN99">
         <v>15</v>
@@ -25404,7 +25404,7 @@
         <v>26</v>
       </c>
       <c r="BE99">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF99">
         <v>13.5</v>
@@ -25428,7 +25428,7 @@
         <v>65</v>
       </c>
       <c r="BM99">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN99">
         <v>6.4</v>
@@ -25446,7 +25446,7 @@
         <v>24</v>
       </c>
       <c r="BS99">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT99">
         <v>5.9</v>
@@ -25461,7 +25461,7 @@
         <v>13.5</v>
       </c>
       <c r="BX99">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY99">
         <v>11</v>
@@ -25517,16 +25517,16 @@
         <v>1.01</v>
       </c>
       <c r="N100">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O100">
         <v>1.19</v>
       </c>
       <c r="P100">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q100">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R100">
         <v>1.49</v>
@@ -25535,10 +25535,10 @@
         <v>2.48</v>
       </c>
       <c r="T100">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U100">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V100">
         <v>1.16</v>
@@ -25735,40 +25735,40 @@
         <v>379</v>
       </c>
       <c r="F101">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G101">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H101">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I101">
         <v>3.85</v>
       </c>
       <c r="J101">
-        <v>2.46</v>
+        <v>1.12</v>
       </c>
       <c r="K101">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="L101">
         <v>1.59</v>
       </c>
       <c r="M101">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N101">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O101">
         <v>1.53</v>
       </c>
       <c r="P101">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Q101">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R101">
         <v>1.14</v>
@@ -25777,7 +25777,7 @@
         <v>3.15</v>
       </c>
       <c r="T101">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U101">
         <v>1.01</v>
@@ -25786,7 +25786,7 @@
         <v>1.35</v>
       </c>
       <c r="W101">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X101">
         <v>1000</v>
@@ -25918,7 +25918,7 @@
         <v>1000</v>
       </c>
       <c r="BO101">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP101">
         <v>1000</v>
@@ -25977,22 +25977,22 @@
         <v>380</v>
       </c>
       <c r="F102">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G102">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H102">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I102">
-        <v>110</v>
+        <v>11.5</v>
       </c>
       <c r="J102">
         <v>3.9</v>
       </c>
       <c r="K102">
-        <v>110</v>
+        <v>6.6</v>
       </c>
       <c r="L102">
         <v>1.01</v>
@@ -26001,22 +26001,22 @@
         <v>1.02</v>
       </c>
       <c r="N102">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O102">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P102">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q102">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="R102">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S102">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="T102">
         <v>1.01</v>
@@ -26028,7 +26028,7 @@
         <v>1.15</v>
       </c>
       <c r="W102">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X102">
         <v>1000</v>
@@ -26219,13 +26219,13 @@
         <v>381</v>
       </c>
       <c r="F103">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G103">
         <v>3.15</v>
       </c>
       <c r="H103">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I103">
         <v>2.88</v>
@@ -26240,22 +26240,22 @@
         <v>1.53</v>
       </c>
       <c r="M103">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N103">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O103">
         <v>1.53</v>
       </c>
       <c r="P103">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
       </c>
       <c r="R103">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S103">
         <v>4.8</v>
@@ -26273,7 +26273,7 @@
         <v>1.46</v>
       </c>
       <c r="X103">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y103">
         <v>10.5</v>
@@ -26336,7 +26336,7 @@
         <v>3.4</v>
       </c>
       <c r="AS103">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AT103">
         <v>7</v>
@@ -26351,7 +26351,7 @@
         <v>3.65</v>
       </c>
       <c r="AX103">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AY103">
         <v>3.35</v>
@@ -26360,22 +26360,22 @@
         <v>18.5</v>
       </c>
       <c r="BA103">
+        <v>3.75</v>
+      </c>
+      <c r="BB103">
         <v>3.8</v>
-      </c>
-      <c r="BB103">
-        <v>3.85</v>
       </c>
       <c r="BC103">
         <v>3.8</v>
       </c>
       <c r="BD103">
+        <v>3.85</v>
+      </c>
+      <c r="BE103">
         <v>3.9</v>
       </c>
-      <c r="BE103">
-        <v>3.95</v>
-      </c>
       <c r="BF103">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG103">
         <v>3.8</v>
@@ -26461,7 +26461,7 @@
         <v>382</v>
       </c>
       <c r="F104">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G104">
         <v>1.47</v>
@@ -26470,7 +26470,7 @@
         <v>9.6</v>
       </c>
       <c r="I104">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J104">
         <v>4.6</v>
@@ -26488,16 +26488,16 @@
         <v>3.4</v>
       </c>
       <c r="O104">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P104">
         <v>1.92</v>
       </c>
       <c r="Q104">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R104">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S104">
         <v>2.68</v>
@@ -26730,16 +26730,16 @@
         <v>1.1</v>
       </c>
       <c r="O105">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="P105">
         <v>1.1</v>
       </c>
       <c r="Q105">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="R105">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S105">
         <v>1.41</v>
@@ -26751,10 +26751,10 @@
         <v>1.01</v>
       </c>
       <c r="V105">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W105">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
         <v>1000</v>
@@ -26948,13 +26948,13 @@
         <v>1.47</v>
       </c>
       <c r="G106">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H106">
         <v>6.8</v>
       </c>
       <c r="I106">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J106">
         <v>3.85</v>
@@ -26969,22 +26969,22 @@
         <v>1.03</v>
       </c>
       <c r="N106">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O106">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P106">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q106">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R106">
         <v>1.32</v>
       </c>
       <c r="S106">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T106">
         <v>1.95</v>
@@ -26996,7 +26996,7 @@
         <v>1.09</v>
       </c>
       <c r="W106">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X106">
         <v>1000</v>
@@ -27226,7 +27226,7 @@
         <v>1.09</v>
       </c>
       <c r="S107">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="T107">
         <v>1.01</v>
@@ -27235,10 +27235,10 @@
         <v>1.01</v>
       </c>
       <c r="V107">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W107">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
         <v>1000</v>
@@ -27429,112 +27429,112 @@
         <v>386</v>
       </c>
       <c r="F108">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G108">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="H108">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="I108">
+        <v>4.7</v>
+      </c>
+      <c r="J108">
+        <v>3.1</v>
+      </c>
+      <c r="K108">
+        <v>3.5</v>
+      </c>
+      <c r="L108">
+        <v>1.01</v>
+      </c>
+      <c r="M108">
+        <v>1.1</v>
+      </c>
+      <c r="N108">
+        <v>2.86</v>
+      </c>
+      <c r="O108">
+        <v>1.46</v>
+      </c>
+      <c r="P108">
+        <v>1.55</v>
+      </c>
+      <c r="Q108">
+        <v>2.32</v>
+      </c>
+      <c r="R108">
+        <v>1.2</v>
+      </c>
+      <c r="S108">
         <v>4</v>
       </c>
-      <c r="J108">
-        <v>2.84</v>
-      </c>
-      <c r="K108">
-        <v>950</v>
-      </c>
-      <c r="L108">
-        <v>1.01</v>
-      </c>
-      <c r="M108">
-        <v>1.07</v>
-      </c>
-      <c r="N108">
-        <v>2.58</v>
-      </c>
-      <c r="O108">
-        <v>1.47</v>
-      </c>
-      <c r="P108">
-        <v>1.45</v>
-      </c>
-      <c r="Q108">
-        <v>1.88</v>
-      </c>
-      <c r="R108">
-        <v>1.08</v>
-      </c>
-      <c r="S108">
-        <v>1.01</v>
-      </c>
       <c r="T108">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U108">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="V108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W108">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="X108">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y108">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z108">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA108">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB108">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC108">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD108">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE108">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF108">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG108">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH108">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI108">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ108">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK108">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL108">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM108">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN108">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO108">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP108">
         <v>1.01</v>
@@ -27680,7 +27680,7 @@
         <v>2.34</v>
       </c>
       <c r="I109">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J109">
         <v>3</v>
@@ -27695,22 +27695,22 @@
         <v>1.05</v>
       </c>
       <c r="N109">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O109">
         <v>1.38</v>
       </c>
       <c r="P109">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q109">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R109">
         <v>1.24</v>
       </c>
       <c r="S109">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="T109">
         <v>1.81</v>
@@ -27719,7 +27719,7 @@
         <v>1.92</v>
       </c>
       <c r="V109">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W109">
         <v>1.4</v>
@@ -27913,22 +27913,22 @@
         <v>388</v>
       </c>
       <c r="F110">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G110">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H110">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I110">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J110">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K110">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L110">
         <v>1.27</v>
@@ -27940,16 +27940,16 @@
         <v>6.2</v>
       </c>
       <c r="O110">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P110">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q110">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R110">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S110">
         <v>2.26</v>
@@ -27961,118 +27961,118 @@
         <v>2.6</v>
       </c>
       <c r="V110">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
         <v>2.12</v>
       </c>
       <c r="X110">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y110">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z110">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA110">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB110">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AC110">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD110">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE110">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF110">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="AG110">
+        <v>11.5</v>
+      </c>
+      <c r="AH110">
+        <v>18.5</v>
+      </c>
+      <c r="AI110">
+        <v>44</v>
+      </c>
+      <c r="AJ110">
+        <v>25</v>
+      </c>
+      <c r="AK110">
+        <v>19.5</v>
+      </c>
+      <c r="AL110">
+        <v>29</v>
+      </c>
+      <c r="AM110">
+        <v>65</v>
+      </c>
+      <c r="AN110">
+        <v>7.2</v>
+      </c>
+      <c r="AO110">
+        <v>32</v>
+      </c>
+      <c r="AP110">
+        <v>6.8</v>
+      </c>
+      <c r="AQ110">
         <v>20</v>
       </c>
-      <c r="AH110">
-        <v>85</v>
-      </c>
-      <c r="AI110">
-        <v>1000</v>
-      </c>
-      <c r="AJ110">
-        <v>1000</v>
-      </c>
-      <c r="AK110">
-        <v>1000</v>
-      </c>
-      <c r="AL110">
-        <v>1000</v>
-      </c>
-      <c r="AM110">
-        <v>1000</v>
-      </c>
-      <c r="AN110">
-        <v>10.5</v>
-      </c>
-      <c r="AO110">
-        <v>1000</v>
-      </c>
-      <c r="AP110">
-        <v>1.51</v>
-      </c>
-      <c r="AQ110">
-        <v>1.51</v>
-      </c>
       <c r="AR110">
-        <v>1.51</v>
+        <v>7</v>
       </c>
       <c r="AS110">
-        <v>1.51</v>
+        <v>7.8</v>
       </c>
       <c r="AT110">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AU110">
+        <v>10</v>
+      </c>
+      <c r="AV110">
+        <v>15</v>
+      </c>
+      <c r="AW110">
         <v>7.2</v>
       </c>
-      <c r="AV110">
-        <v>11</v>
-      </c>
-      <c r="AW110">
-        <v>1.51</v>
-      </c>
       <c r="AX110">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY110">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ110">
+        <v>14</v>
+      </c>
+      <c r="BA110">
+        <v>7</v>
+      </c>
+      <c r="BB110">
+        <v>19</v>
+      </c>
+      <c r="BC110">
+        <v>15</v>
+      </c>
+      <c r="BD110">
+        <v>21</v>
+      </c>
+      <c r="BE110">
         <v>7.4</v>
       </c>
-      <c r="AZ110">
-        <v>10</v>
-      </c>
-      <c r="BA110">
-        <v>1.51</v>
-      </c>
-      <c r="BB110">
-        <v>1.51</v>
-      </c>
-      <c r="BC110">
-        <v>8.6</v>
-      </c>
-      <c r="BD110">
-        <v>1.51</v>
-      </c>
-      <c r="BE110">
-        <v>1.51</v>
-      </c>
       <c r="BF110">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG110">
-        <v>1.51</v>
+        <v>20</v>
       </c>
       <c r="BH110">
         <v>6.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-18.xlsx
@@ -1183,7 +1183,7 @@
     <t>New York Red Bulls</t>
   </si>
   <si>
-    <t>2026-09-17 03:45:33</t>
+    <t>2026-09-17 06:05:55</t>
   </si>
 </sst>
 </file>
@@ -1783,7 +1783,7 @@
         <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
         <v>3.7</v>
@@ -1813,16 +1813,16 @@
         <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -1879,10 +1879,10 @@
         <v>160</v>
       </c>
       <c r="AN2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP2">
         <v>9.6</v>
@@ -1918,7 +1918,7 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
         <v>24</v>
@@ -1930,7 +1930,7 @@
         <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
@@ -1942,7 +1942,7 @@
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
         <v>11</v>
@@ -1954,25 +1954,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
         <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
         <v>7</v>
@@ -1984,19 +1984,19 @@
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX2">
         <v>50</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>389</v>
@@ -2019,46 +2019,46 @@
         <v>281</v>
       </c>
       <c r="F3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G3">
         <v>1.16</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <v>29</v>
       </c>
       <c r="J3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>14</v>
       </c>
       <c r="L3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="O3">
         <v>1.06</v>
       </c>
       <c r="P3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="R3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
         <v>1.78</v>
@@ -2070,7 +2070,7 @@
         <v>1.04</v>
       </c>
       <c r="W3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="X3">
         <v>120</v>
@@ -2100,7 +2100,7 @@
         <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH3">
         <v>46</v>
@@ -2112,7 +2112,7 @@
         <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL3">
         <v>40</v>
@@ -2127,58 +2127,58 @@
         <v>240</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
       </c>
       <c r="AV3">
+        <v>7.8</v>
+      </c>
+      <c r="AW3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX3">
+        <v>5.9</v>
+      </c>
+      <c r="AY3">
+        <v>5.7</v>
+      </c>
+      <c r="AZ3">
         <v>7</v>
       </c>
-      <c r="AW3">
-        <v>7.4</v>
-      </c>
-      <c r="AX3">
+      <c r="BA3">
+        <v>8</v>
+      </c>
+      <c r="BB3">
+        <v>5.4</v>
+      </c>
+      <c r="BC3">
         <v>5.5</v>
       </c>
-      <c r="AY3">
-        <v>5.5</v>
-      </c>
-      <c r="AZ3">
-        <v>19.5</v>
-      </c>
-      <c r="BA3">
-        <v>7.2</v>
-      </c>
-      <c r="BB3">
-        <v>5</v>
-      </c>
-      <c r="BC3">
-        <v>5.3</v>
-      </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF3">
         <v>1.88</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2261,34 +2261,34 @@
         <v>282</v>
       </c>
       <c r="F4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H4">
         <v>2.14</v>
       </c>
       <c r="I4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
         <v>1.67</v>
@@ -2297,16 +2297,16 @@
         <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V4">
         <v>1.79</v>
@@ -2327,7 +2327,7 @@
         <v>36</v>
       </c>
       <c r="AB4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -2366,10 +2366,10 @@
         <v>90</v>
       </c>
       <c r="AO4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP4">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4">
         <v>7</v>
@@ -2396,28 +2396,28 @@
         <v>23</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC4">
         <v>6.6</v>
       </c>
       <c r="BD4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
         <v>20</v>
@@ -2503,22 +2503,22 @@
         <v>283</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>1.12</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="P5">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="Q5">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.67</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2745,46 +2745,46 @@
         <v>284</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>2.38</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>2.6</v>
       </c>
       <c r="I6">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="K6">
-        <v>920</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>2.04</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2987,19 +2987,19 @@
         <v>285</v>
       </c>
       <c r="F7">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
         <v>4.4</v>
@@ -3011,31 +3011,31 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
         <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="T7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W7">
         <v>2.16</v>
@@ -3044,34 +3044,34 @@
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE7">
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -3089,7 +3089,7 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO7">
         <v>1000</v>
@@ -3098,31 +3098,31 @@
         <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS7">
         <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AX7">
         <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ7">
         <v>1.01</v>
@@ -3137,7 +3137,7 @@
         <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE7">
         <v>1.01</v>
@@ -3241,7 +3241,7 @@
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K8">
         <v>900</v>
@@ -3259,13 +3259,13 @@
         <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.48</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
         <v>1.49</v>
@@ -3277,10 +3277,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3483,7 +3483,7 @@
         <v>1.99</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
         <v>4.3</v>
@@ -3713,19 +3713,19 @@
         <v>288</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G10">
         <v>600</v>
       </c>
       <c r="H10">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3749,7 +3749,7 @@
         <v>1.53</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
         <v>1.54</v>
@@ -3761,10 +3761,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3955,46 +3955,46 @@
         <v>289</v>
       </c>
       <c r="F11">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="G11">
         <v>2.08</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="I11">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N11">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="O11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q11">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
         <v>1.22</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -4003,7 +4003,7 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W11">
         <v>1.93</v>
@@ -4197,19 +4197,19 @@
         <v>290</v>
       </c>
       <c r="F12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G12">
         <v>600</v>
       </c>
       <c r="H12">
-        <v>1.42</v>
+        <v>2.72</v>
       </c>
       <c r="I12">
         <v>870</v>
       </c>
       <c r="J12">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -4221,7 +4221,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="O12">
         <v>1.01</v>
@@ -4233,7 +4233,7 @@
         <v>1.27</v>
       </c>
       <c r="R12">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
         <v>1.28</v>
@@ -4245,7 +4245,7 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W12">
         <v>1.4</v>
@@ -4448,7 +4448,7 @@
         <v>3.75</v>
       </c>
       <c r="I13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J13">
         <v>3.35</v>
@@ -4463,13 +4463,13 @@
         <v>1.08</v>
       </c>
       <c r="N13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O13">
         <v>1.35</v>
       </c>
       <c r="P13">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q13">
         <v>2</v>
@@ -4487,7 +4487,7 @@
         <v>2</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
         <v>1.83</v>
@@ -4684,19 +4684,19 @@
         <v>1.12</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>930</v>
       </c>
       <c r="H14">
         <v>1.12</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>930</v>
       </c>
       <c r="J14">
         <v>1.12</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4711,13 +4711,13 @@
         <v>1.02</v>
       </c>
       <c r="P14">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
         <v>1.49</v>
@@ -4729,10 +4729,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4947,7 +4947,7 @@
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15">
         <v>1.11</v>
@@ -4956,7 +4956,7 @@
         <v>3.55</v>
       </c>
       <c r="Q15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R15">
         <v>2.08</v>
@@ -4968,7 +4968,7 @@
         <v>1.4</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V15">
         <v>1.35</v>
@@ -4977,7 +4977,7 @@
         <v>1.99</v>
       </c>
       <c r="X15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y15">
         <v>32</v>
@@ -4989,13 +4989,13 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE15">
         <v>34</v>
@@ -5007,19 +5007,19 @@
         <v>13</v>
       </c>
       <c r="AH15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ15">
         <v>28</v>
       </c>
       <c r="AK15">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM15">
         <v>42</v>
@@ -5028,7 +5028,7 @@
         <v>6.2</v>
       </c>
       <c r="AO15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP15">
         <v>26</v>
@@ -5037,13 +5037,13 @@
         <v>20</v>
       </c>
       <c r="AR15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS15">
         <v>32</v>
       </c>
       <c r="AT15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU15">
         <v>11</v>
@@ -5055,22 +5055,22 @@
         <v>21</v>
       </c>
       <c r="AX15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB15">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
         <v>18.5</v>
@@ -5079,7 +5079,7 @@
         <v>22</v>
       </c>
       <c r="BF15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG15">
         <v>14</v>
@@ -5177,7 +5177,7 @@
         <v>870</v>
       </c>
       <c r="J16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -5201,10 +5201,10 @@
         <v>1.31</v>
       </c>
       <c r="R16">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -5213,10 +5213,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5449,7 +5449,7 @@
         <v>3.3</v>
       </c>
       <c r="T17">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -5661,7 +5661,7 @@
         <v>870</v>
       </c>
       <c r="J18">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5673,34 +5673,34 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="O18">
         <v>1.02</v>
       </c>
       <c r="P18">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
         <v>1.25</v>
       </c>
       <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>1.27</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.11</v>
+      </c>
+      <c r="W18">
         <v>1.09</v>
-      </c>
-      <c r="S18">
-        <v>1.26</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.08</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5894,7 +5894,7 @@
         <v>1.38</v>
       </c>
       <c r="G19">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H19">
         <v>8.800000000000001</v>
@@ -5906,7 +5906,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5942,7 +5942,7 @@
         <v>1.1</v>
       </c>
       <c r="W19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X19">
         <v>24</v>
@@ -5966,7 +5966,7 @@
         <v>36</v>
       </c>
       <c r="AE19">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF19">
         <v>8.4</v>
@@ -6008,7 +6008,7 @@
         <v>7.2</v>
       </c>
       <c r="AS19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT19">
         <v>7.6</v>
@@ -6136,7 +6136,7 @@
         <v>1.86</v>
       </c>
       <c r="G20">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H20">
         <v>4.5</v>
@@ -6157,28 +6157,28 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O20">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P20">
         <v>1.94</v>
       </c>
       <c r="Q20">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
         <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
         <v>1.83</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V20">
         <v>1.25</v>
@@ -6217,7 +6217,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI20">
         <v>75</v>
@@ -6229,7 +6229,7 @@
         <v>20</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM20">
         <v>120</v>
@@ -6247,10 +6247,10 @@
         <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS20">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20">
         <v>7.8</v>
@@ -6262,7 +6262,7 @@
         <v>16</v>
       </c>
       <c r="AW20">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20">
         <v>10</v>
@@ -6274,7 +6274,7 @@
         <v>16</v>
       </c>
       <c r="BA20">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB20">
         <v>19</v>
@@ -6283,16 +6283,16 @@
         <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE20">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20">
         <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6375,22 +6375,22 @@
         <v>299</v>
       </c>
       <c r="F21">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="G21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H21">
         <v>1.43</v>
       </c>
       <c r="I21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J21">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
-        <v>7.8</v>
+        <v>110</v>
       </c>
       <c r="L21">
         <v>1.31</v>
@@ -6423,10 +6423,10 @@
         <v>1.01</v>
       </c>
       <c r="V21">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6620,16 +6620,16 @@
         <v>1.1</v>
       </c>
       <c r="G22">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H22">
         <v>1.1</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J22">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K22">
         <v>950</v>
@@ -6641,22 +6641,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
         <v>1.37</v>
       </c>
       <c r="R22">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6871,7 +6871,7 @@
         <v>4.7</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K23">
         <v>4.3</v>
@@ -6916,7 +6916,7 @@
         <v>20</v>
       </c>
       <c r="Y23">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z23">
         <v>38</v>
@@ -6952,7 +6952,7 @@
         <v>20</v>
       </c>
       <c r="AK23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL23">
         <v>30</v>
@@ -6970,13 +6970,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR23">
         <v>23</v>
       </c>
       <c r="AS23">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AT23">
         <v>10.5</v>
@@ -6988,7 +6988,7 @@
         <v>16</v>
       </c>
       <c r="AW23">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX23">
         <v>11</v>
@@ -7000,7 +7000,7 @@
         <v>15</v>
       </c>
       <c r="BA23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB23">
         <v>17</v>
@@ -7009,10 +7009,10 @@
         <v>15.5</v>
       </c>
       <c r="BD23">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BE23">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF23">
         <v>8.4</v>
@@ -7355,10 +7355,10 @@
         <v>6.4</v>
       </c>
       <c r="J25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L25">
         <v>1.3</v>
@@ -7373,19 +7373,19 @@
         <v>1.25</v>
       </c>
       <c r="P25">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R25">
         <v>1.48</v>
       </c>
       <c r="S25">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T25">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U25">
         <v>2.08</v>
@@ -7394,16 +7394,16 @@
         <v>1.19</v>
       </c>
       <c r="W25">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X25">
         <v>23</v>
       </c>
       <c r="Y25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z25">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA25">
         <v>1000</v>
@@ -7454,7 +7454,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ25">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25">
         <v>29</v>
@@ -7469,10 +7469,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW25">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX25">
         <v>9.199999999999999</v>
@@ -7484,7 +7484,7 @@
         <v>19</v>
       </c>
       <c r="BA25">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB25">
         <v>13.5</v>
@@ -7493,10 +7493,10 @@
         <v>14</v>
       </c>
       <c r="BD25">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BE25">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF25">
         <v>7</v>
@@ -7585,19 +7585,19 @@
         <v>304</v>
       </c>
       <c r="F26">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>2.28</v>
       </c>
       <c r="H26">
-        <v>1.23</v>
+        <v>3.85</v>
       </c>
       <c r="I26">
         <v>110</v>
       </c>
       <c r="J26">
-        <v>1.3</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -7612,7 +7612,7 @@
         <v>1.87</v>
       </c>
       <c r="O26">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P26">
         <v>1.86</v>
@@ -7621,10 +7621,10 @@
         <v>1.33</v>
       </c>
       <c r="R26">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>2.52</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7636,7 +7636,7 @@
         <v>1.06</v>
       </c>
       <c r="W26">
-        <v>1.21</v>
+        <v>1.79</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7827,16 +7827,16 @@
         <v>305</v>
       </c>
       <c r="F27">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G27">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J27">
         <v>3.65</v>
@@ -7848,10 +7848,10 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
         <v>1.34</v>
@@ -7860,7 +7860,7 @@
         <v>1.8</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R27">
         <v>1.29</v>
@@ -7869,13 +7869,13 @@
         <v>3.5</v>
       </c>
       <c r="T27">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U27">
         <v>1.9</v>
       </c>
       <c r="V27">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W27">
         <v>2.02</v>
@@ -7947,7 +7947,7 @@
         <v>1.41</v>
       </c>
       <c r="AT27">
-        <v>6.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU27">
         <v>1.27</v>
@@ -8072,7 +8072,7 @@
         <v>1.1</v>
       </c>
       <c r="G28">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="H28">
         <v>9.199999999999999</v>
@@ -8084,7 +8084,7 @@
         <v>6.8</v>
       </c>
       <c r="K28">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -8105,7 +8105,7 @@
         <v>1.09</v>
       </c>
       <c r="R28">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="S28">
         <v>1.73</v>
@@ -8120,7 +8120,7 @@
         <v>1.01</v>
       </c>
       <c r="W28">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -8326,7 +8326,7 @@
         <v>3.65</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L29">
         <v>1.42</v>
@@ -8356,7 +8356,7 @@
         <v>1.87</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V29">
         <v>2.02</v>
@@ -8365,37 +8365,37 @@
         <v>1.27</v>
       </c>
       <c r="X29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y29">
         <v>12</v>
       </c>
       <c r="Z29">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AA29">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB29">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AC29">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD29">
         <v>17</v>
       </c>
       <c r="AE29">
+        <v>130</v>
+      </c>
+      <c r="AF29">
         <v>110</v>
       </c>
-      <c r="AF29">
-        <v>90</v>
-      </c>
       <c r="AG29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AH29">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI29">
         <v>1000</v>
@@ -8419,7 +8419,7 @@
         <v>40</v>
       </c>
       <c r="AP29">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29">
         <v>6.8</v>
@@ -8428,10 +8428,10 @@
         <v>8.4</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AT29">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU29">
         <v>6.6</v>
@@ -8440,34 +8440,34 @@
         <v>8.4</v>
       </c>
       <c r="AW29">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AX29">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY29">
         <v>13</v>
       </c>
       <c r="AZ29">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA29">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BB29">
         <v>30</v>
       </c>
       <c r="BC29">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BD29">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BE29">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="BF29">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BG29">
         <v>9.800000000000001</v>
@@ -8479,7 +8479,7 @@
         <v>2.66</v>
       </c>
       <c r="BJ29">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="BK29">
         <v>1.01</v>
@@ -8568,7 +8568,7 @@
         <v>4.1</v>
       </c>
       <c r="K30">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8577,16 +8577,16 @@
         <v>1.04</v>
       </c>
       <c r="N30">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P30">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q30">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R30">
         <v>1.62</v>
@@ -8598,7 +8598,7 @@
         <v>1.59</v>
       </c>
       <c r="U30">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V30">
         <v>2</v>
@@ -8607,7 +8607,7 @@
         <v>1.32</v>
       </c>
       <c r="X30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y30">
         <v>15.5</v>
@@ -8685,7 +8685,7 @@
         <v>15.5</v>
       </c>
       <c r="AX30">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="AY30">
         <v>13.5</v>
@@ -8700,13 +8700,13 @@
         <v>29</v>
       </c>
       <c r="BC30">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="BD30">
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BF30">
         <v>21</v>
@@ -8834,7 +8834,7 @@
         <v>1.42</v>
       </c>
       <c r="S31">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T31">
         <v>1.67</v>
@@ -8882,7 +8882,7 @@
         <v>19</v>
       </c>
       <c r="AI31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ31">
         <v>32</v>
@@ -8897,7 +8897,7 @@
         <v>90</v>
       </c>
       <c r="AN31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO31">
         <v>38</v>
@@ -9037,13 +9037,13 @@
         <v>310</v>
       </c>
       <c r="F32">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G32">
         <v>2.02</v>
       </c>
       <c r="H32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I32">
         <v>3.9</v>
@@ -9073,7 +9073,7 @@
         <v>1.62</v>
       </c>
       <c r="R32">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S32">
         <v>2.58</v>
@@ -9088,7 +9088,7 @@
         <v>1.34</v>
       </c>
       <c r="W32">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X32">
         <v>25</v>
@@ -9103,7 +9103,7 @@
         <v>85</v>
       </c>
       <c r="AB32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC32">
         <v>10.5</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="AS32">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -9172,7 +9172,7 @@
         <v>12</v>
       </c>
       <c r="AY32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32">
         <v>14</v>
@@ -9184,19 +9184,19 @@
         <v>18.5</v>
       </c>
       <c r="BC32">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BD32">
         <v>21</v>
       </c>
       <c r="BE32">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF32">
         <v>8.800000000000001</v>
       </c>
       <c r="BG32">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9282,7 +9282,7 @@
         <v>2.06</v>
       </c>
       <c r="G33">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H33">
         <v>3.1</v>
@@ -9306,19 +9306,19 @@
         <v>2.8</v>
       </c>
       <c r="O33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P33">
         <v>2.32</v>
       </c>
       <c r="Q33">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R33">
         <v>1.54</v>
       </c>
       <c r="S33">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="T33">
         <v>1.01</v>
@@ -9327,7 +9327,7 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
         <v>1.74</v>
@@ -9554,7 +9554,7 @@
         <v>1.98</v>
       </c>
       <c r="Q34">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
         <v>1.3</v>
@@ -10005,7 +10005,7 @@
         <v>314</v>
       </c>
       <c r="F36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G36">
         <v>1.51</v>
@@ -10014,13 +10014,13 @@
         <v>6.8</v>
       </c>
       <c r="I36">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J36">
         <v>5.2</v>
       </c>
       <c r="K36">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -10053,7 +10053,7 @@
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36">
         <v>2.96</v>
@@ -10247,22 +10247,22 @@
         <v>315</v>
       </c>
       <c r="F37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G37">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="H37">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="J37">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="K37">
-        <v>870</v>
+        <v>19.5</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -10295,10 +10295,10 @@
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W37">
-        <v>2.58</v>
+        <v>8.4</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -10731,16 +10731,16 @@
         <v>317</v>
       </c>
       <c r="F39">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G39">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H39">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I39">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J39">
         <v>4.1</v>
@@ -10761,28 +10761,28 @@
         <v>1.15</v>
       </c>
       <c r="P39">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
         <v>1.49</v>
       </c>
       <c r="R39">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T39">
         <v>1.46</v>
       </c>
       <c r="U39">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V39">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W39">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X39">
         <v>32</v>
@@ -10821,7 +10821,7 @@
         <v>27</v>
       </c>
       <c r="AJ39">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AK39">
         <v>29</v>
@@ -10854,7 +10854,7 @@
         <v>18.5</v>
       </c>
       <c r="AU39">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV39">
         <v>10.5</v>
@@ -10863,7 +10863,7 @@
         <v>18.5</v>
       </c>
       <c r="AX39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY39">
         <v>12.5</v>
@@ -10872,10 +10872,10 @@
         <v>12.5</v>
       </c>
       <c r="BA39">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BB39">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC39">
         <v>20</v>
@@ -10997,16 +10997,16 @@
         <v>1.03</v>
       </c>
       <c r="N40">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="O40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P40">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q40">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="R40">
         <v>1.74</v>
@@ -11024,7 +11024,7 @@
         <v>1.21</v>
       </c>
       <c r="W40">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X40">
         <v>38</v>
@@ -11072,7 +11072,7 @@
         <v>26</v>
       </c>
       <c r="AM40">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN40">
         <v>6</v>
@@ -11081,13 +11081,13 @@
         <v>44</v>
       </c>
       <c r="AP40">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ40">
         <v>21</v>
       </c>
       <c r="AR40">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AS40">
         <v>8.800000000000001</v>
@@ -11099,7 +11099,7 @@
         <v>10</v>
       </c>
       <c r="AV40">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW40">
         <v>8.199999999999999</v>
@@ -11132,7 +11132,7 @@
         <v>5.4</v>
       </c>
       <c r="BG40">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH40">
         <v>970</v>
@@ -11218,7 +11218,7 @@
         <v>2.44</v>
       </c>
       <c r="G41">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H41">
         <v>3.15</v>
@@ -11227,46 +11227,46 @@
         <v>3.3</v>
       </c>
       <c r="J41">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K41">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L41">
         <v>1.42</v>
       </c>
       <c r="M41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N41">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O41">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P41">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S41">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T41">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U41">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X41">
         <v>14.5</v>
@@ -11275,28 +11275,28 @@
         <v>13.5</v>
       </c>
       <c r="Z41">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA41">
         <v>65</v>
       </c>
       <c r="AB41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC41">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD41">
         <v>16</v>
       </c>
       <c r="AE41">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AF41">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG41">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH41">
         <v>21</v>
@@ -11305,7 +11305,7 @@
         <v>55</v>
       </c>
       <c r="AJ41">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK41">
         <v>30</v>
@@ -11317,64 +11317,64 @@
         <v>110</v>
       </c>
       <c r="AN41">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO41">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP41">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR41">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS41">
         <v>22</v>
       </c>
       <c r="AT41">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU41">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV41">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW41">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AX41">
         <v>13</v>
       </c>
       <c r="AY41">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ41">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA41">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BB41">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BC41">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD41">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="BE41">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF41">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG41">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH41">
         <v>970</v>
@@ -11460,13 +11460,13 @@
         <v>3.3</v>
       </c>
       <c r="G42">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H42">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I42">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J42">
         <v>3.15</v>
@@ -11487,10 +11487,10 @@
         <v>1.35</v>
       </c>
       <c r="P42">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q42">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
         <v>1.3</v>
@@ -11505,10 +11505,10 @@
         <v>2.04</v>
       </c>
       <c r="V42">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W42">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X42">
         <v>14</v>
@@ -11532,7 +11532,7 @@
         <v>12</v>
       </c>
       <c r="AE42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF42">
         <v>25</v>
@@ -11616,7 +11616,7 @@
         <v>36</v>
       </c>
       <c r="BG42">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH42">
         <v>3.9</v>
@@ -11699,22 +11699,22 @@
         <v>321</v>
       </c>
       <c r="F43">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G43">
         <v>2.62</v>
       </c>
       <c r="H43">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I43">
         <v>3.3</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K43">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L43">
         <v>1.35</v>
@@ -11726,19 +11726,19 @@
         <v>3.85</v>
       </c>
       <c r="O43">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P43">
         <v>1.93</v>
       </c>
       <c r="Q43">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R43">
         <v>1.37</v>
       </c>
       <c r="S43">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T43">
         <v>1.73</v>
@@ -11747,97 +11747,97 @@
         <v>2.24</v>
       </c>
       <c r="V43">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y43">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB43">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC43">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE43">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF43">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AG43">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH43">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ43">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK43">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO43">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS43">
         <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU43">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW43">
         <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA43">
         <v>1.01</v>
@@ -11846,7 +11846,7 @@
         <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD43">
         <v>1.01</v>
@@ -11870,7 +11870,7 @@
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL43">
         <v>1000</v>
@@ -11879,7 +11879,7 @@
         <v>1.01</v>
       </c>
       <c r="BN43">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="BO43">
         <v>1.01</v>
@@ -11965,13 +11965,13 @@
         <v>1.04</v>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O44">
         <v>1.2</v>
       </c>
       <c r="P44">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q44">
         <v>1.58</v>
@@ -12013,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="AD44">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE44">
         <v>48</v>
@@ -12022,7 +12022,7 @@
         <v>16</v>
       </c>
       <c r="AG44">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH44">
         <v>19</v>
@@ -12043,34 +12043,34 @@
         <v>70</v>
       </c>
       <c r="AN44">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO44">
         <v>29</v>
       </c>
       <c r="AP44">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ44">
         <v>18.5</v>
       </c>
       <c r="AR44">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS44">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT44">
         <v>12</v>
       </c>
       <c r="AU44">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV44">
         <v>14</v>
       </c>
       <c r="AW44">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -12082,7 +12082,7 @@
         <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB44">
         <v>19.5</v>
@@ -12183,19 +12183,19 @@
         <v>323</v>
       </c>
       <c r="F45">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G45">
         <v>1.66</v>
       </c>
       <c r="H45">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I45">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J45">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K45">
         <v>4.7</v>
@@ -12213,7 +12213,7 @@
         <v>1.16</v>
       </c>
       <c r="P45">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q45">
         <v>1.54</v>
@@ -12222,7 +12222,7 @@
         <v>1.53</v>
       </c>
       <c r="S45">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="T45">
         <v>1.58</v>
@@ -12237,49 +12237,49 @@
         <v>1.01</v>
       </c>
       <c r="X45">
+        <v>110</v>
+      </c>
+      <c r="Y45">
+        <v>110</v>
+      </c>
+      <c r="Z45">
+        <v>180</v>
+      </c>
+      <c r="AA45">
+        <v>1000</v>
+      </c>
+      <c r="AB45">
+        <v>970</v>
+      </c>
+      <c r="AC45">
+        <v>970</v>
+      </c>
+      <c r="AD45">
         <v>95</v>
       </c>
-      <c r="Y45">
-        <v>95</v>
-      </c>
-      <c r="Z45">
-        <v>160</v>
-      </c>
-      <c r="AA45">
-        <v>1000</v>
-      </c>
-      <c r="AB45">
-        <v>25</v>
-      </c>
-      <c r="AC45">
-        <v>12.5</v>
-      </c>
-      <c r="AD45">
-        <v>85</v>
-      </c>
       <c r="AE45">
         <v>1000</v>
       </c>
       <c r="AF45">
+        <v>970</v>
+      </c>
+      <c r="AG45">
         <v>16</v>
       </c>
-      <c r="AG45">
-        <v>12</v>
-      </c>
       <c r="AH45">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45">
         <v>1000</v>
       </c>
       <c r="AJ45">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AK45">
         <v>970</v>
       </c>
       <c r="AL45">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM45">
         <v>1000</v>
@@ -12291,58 +12291,58 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR45">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS45">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AT45">
         <v>10</v>
       </c>
       <c r="AU45">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV45">
         <v>15.5</v>
       </c>
       <c r="AW45">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AX45">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY45">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AZ45">
         <v>10.5</v>
       </c>
       <c r="BA45">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="BB45">
+        <v>11</v>
+      </c>
+      <c r="BC45">
         <v>11.5</v>
       </c>
-      <c r="BC45">
-        <v>10.5</v>
-      </c>
       <c r="BD45">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BE45">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="BF45">
         <v>5.2</v>
       </c>
       <c r="BG45">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="BH45">
         <v>970</v>
@@ -12428,16 +12428,16 @@
         <v>1.36</v>
       </c>
       <c r="G46">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H46">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>990</v>
       </c>
       <c r="J46">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="K46">
         <v>5.3</v>
@@ -12449,7 +12449,7 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="O46">
         <v>1.27</v>
@@ -12458,10 +12458,10 @@
         <v>1.84</v>
       </c>
       <c r="Q46">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="R46">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S46">
         <v>1.01</v>
@@ -12470,13 +12470,13 @@
         <v>1.11</v>
       </c>
       <c r="U46">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="V46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W46">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12909,40 +12909,40 @@
         <v>326</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G48">
         <v>6.4</v>
       </c>
       <c r="H48">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I48">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J48">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K48">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L48">
         <v>1.35</v>
       </c>
       <c r="M48">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N48">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q48">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R48">
         <v>1.24</v>
@@ -12957,16 +12957,16 @@
         <v>1.01</v>
       </c>
       <c r="V48">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X48">
         <v>1000</v>
       </c>
       <c r="Y48">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z48">
         <v>1000</v>
@@ -12978,7 +12978,7 @@
         <v>1000</v>
       </c>
       <c r="AC48">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD48">
         <v>1000</v>
@@ -13017,34 +13017,34 @@
         <v>1000</v>
       </c>
       <c r="AP48">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ48">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR48">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS48">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT48">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU48">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV48">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW48">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX48">
         <v>1.01</v>
       </c>
       <c r="AY48">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ48">
         <v>1.01</v>
@@ -13068,13 +13068,13 @@
         <v>1.01</v>
       </c>
       <c r="BG48">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH48">
         <v>1000</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ48">
         <v>1000</v>
@@ -13110,7 +13110,7 @@
         <v>1000</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV48">
         <v>1000</v>
@@ -13151,22 +13151,22 @@
         <v>327</v>
       </c>
       <c r="F49">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="G49">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H49">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I49">
         <v>3.75</v>
       </c>
       <c r="J49">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K49">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13181,70 +13181,70 @@
         <v>1.21</v>
       </c>
       <c r="P49">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q49">
         <v>1.62</v>
       </c>
       <c r="R49">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S49">
         <v>2.56</v>
       </c>
       <c r="T49">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U49">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W49">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X49">
         <v>27</v>
       </c>
       <c r="Y49">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z49">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA49">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC49">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD49">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE49">
+        <v>42</v>
+      </c>
+      <c r="AF49">
+        <v>17.5</v>
+      </c>
+      <c r="AG49">
+        <v>12.5</v>
+      </c>
+      <c r="AH49">
+        <v>17.5</v>
+      </c>
+      <c r="AI49">
         <v>44</v>
       </c>
-      <c r="AF49">
-        <v>18</v>
-      </c>
-      <c r="AG49">
-        <v>11</v>
-      </c>
-      <c r="AH49">
-        <v>21</v>
-      </c>
-      <c r="AI49">
-        <v>50</v>
-      </c>
       <c r="AJ49">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AK49">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL49">
         <v>38</v>
@@ -13253,7 +13253,7 @@
         <v>85</v>
       </c>
       <c r="AN49">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO49">
         <v>34</v>
@@ -13262,43 +13262,43 @@
         <v>18</v>
       </c>
       <c r="AQ49">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR49">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS49">
         <v>1.01</v>
       </c>
       <c r="AT49">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU49">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW49">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AX49">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY49">
         <v>9.6</v>
       </c>
       <c r="AZ49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA49">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB49">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC49">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BD49">
         <v>1.01</v>
@@ -13307,10 +13307,10 @@
         <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG49">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13423,7 +13423,7 @@
         <v>1.14</v>
       </c>
       <c r="P50">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q50">
         <v>1.45</v>
@@ -13483,7 +13483,7 @@
         <v>85</v>
       </c>
       <c r="AJ50">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK50">
         <v>14.5</v>
@@ -13635,22 +13635,22 @@
         <v>329</v>
       </c>
       <c r="F51">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G51">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H51">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I51">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J51">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K51">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13659,121 +13659,121 @@
         <v>1.05</v>
       </c>
       <c r="N51">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O51">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P51">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q51">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R51">
         <v>1.51</v>
       </c>
       <c r="S51">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T51">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W51">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X51">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y51">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z51">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA51">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB51">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC51">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD51">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE51">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF51">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG51">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH51">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI51">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ51">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK51">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL51">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM51">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN51">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO51">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP51">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ51">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR51">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS51">
         <v>1.01</v>
       </c>
       <c r="AT51">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU51">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV51">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW51">
         <v>1.01</v>
       </c>
       <c r="AX51">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY51">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ51">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA51">
         <v>1.01</v>
@@ -13782,7 +13782,7 @@
         <v>1.01</v>
       </c>
       <c r="BC51">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD51">
         <v>1.01</v>
@@ -13791,10 +13791,10 @@
         <v>1.01</v>
       </c>
       <c r="BF51">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG51">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13883,13 +13883,13 @@
         <v>2.74</v>
       </c>
       <c r="H52">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I52">
         <v>2.76</v>
       </c>
       <c r="J52">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K52">
         <v>5.1</v>
@@ -13904,10 +13904,10 @@
         <v>6.4</v>
       </c>
       <c r="O52">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P52">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Q52">
         <v>1.4</v>
@@ -13916,13 +13916,13 @@
         <v>1.79</v>
       </c>
       <c r="S52">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="T52">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U52">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V52">
         <v>1.56</v>
@@ -14119,10 +14119,10 @@
         <v>331</v>
       </c>
       <c r="F53">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G53">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H53">
         <v>3.35</v>
@@ -14134,43 +14134,43 @@
         <v>4.3</v>
       </c>
       <c r="K53">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L53">
         <v>1.01</v>
       </c>
       <c r="M53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N53">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P53">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R53">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S53">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T53">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="U53">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V53">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W53">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X53">
         <v>1000</v>
@@ -14221,7 +14221,7 @@
         <v>1000</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO53">
         <v>1000</v>
@@ -14275,7 +14275,7 @@
         <v>1.01</v>
       </c>
       <c r="BF53">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG53">
         <v>1.01</v>
@@ -14373,7 +14373,7 @@
         <v>6</v>
       </c>
       <c r="J54">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K54">
         <v>5.4</v>
@@ -14385,10 +14385,10 @@
         <v>1.02</v>
       </c>
       <c r="N54">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="O54">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P54">
         <v>2.3</v>
@@ -14400,7 +14400,7 @@
         <v>1.52</v>
       </c>
       <c r="S54">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T54">
         <v>1.57</v>
@@ -14409,7 +14409,7 @@
         <v>2.24</v>
       </c>
       <c r="V54">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W54">
         <v>2.16</v>
@@ -14603,22 +14603,22 @@
         <v>333</v>
       </c>
       <c r="F55">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G55">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H55">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I55">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J55">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K55">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14642,7 +14642,7 @@
         <v>1.3</v>
       </c>
       <c r="S55">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T55">
         <v>1.73</v>
@@ -14651,13 +14651,13 @@
         <v>1.99</v>
       </c>
       <c r="V55">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X55">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y55">
         <v>16.5</v>
@@ -14711,28 +14711,28 @@
         <v>60</v>
       </c>
       <c r="AP55">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="AQ55">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR55">
         <v>16</v>
       </c>
       <c r="AS55">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AT55">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AU55">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV55">
         <v>9.6</v>
       </c>
       <c r="AW55">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AX55">
         <v>9.199999999999999</v>
@@ -14741,10 +14741,10 @@
         <v>7.2</v>
       </c>
       <c r="AZ55">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA55">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BB55">
         <v>18</v>
@@ -14753,16 +14753,16 @@
         <v>15</v>
       </c>
       <c r="BD55">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BE55">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF55">
         <v>11.5</v>
       </c>
       <c r="BG55">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14848,7 +14848,7 @@
         <v>2.3</v>
       </c>
       <c r="G56">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H56">
         <v>3.2</v>
@@ -14857,10 +14857,10 @@
         <v>3.4</v>
       </c>
       <c r="J56">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -14872,19 +14872,19 @@
         <v>3.9</v>
       </c>
       <c r="O56">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P56">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="R56">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S56">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T56">
         <v>1.64</v>
@@ -14911,10 +14911,10 @@
         <v>1000</v>
       </c>
       <c r="AB56">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AC56">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD56">
         <v>970</v>
@@ -14923,10 +14923,10 @@
         <v>1000</v>
       </c>
       <c r="AF56">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG56">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AH56">
         <v>90</v>
@@ -14953,16 +14953,16 @@
         <v>1000</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="AR56">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AS56">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AT56">
         <v>9</v>
@@ -14971,40 +14971,40 @@
         <v>6.2</v>
       </c>
       <c r="AV56">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AW56">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AX56">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AY56">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AZ56">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="BA56">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BB56">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BC56">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BD56">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BE56">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="BF56">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="BG56">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -15087,10 +15087,10 @@
         <v>335</v>
       </c>
       <c r="F57">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G57">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H57">
         <v>4.3</v>
@@ -15099,10 +15099,10 @@
         <v>4.8</v>
       </c>
       <c r="J57">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K57">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -15111,7 +15111,7 @@
         <v>1.06</v>
       </c>
       <c r="N57">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O57">
         <v>1.29</v>
@@ -15120,7 +15120,7 @@
         <v>2</v>
       </c>
       <c r="Q57">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R57">
         <v>1.41</v>
@@ -15129,7 +15129,7 @@
         <v>3.1</v>
       </c>
       <c r="T57">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U57">
         <v>2.12</v>
@@ -15138,7 +15138,7 @@
         <v>1.27</v>
       </c>
       <c r="W57">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X57">
         <v>20</v>
@@ -15180,7 +15180,7 @@
         <v>23</v>
       </c>
       <c r="AK57">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL57">
         <v>40</v>
@@ -15201,10 +15201,10 @@
         <v>14.5</v>
       </c>
       <c r="AR57">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS57">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT57">
         <v>8.4</v>
@@ -15228,19 +15228,19 @@
         <v>15.5</v>
       </c>
       <c r="BA57">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB57">
         <v>18</v>
       </c>
       <c r="BC57">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD57">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE57">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF57">
         <v>10</v>
@@ -15335,13 +15335,13 @@
         <v>1.71</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I58">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J58">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K58">
         <v>4.8</v>
@@ -15356,10 +15356,10 @@
         <v>6.6</v>
       </c>
       <c r="O58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P58">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q58">
         <v>1.46</v>
@@ -15368,7 +15368,7 @@
         <v>1.8</v>
       </c>
       <c r="S58">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T58">
         <v>1.54</v>
@@ -15377,7 +15377,7 @@
         <v>2.68</v>
       </c>
       <c r="V58">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W58">
         <v>2.4</v>
@@ -15401,7 +15401,7 @@
         <v>12</v>
       </c>
       <c r="AD58">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE58">
         <v>70</v>
@@ -15431,22 +15431,22 @@
         <v>65</v>
       </c>
       <c r="AN58">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO58">
         <v>38</v>
       </c>
       <c r="AP58">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ58">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR58">
         <v>7.6</v>
       </c>
       <c r="AS58">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT58">
         <v>13</v>
@@ -15458,7 +15458,7 @@
         <v>18.5</v>
       </c>
       <c r="AW58">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX58">
         <v>12.5</v>
@@ -15470,7 +15470,7 @@
         <v>14</v>
       </c>
       <c r="BA58">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB58">
         <v>16</v>
@@ -15488,7 +15488,7 @@
         <v>5.2</v>
       </c>
       <c r="BG58">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -15580,13 +15580,13 @@
         <v>3.45</v>
       </c>
       <c r="I59">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J59">
         <v>3.25</v>
       </c>
       <c r="K59">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L59">
         <v>1.44</v>
@@ -15601,7 +15601,7 @@
         <v>1.39</v>
       </c>
       <c r="P59">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q59">
         <v>2.12</v>
@@ -15610,7 +15610,7 @@
         <v>1.25</v>
       </c>
       <c r="S59">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T59">
         <v>1.82</v>
@@ -15622,13 +15622,13 @@
         <v>1.37</v>
       </c>
       <c r="W59">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X59">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y59">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z59">
         <v>29</v>
@@ -15637,10 +15637,10 @@
         <v>90</v>
       </c>
       <c r="AB59">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC59">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD59">
         <v>18.5</v>
@@ -15649,7 +15649,7 @@
         <v>60</v>
       </c>
       <c r="AF59">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG59">
         <v>13.5</v>
@@ -15667,7 +15667,7 @@
         <v>36</v>
       </c>
       <c r="AL59">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM59">
         <v>1000</v>
@@ -15688,19 +15688,19 @@
         <v>5</v>
       </c>
       <c r="AS59">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT59">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AU59">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV59">
         <v>11</v>
       </c>
       <c r="AW59">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX59">
         <v>10.5</v>
@@ -15712,25 +15712,25 @@
         <v>13.5</v>
       </c>
       <c r="BA59">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BB59">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC59">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD59">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BE59">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BF59">
+        <v>4.3</v>
+      </c>
+      <c r="BG59">
         <v>4.6</v>
-      </c>
-      <c r="BG59">
-        <v>5</v>
       </c>
       <c r="BH59">
         <v>970</v>
@@ -15819,7 +15819,7 @@
         <v>2.44</v>
       </c>
       <c r="H60">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I60">
         <v>3.35</v>
@@ -15828,7 +15828,7 @@
         <v>3.5</v>
       </c>
       <c r="K60">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15855,7 +15855,7 @@
         <v>2.8</v>
       </c>
       <c r="T60">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U60">
         <v>2.16</v>
@@ -15891,7 +15891,7 @@
         <v>48</v>
       </c>
       <c r="AF60">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG60">
         <v>12</v>
@@ -15927,13 +15927,13 @@
         <v>12</v>
       </c>
       <c r="AR60">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AS60">
         <v>32</v>
       </c>
       <c r="AT60">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU60">
         <v>7.4</v>
@@ -15954,7 +15954,7 @@
         <v>14.5</v>
       </c>
       <c r="BA60">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB60">
         <v>23</v>
@@ -15966,10 +15966,10 @@
         <v>25</v>
       </c>
       <c r="BE60">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF60">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG60">
         <v>18.5</v>
@@ -16055,10 +16055,10 @@
         <v>339</v>
       </c>
       <c r="F61">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G61">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H61">
         <v>6</v>
@@ -16070,7 +16070,7 @@
         <v>3.6</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -16297,7 +16297,7 @@
         <v>340</v>
       </c>
       <c r="F62">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G62">
         <v>2.48</v>
@@ -16321,13 +16321,13 @@
         <v>1.09</v>
       </c>
       <c r="N62">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O62">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P62">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q62">
         <v>2.22</v>
@@ -16345,7 +16345,7 @@
         <v>1.97</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
         <v>1.67</v>
@@ -16357,7 +16357,7 @@
         <v>11.5</v>
       </c>
       <c r="Z62">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA62">
         <v>80</v>
@@ -16411,10 +16411,10 @@
         <v>10</v>
       </c>
       <c r="AR62">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS62">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT62">
         <v>7.8</v>
@@ -16438,7 +16438,7 @@
         <v>17</v>
       </c>
       <c r="BA62">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB62">
         <v>21</v>
@@ -16545,10 +16545,10 @@
         <v>3.05</v>
       </c>
       <c r="H63">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I63">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="J63">
         <v>3.55</v>
@@ -16563,16 +16563,16 @@
         <v>1.02</v>
       </c>
       <c r="N63">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O63">
         <v>1.09</v>
       </c>
       <c r="P63">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Q63">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R63">
         <v>1.9</v>
@@ -16584,13 +16584,13 @@
         <v>1.33</v>
       </c>
       <c r="U63">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V63">
         <v>1.6</v>
       </c>
       <c r="W63">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16611,7 +16611,7 @@
         <v>24</v>
       </c>
       <c r="AD63">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE63">
         <v>1000</v>
@@ -16620,10 +16620,10 @@
         <v>1000</v>
       </c>
       <c r="AG63">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AH63">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI63">
         <v>1000</v>
@@ -16790,13 +16790,13 @@
         <v>1.98</v>
       </c>
       <c r="I64">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J64">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L64">
         <v>1.01</v>
@@ -16805,13 +16805,13 @@
         <v>1.02</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O64">
         <v>1.25</v>
       </c>
       <c r="P64">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q64">
         <v>1.83</v>
@@ -16823,7 +16823,7 @@
         <v>2.94</v>
       </c>
       <c r="T64">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U64">
         <v>2.1</v>
@@ -17023,58 +17023,58 @@
         <v>343</v>
       </c>
       <c r="F65">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H65">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I65">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J65">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K65">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L65">
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N65">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="O65">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P65">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q65">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R65">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S65">
         <v>2.16</v>
       </c>
       <c r="T65">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U65">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="V65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W65">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X65">
         <v>1000</v>
@@ -17092,10 +17092,10 @@
         <v>1000</v>
       </c>
       <c r="AC65">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD65">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE65">
         <v>1000</v>
@@ -17104,10 +17104,10 @@
         <v>1000</v>
       </c>
       <c r="AG65">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AH65">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI65">
         <v>1000</v>
@@ -17128,7 +17128,7 @@
         <v>1000</v>
       </c>
       <c r="AO65">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP65">
         <v>1.01</v>
@@ -17295,16 +17295,16 @@
         <v>1.01</v>
       </c>
       <c r="P66">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q66">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="R66">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S66">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="T66">
         <v>1.01</v>
@@ -17510,7 +17510,7 @@
         <v>2.52</v>
       </c>
       <c r="G67">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H67">
         <v>2.6</v>
@@ -17764,7 +17764,7 @@
         <v>4.4</v>
       </c>
       <c r="K68">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17773,22 +17773,22 @@
         <v>1.02</v>
       </c>
       <c r="N68">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="O68">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P68">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="Q68">
         <v>1.39</v>
       </c>
       <c r="R68">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S68">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="T68">
         <v>1.42</v>
@@ -17851,64 +17851,64 @@
         <v>1000</v>
       </c>
       <c r="AN68">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AO68">
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AQ68">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR68">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS68">
         <v>1.01</v>
       </c>
       <c r="AT68">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU68">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV68">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW68">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AX68">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY68">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ68">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA68">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB68">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC68">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD68">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE68">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF68">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG68">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -18000,7 +18000,7 @@
         <v>2.14</v>
       </c>
       <c r="I69">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J69">
         <v>3.95</v>
@@ -18030,7 +18030,7 @@
         <v>1.66</v>
       </c>
       <c r="S69">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T69">
         <v>1.43</v>
@@ -18039,7 +18039,7 @@
         <v>2.62</v>
       </c>
       <c r="V69">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W69">
         <v>1.4</v>
@@ -18236,13 +18236,13 @@
         <v>3.15</v>
       </c>
       <c r="G70">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H70">
         <v>2.02</v>
       </c>
       <c r="I70">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J70">
         <v>4.3</v>
@@ -18257,7 +18257,7 @@
         <v>1.02</v>
       </c>
       <c r="N70">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O70">
         <v>1.11</v>
@@ -18269,22 +18269,22 @@
         <v>1.34</v>
       </c>
       <c r="R70">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S70">
         <v>1.85</v>
       </c>
       <c r="T70">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U70">
         <v>3.2</v>
       </c>
       <c r="V70">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W70">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X70">
         <v>55</v>
@@ -18475,10 +18475,10 @@
         <v>349</v>
       </c>
       <c r="F71">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G71">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H71">
         <v>4.5</v>
@@ -18490,7 +18490,7 @@
         <v>4.3</v>
       </c>
       <c r="K71">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L71">
         <v>1.01</v>
@@ -18499,19 +18499,19 @@
         <v>1.03</v>
       </c>
       <c r="N71">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O71">
         <v>1.17</v>
       </c>
       <c r="P71">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q71">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R71">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S71">
         <v>2.28</v>
@@ -18520,73 +18520,73 @@
         <v>1.58</v>
       </c>
       <c r="U71">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V71">
         <v>1.23</v>
       </c>
       <c r="W71">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X71">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y71">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z71">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA71">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB71">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC71">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD71">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE71">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF71">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG71">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH71">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI71">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ71">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK71">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL71">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM71">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO71">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP71">
         <v>1.01</v>
       </c>
       <c r="AQ71">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR71">
         <v>1.01</v>
@@ -18595,43 +18595,43 @@
         <v>1.01</v>
       </c>
       <c r="AT71">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU71">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV71">
+        <v>16.5</v>
+      </c>
+      <c r="AW71">
+        <v>1.01</v>
+      </c>
+      <c r="AX71">
+        <v>11.5</v>
+      </c>
+      <c r="AY71">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV71">
-        <v>1.01</v>
-      </c>
-      <c r="AW71">
-        <v>1.01</v>
-      </c>
-      <c r="AX71">
-        <v>11</v>
-      </c>
-      <c r="AY71">
-        <v>8.6</v>
-      </c>
       <c r="AZ71">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA71">
         <v>1.01</v>
       </c>
       <c r="BB71">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC71">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD71">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BE71">
         <v>1.01</v>
       </c>
       <c r="BF71">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG71">
         <v>1.01</v>
@@ -18723,10 +18723,10 @@
         <v>2.6</v>
       </c>
       <c r="H72">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I72">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J72">
         <v>4</v>
@@ -18741,28 +18741,28 @@
         <v>1.03</v>
       </c>
       <c r="N72">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="O72">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P72">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q72">
         <v>1.48</v>
       </c>
       <c r="R72">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S72">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="T72">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="U72">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="V72">
         <v>1.54</v>
@@ -18771,112 +18771,112 @@
         <v>1.62</v>
       </c>
       <c r="X72">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y72">
+        <v>20</v>
+      </c>
+      <c r="Z72">
+        <v>25</v>
+      </c>
+      <c r="AA72">
+        <v>48</v>
+      </c>
+      <c r="AB72">
+        <v>19</v>
+      </c>
+      <c r="AC72">
+        <v>12.5</v>
+      </c>
+      <c r="AD72">
+        <v>14</v>
+      </c>
+      <c r="AE72">
         <v>26</v>
       </c>
-      <c r="Z72">
-        <v>34</v>
-      </c>
-      <c r="AA72">
+      <c r="AF72">
+        <v>22</v>
+      </c>
+      <c r="AG72">
+        <v>13</v>
+      </c>
+      <c r="AH72">
+        <v>15</v>
+      </c>
+      <c r="AI72">
+        <v>29</v>
+      </c>
+      <c r="AJ72">
+        <v>36</v>
+      </c>
+      <c r="AK72">
+        <v>23</v>
+      </c>
+      <c r="AL72">
+        <v>27</v>
+      </c>
+      <c r="AM72">
         <v>55</v>
       </c>
-      <c r="AB72">
-        <v>25</v>
-      </c>
-      <c r="AC72">
-        <v>15</v>
-      </c>
-      <c r="AD72">
-        <v>18.5</v>
-      </c>
-      <c r="AE72">
-        <v>34</v>
-      </c>
-      <c r="AF72">
-        <v>30</v>
-      </c>
-      <c r="AG72">
-        <v>17.5</v>
-      </c>
-      <c r="AH72">
-        <v>19</v>
-      </c>
-      <c r="AI72">
-        <v>40</v>
-      </c>
-      <c r="AJ72">
-        <v>48</v>
-      </c>
-      <c r="AK72">
-        <v>30</v>
-      </c>
-      <c r="AL72">
-        <v>38</v>
-      </c>
-      <c r="AM72">
-        <v>65</v>
-      </c>
       <c r="AN72">
+        <v>11.5</v>
+      </c>
+      <c r="AO72">
+        <v>13.5</v>
+      </c>
+      <c r="AP72">
+        <v>1.01</v>
+      </c>
+      <c r="AQ72">
+        <v>17</v>
+      </c>
+      <c r="AR72">
+        <v>1.01</v>
+      </c>
+      <c r="AS72">
+        <v>1.01</v>
+      </c>
+      <c r="AT72">
         <v>16</v>
       </c>
-      <c r="AO72">
-        <v>18</v>
-      </c>
-      <c r="AP72">
-        <v>1.01</v>
-      </c>
-      <c r="AQ72">
-        <v>14</v>
-      </c>
-      <c r="AR72">
-        <v>15</v>
-      </c>
-      <c r="AS72">
-        <v>1.01</v>
-      </c>
-      <c r="AT72">
-        <v>13</v>
-      </c>
       <c r="AU72">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AV72">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW72">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AX72">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY72">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ72">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA72">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB72">
         <v>1.01</v>
       </c>
       <c r="BC72">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD72">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE72">
         <v>1.01</v>
       </c>
       <c r="BF72">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG72">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -18959,22 +18959,22 @@
         <v>351</v>
       </c>
       <c r="F73">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G73">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="H73">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I73">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J73">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K73">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -18983,34 +18983,34 @@
         <v>1.02</v>
       </c>
       <c r="N73">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O73">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P73">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q73">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R73">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S73">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="T73">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="U73">
         <v>2.56</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -19207,13 +19207,13 @@
         <v>1.09</v>
       </c>
       <c r="H74">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I74">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J74">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="K74">
         <v>21</v>
@@ -19225,34 +19225,34 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O74">
         <v>1.04</v>
       </c>
       <c r="P74">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q74">
         <v>1.15</v>
       </c>
       <c r="R74">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="S74">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T74">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U74">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V74">
         <v>1.02</v>
       </c>
       <c r="W74">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X74">
         <v>140</v>
@@ -19279,10 +19279,10 @@
         <v>480</v>
       </c>
       <c r="AF74">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG74">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH74">
         <v>70</v>
@@ -19297,13 +19297,13 @@
         <v>15.5</v>
       </c>
       <c r="AL74">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM74">
         <v>1000</v>
       </c>
       <c r="AN74">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AO74">
         <v>340</v>
@@ -19312,40 +19312,40 @@
         <v>100</v>
       </c>
       <c r="AQ74">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AR74">
         <v>100</v>
       </c>
       <c r="AS74">
-        <v>100</v>
+        <v>19.5</v>
       </c>
       <c r="AT74">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AU74">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV74">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AW74">
         <v>100</v>
       </c>
       <c r="AX74">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY74">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ74">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BA74">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="BB74">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC74">
         <v>13.5</v>
@@ -19357,7 +19357,7 @@
         <v>46</v>
       </c>
       <c r="BF74">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="BG74">
         <v>100</v>
@@ -19446,13 +19446,13 @@
         <v>1.7</v>
       </c>
       <c r="G75">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H75">
         <v>4.9</v>
       </c>
       <c r="I75">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J75">
         <v>4.2</v>
@@ -19494,7 +19494,7 @@
         <v>1.23</v>
       </c>
       <c r="W75">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X75">
         <v>30</v>
@@ -19688,7 +19688,7 @@
         <v>3.35</v>
       </c>
       <c r="G76">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H76">
         <v>2.18</v>
@@ -19700,7 +19700,7 @@
         <v>3.2</v>
       </c>
       <c r="K76">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L76">
         <v>1.34</v>
@@ -19718,16 +19718,16 @@
         <v>1.75</v>
       </c>
       <c r="Q76">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R76">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S76">
         <v>3.65</v>
       </c>
       <c r="T76">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U76">
         <v>1.92</v>
@@ -19927,19 +19927,19 @@
         <v>355</v>
       </c>
       <c r="F77">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G77">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H77">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I77">
         <v>3.05</v>
       </c>
       <c r="J77">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K77">
         <v>3.85</v>
@@ -19975,10 +19975,10 @@
         <v>2.28</v>
       </c>
       <c r="V77">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X77">
         <v>17.5</v>
@@ -20017,10 +20017,10 @@
         <v>42</v>
       </c>
       <c r="AJ77">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK77">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL77">
         <v>38</v>
@@ -20029,7 +20029,7 @@
         <v>95</v>
       </c>
       <c r="AN77">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO77">
         <v>27</v>
@@ -20038,10 +20038,10 @@
         <v>15</v>
       </c>
       <c r="AQ77">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR77">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS77">
         <v>36</v>
@@ -20083,7 +20083,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF77">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG77">
         <v>21</v>
@@ -20169,13 +20169,13 @@
         <v>356</v>
       </c>
       <c r="F78">
+        <v>2.32</v>
+      </c>
+      <c r="G78">
         <v>2.34</v>
       </c>
-      <c r="G78">
-        <v>2.38</v>
-      </c>
       <c r="H78">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I78">
         <v>3.55</v>
@@ -20220,7 +20220,7 @@
         <v>1.39</v>
       </c>
       <c r="W78">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X78">
         <v>13</v>
@@ -20247,7 +20247,7 @@
         <v>44</v>
       </c>
       <c r="AF78">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG78">
         <v>11.5</v>
@@ -20289,7 +20289,7 @@
         <v>50</v>
       </c>
       <c r="AT78">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU78">
         <v>7.2</v>
@@ -20322,7 +20322,7 @@
         <v>36</v>
       </c>
       <c r="BE78">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF78">
         <v>18</v>
@@ -20411,13 +20411,13 @@
         <v>357</v>
       </c>
       <c r="F79">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G79">
         <v>110</v>
       </c>
       <c r="H79">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I79">
         <v>110</v>
@@ -20435,22 +20435,22 @@
         <v>1.01</v>
       </c>
       <c r="N79">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="O79">
         <v>1.2</v>
       </c>
       <c r="P79">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Q79">
         <v>1.2</v>
       </c>
       <c r="R79">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S79">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
         <v>1.01</v>
@@ -20653,7 +20653,7 @@
         <v>358</v>
       </c>
       <c r="F80">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G80">
         <v>2.52</v>
@@ -20665,13 +20665,13 @@
         <v>3.2</v>
       </c>
       <c r="J80">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K80">
         <v>4.5</v>
       </c>
       <c r="L80">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M80">
         <v>1.05</v>
@@ -20680,7 +20680,7 @@
         <v>4.4</v>
       </c>
       <c r="O80">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P80">
         <v>2.2</v>
@@ -20689,7 +20689,7 @@
         <v>1.67</v>
       </c>
       <c r="R80">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S80">
         <v>2.62</v>
@@ -20704,7 +20704,7 @@
         <v>1.46</v>
       </c>
       <c r="W80">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X80">
         <v>1000</v>
@@ -20755,7 +20755,7 @@
         <v>1000</v>
       </c>
       <c r="AN80">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO80">
         <v>1000</v>
@@ -20818,61 +20818,61 @@
         <v>970</v>
       </c>
       <c r="BI80">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="BJ80">
         <v>1000</v>
       </c>
       <c r="BK80">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="BL80">
         <v>1000</v>
       </c>
       <c r="BM80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BN80">
         <v>970</v>
       </c>
       <c r="BO80">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="BP80">
         <v>1000</v>
       </c>
       <c r="BQ80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BR80">
         <v>1000</v>
       </c>
       <c r="BS80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BT80">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU80">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BV80">
         <v>1000</v>
       </c>
       <c r="BW80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BX80">
         <v>1000</v>
       </c>
       <c r="BY80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BZ80">
         <v>1000</v>
       </c>
       <c r="CA80">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="CB80" t="s">
         <v>389</v>
@@ -20919,19 +20919,19 @@
         <v>1.01</v>
       </c>
       <c r="N81">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="O81">
         <v>1.01</v>
       </c>
       <c r="P81">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q81">
         <v>1.29</v>
       </c>
       <c r="R81">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S81">
         <v>1.29</v>
@@ -20943,10 +20943,10 @@
         <v>1.01</v>
       </c>
       <c r="V81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1000</v>
@@ -21137,10 +21137,10 @@
         <v>360</v>
       </c>
       <c r="F82">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G82">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H82">
         <v>1.12</v>
@@ -21149,7 +21149,7 @@
         <v>110</v>
       </c>
       <c r="J82">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="K82">
         <v>890</v>
@@ -21158,25 +21158,25 @@
         <v>1.01</v>
       </c>
       <c r="M82">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N82">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O82">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P82">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="Q82">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="R82">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="S82">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="T82">
         <v>1.01</v>
@@ -21185,7 +21185,7 @@
         <v>1.01</v>
       </c>
       <c r="V82">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W82">
         <v>1.05</v>
@@ -21403,13 +21403,13 @@
         <v>1.01</v>
       </c>
       <c r="N83">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O83">
         <v>1.01</v>
       </c>
       <c r="P83">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Q83">
         <v>1.33</v>
@@ -21624,19 +21624,19 @@
         <v>2.74</v>
       </c>
       <c r="G84">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H84">
         <v>2.4</v>
       </c>
       <c r="I84">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J84">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K84">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L84">
         <v>1.01</v>
@@ -21669,7 +21669,7 @@
         <v>1.01</v>
       </c>
       <c r="V84">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W84">
         <v>1.45</v>
@@ -21869,10 +21869,10 @@
         <v>3.3</v>
       </c>
       <c r="H85">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I85">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J85">
         <v>3.55</v>
@@ -21911,13 +21911,13 @@
         <v>2.34</v>
       </c>
       <c r="V85">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
         <v>1.43</v>
       </c>
       <c r="X85">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y85">
         <v>11.5</v>
@@ -21938,7 +21938,7 @@
         <v>11.5</v>
       </c>
       <c r="AE85">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF85">
         <v>23</v>
@@ -21968,7 +21968,7 @@
         <v>30</v>
       </c>
       <c r="AO85">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP85">
         <v>14</v>
@@ -22034,7 +22034,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK85">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL85">
         <v>120</v>
@@ -22105,7 +22105,7 @@
         <v>364</v>
       </c>
       <c r="F86">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G86">
         <v>2.02</v>
@@ -22114,13 +22114,13 @@
         <v>3.95</v>
       </c>
       <c r="I86">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J86">
         <v>3.45</v>
       </c>
       <c r="K86">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L86">
         <v>1.01</v>
@@ -22129,7 +22129,7 @@
         <v>1.02</v>
       </c>
       <c r="N86">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O86">
         <v>1.21</v>
@@ -22141,7 +22141,7 @@
         <v>1.71</v>
       </c>
       <c r="R86">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S86">
         <v>2.78</v>
@@ -22183,7 +22183,7 @@
         <v>1000</v>
       </c>
       <c r="AF86">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG86">
         <v>970</v>
@@ -22198,7 +22198,7 @@
         <v>1000</v>
       </c>
       <c r="AK86">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL86">
         <v>1000</v>
@@ -22267,7 +22267,7 @@
         <v>1.01</v>
       </c>
       <c r="BH86">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI86">
         <v>1.01</v>
@@ -22285,7 +22285,7 @@
         <v>1.01</v>
       </c>
       <c r="BN86">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO86">
         <v>1.01</v>
@@ -22347,58 +22347,58 @@
         <v>365</v>
       </c>
       <c r="F87">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="G87">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="H87">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I87">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J87">
         <v>5.2</v>
       </c>
       <c r="K87">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="L87">
         <v>1.01</v>
       </c>
       <c r="M87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N87">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="O87">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P87">
         <v>2.46</v>
       </c>
       <c r="Q87">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R87">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S87">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="T87">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U87">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V87">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W87">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="X87">
         <v>1000</v>
@@ -22598,10 +22598,10 @@
         <v>3.15</v>
       </c>
       <c r="I88">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J88">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K88">
         <v>3.85</v>
@@ -22616,19 +22616,19 @@
         <v>3.6</v>
       </c>
       <c r="O88">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P88">
+        <v>1.83</v>
+      </c>
+      <c r="Q88">
         <v>1.92</v>
-      </c>
-      <c r="Q88">
-        <v>1.91</v>
       </c>
       <c r="R88">
         <v>1.31</v>
       </c>
       <c r="S88">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T88">
         <v>1.71</v>
@@ -22834,19 +22834,19 @@
         <v>1.55</v>
       </c>
       <c r="G89">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="H89">
         <v>5.7</v>
       </c>
       <c r="I89">
-        <v>9.800000000000001</v>
+        <v>870</v>
       </c>
       <c r="J89">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K89">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L89">
         <v>1.01</v>
@@ -22855,7 +22855,7 @@
         <v>1.01</v>
       </c>
       <c r="N89">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="O89">
         <v>1.15</v>
@@ -22882,7 +22882,7 @@
         <v>1.17</v>
       </c>
       <c r="W89">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X89">
         <v>1000</v>
@@ -23079,10 +23079,10 @@
         <v>4.8</v>
       </c>
       <c r="H90">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I90">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J90">
         <v>3.75</v>
@@ -23333,34 +23333,34 @@
         <v>3.95</v>
       </c>
       <c r="L91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M91">
         <v>1.04</v>
       </c>
       <c r="N91">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O91">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P91">
         <v>2.56</v>
       </c>
       <c r="Q91">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R91">
         <v>1.63</v>
       </c>
       <c r="S91">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T91">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U91">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V91">
         <v>1.37</v>
@@ -23372,7 +23372,7 @@
         <v>23</v>
       </c>
       <c r="Y91">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z91">
         <v>30</v>
@@ -23420,7 +23420,7 @@
         <v>10.5</v>
       </c>
       <c r="AO91">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP91">
         <v>21</v>
@@ -23465,13 +23465,13 @@
         <v>17</v>
       </c>
       <c r="BD91">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BE91">
         <v>48</v>
       </c>
       <c r="BF91">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG91">
         <v>21</v>
@@ -23557,19 +23557,19 @@
         <v>370</v>
       </c>
       <c r="F92">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G92">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H92">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I92">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J92">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K92">
         <v>4.1</v>
@@ -23581,16 +23581,16 @@
         <v>1.05</v>
       </c>
       <c r="N92">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O92">
         <v>1.22</v>
       </c>
       <c r="P92">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q92">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R92">
         <v>1.45</v>
@@ -23599,7 +23599,7 @@
         <v>2.62</v>
       </c>
       <c r="T92">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U92">
         <v>2.28</v>
@@ -23608,7 +23608,7 @@
         <v>1.37</v>
       </c>
       <c r="W92">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X92">
         <v>1000</v>
@@ -23623,7 +23623,7 @@
         <v>1000</v>
       </c>
       <c r="AB92">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC92">
         <v>970</v>
@@ -23638,7 +23638,7 @@
         <v>1000</v>
       </c>
       <c r="AG92">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH92">
         <v>1000</v>
@@ -23659,64 +23659,64 @@
         <v>1000</v>
       </c>
       <c r="AN92">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO92">
         <v>1000</v>
       </c>
       <c r="AP92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AQ92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AR92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AS92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AT92">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AU92">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AW92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AX92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AY92">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AZ92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BA92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BB92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BC92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BD92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BE92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BF92">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BG92">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="BH92">
         <v>1000</v>
@@ -23802,10 +23802,10 @@
         <v>1.87</v>
       </c>
       <c r="G93">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H93">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I93">
         <v>5.1</v>
@@ -23814,7 +23814,7 @@
         <v>3.65</v>
       </c>
       <c r="K93">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L93">
         <v>1.4</v>
@@ -23826,10 +23826,10 @@
         <v>3.5</v>
       </c>
       <c r="O93">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P93">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q93">
         <v>2.06</v>
@@ -23838,7 +23838,7 @@
         <v>1.32</v>
       </c>
       <c r="S93">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T93">
         <v>1.94</v>
@@ -23850,16 +23850,16 @@
         <v>1.25</v>
       </c>
       <c r="W93">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X93">
         <v>16</v>
       </c>
       <c r="Y93">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z93">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA93">
         <v>130</v>
@@ -23868,7 +23868,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC93">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD93">
         <v>22</v>
@@ -23889,7 +23889,7 @@
         <v>100</v>
       </c>
       <c r="AJ93">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK93">
         <v>22</v>
@@ -23901,34 +23901,34 @@
         <v>150</v>
       </c>
       <c r="AN93">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO93">
         <v>95</v>
       </c>
       <c r="AP93">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ93">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR93">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AS93">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT93">
         <v>7.4</v>
       </c>
       <c r="AU93">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV93">
         <v>16.5</v>
       </c>
       <c r="AW93">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX93">
         <v>9.6</v>
@@ -23937,28 +23937,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ93">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA93">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB93">
         <v>17</v>
       </c>
       <c r="BC93">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD93">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE93">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF93">
         <v>12</v>
       </c>
       <c r="BG93">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH93">
         <v>970</v>
@@ -24044,7 +24044,7 @@
         <v>2.2</v>
       </c>
       <c r="G94">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H94">
         <v>3.15</v>
@@ -24056,7 +24056,7 @@
         <v>3.3</v>
       </c>
       <c r="K94">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L94">
         <v>1.01</v>
@@ -24065,7 +24065,7 @@
         <v>1.03</v>
       </c>
       <c r="N94">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O94">
         <v>1.26</v>
@@ -24074,7 +24074,7 @@
         <v>1.96</v>
       </c>
       <c r="Q94">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R94">
         <v>1.37</v>
@@ -24092,7 +24092,7 @@
         <v>1.35</v>
       </c>
       <c r="W94">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X94">
         <v>1000</v>
@@ -24283,10 +24283,10 @@
         <v>373</v>
       </c>
       <c r="F95">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G95">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H95">
         <v>4.7</v>
@@ -24322,31 +24322,31 @@
         <v>1.41</v>
       </c>
       <c r="S95">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T95">
         <v>1.78</v>
       </c>
       <c r="U95">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V95">
         <v>1.26</v>
       </c>
       <c r="W95">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X95">
         <v>15.5</v>
       </c>
       <c r="Y95">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z95">
         <v>36</v>
       </c>
       <c r="AA95">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB95">
         <v>9.800000000000001</v>
@@ -24370,7 +24370,7 @@
         <v>18.5</v>
       </c>
       <c r="AI95">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ95">
         <v>21</v>
@@ -24397,7 +24397,7 @@
         <v>16.5</v>
       </c>
       <c r="AR95">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS95">
         <v>36</v>
@@ -24409,7 +24409,7 @@
         <v>8</v>
       </c>
       <c r="AV95">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW95">
         <v>50</v>
@@ -24454,7 +24454,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK95">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL95">
         <v>140</v>
@@ -24472,7 +24472,7 @@
         <v>13</v>
       </c>
       <c r="BQ95">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR95">
         <v>32</v>
@@ -24549,19 +24549,19 @@
         <v>1.01</v>
       </c>
       <c r="N96">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O96">
         <v>1.02</v>
       </c>
       <c r="P96">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q96">
         <v>1.39</v>
       </c>
       <c r="R96">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S96">
         <v>1.4</v>
@@ -24767,109 +24767,109 @@
         <v>375</v>
       </c>
       <c r="F97">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G97">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H97">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I97">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J97">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K97">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L97">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M97">
         <v>1.04</v>
       </c>
       <c r="N97">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O97">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P97">
         <v>2.36</v>
       </c>
       <c r="Q97">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R97">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S97">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T97">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U97">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V97">
         <v>1.14</v>
       </c>
       <c r="W97">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X97">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y97">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z97">
         <v>65</v>
       </c>
       <c r="AA97">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AB97">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC97">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD97">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE97">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF97">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG97">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH97">
         <v>26</v>
       </c>
       <c r="AI97">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ97">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK97">
         <v>15</v>
       </c>
       <c r="AL97">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM97">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN97">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO97">
         <v>120</v>
@@ -24881,49 +24881,49 @@
         <v>19.5</v>
       </c>
       <c r="AR97">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS97">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT97">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU97">
         <v>10.5</v>
       </c>
       <c r="AV97">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AW97">
         <v>7.2</v>
       </c>
       <c r="AX97">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY97">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ97">
         <v>18</v>
       </c>
       <c r="BA97">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB97">
         <v>11</v>
       </c>
       <c r="BC97">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD97">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE97">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF97">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG97">
         <v>7.2</v>
@@ -25012,7 +25012,7 @@
         <v>1.92</v>
       </c>
       <c r="G98">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H98">
         <v>4.3</v>
@@ -25027,7 +25027,7 @@
         <v>3.95</v>
       </c>
       <c r="L98">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M98">
         <v>1.06</v>
@@ -25039,10 +25039,10 @@
         <v>1.3</v>
       </c>
       <c r="P98">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q98">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R98">
         <v>1.41</v>
@@ -25051,7 +25051,7 @@
         <v>3.25</v>
       </c>
       <c r="T98">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U98">
         <v>2.16</v>
@@ -25081,7 +25081,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD98">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE98">
         <v>55</v>
@@ -25111,7 +25111,7 @@
         <v>100</v>
       </c>
       <c r="AN98">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO98">
         <v>60</v>
@@ -25123,7 +25123,7 @@
         <v>15</v>
       </c>
       <c r="AR98">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AS98">
         <v>36</v>
@@ -25132,19 +25132,19 @@
         <v>9</v>
       </c>
       <c r="AU98">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV98">
         <v>16</v>
       </c>
       <c r="AW98">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX98">
         <v>11</v>
       </c>
       <c r="AY98">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ98">
         <v>16.5</v>
@@ -25153,7 +25153,7 @@
         <v>50</v>
       </c>
       <c r="BB98">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC98">
         <v>17.5</v>
@@ -25168,13 +25168,13 @@
         <v>11</v>
       </c>
       <c r="BG98">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BH98">
         <v>970</v>
       </c>
       <c r="BI98">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BJ98">
         <v>970</v>
@@ -25198,7 +25198,7 @@
         <v>1000</v>
       </c>
       <c r="BQ98">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BR98">
         <v>1000</v>
@@ -25251,7 +25251,7 @@
         <v>377</v>
       </c>
       <c r="F99">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G99">
         <v>2.94</v>
@@ -25278,7 +25278,7 @@
         <v>6.6</v>
       </c>
       <c r="O99">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P99">
         <v>2.88</v>
@@ -25293,7 +25293,7 @@
         <v>2.26</v>
       </c>
       <c r="T99">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U99">
         <v>3</v>
@@ -25314,7 +25314,7 @@
         <v>21</v>
       </c>
       <c r="AA99">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB99">
         <v>19.5</v>
@@ -25326,7 +25326,7 @@
         <v>11.5</v>
       </c>
       <c r="AE99">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF99">
         <v>25</v>
@@ -25398,16 +25398,16 @@
         <v>42</v>
       </c>
       <c r="BC99">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD99">
         <v>26</v>
       </c>
       <c r="BE99">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF99">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG99">
         <v>10.5</v>
@@ -25428,10 +25428,10 @@
         <v>65</v>
       </c>
       <c r="BM99">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BN99">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO99">
         <v>5.9</v>
@@ -25446,7 +25446,7 @@
         <v>24</v>
       </c>
       <c r="BS99">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT99">
         <v>5.9</v>
@@ -25458,19 +25458,19 @@
         <v>15.5</v>
       </c>
       <c r="BW99">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX99">
         <v>21</v>
       </c>
       <c r="BY99">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ99">
         <v>14</v>
       </c>
       <c r="CA99">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB99" t="s">
         <v>389</v>
@@ -25493,40 +25493,40 @@
         <v>378</v>
       </c>
       <c r="F100">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G100">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H100">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I100">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J100">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K100">
         <v>5.2</v>
       </c>
       <c r="L100">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N100">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O100">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P100">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q100">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R100">
         <v>1.49</v>
@@ -25538,13 +25538,13 @@
         <v>1.73</v>
       </c>
       <c r="U100">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V100">
         <v>1.16</v>
       </c>
       <c r="W100">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="X100">
         <v>1000</v>
@@ -25583,10 +25583,10 @@
         <v>1000</v>
       </c>
       <c r="AJ100">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK100">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL100">
         <v>1000</v>
@@ -25595,7 +25595,7 @@
         <v>1000</v>
       </c>
       <c r="AN100">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO100">
         <v>1000</v>
@@ -25613,10 +25613,10 @@
         <v>1.01</v>
       </c>
       <c r="AT100">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU100">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV100">
         <v>1.01</v>
@@ -25625,10 +25625,10 @@
         <v>1.01</v>
       </c>
       <c r="AX100">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY100">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ100">
         <v>1.01</v>
@@ -25640,7 +25640,7 @@
         <v>1.01</v>
       </c>
       <c r="BC100">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD100">
         <v>1.01</v>
@@ -25649,7 +25649,7 @@
         <v>1.01</v>
       </c>
       <c r="BF100">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG100">
         <v>1.01</v>
@@ -25735,22 +25735,22 @@
         <v>379</v>
       </c>
       <c r="F101">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G101">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H101">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I101">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J101">
         <v>1.12</v>
       </c>
       <c r="K101">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="L101">
         <v>1.59</v>
@@ -25765,7 +25765,7 @@
         <v>1.53</v>
       </c>
       <c r="P101">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -25783,7 +25783,7 @@
         <v>1.01</v>
       </c>
       <c r="V101">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W101">
         <v>1.52</v>
@@ -26001,22 +26001,22 @@
         <v>1.02</v>
       </c>
       <c r="N102">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="O102">
         <v>1.25</v>
       </c>
       <c r="P102">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q102">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="R102">
         <v>1.32</v>
       </c>
       <c r="S102">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="T102">
         <v>1.01</v>
@@ -26219,13 +26219,13 @@
         <v>381</v>
       </c>
       <c r="F103">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G103">
         <v>3.15</v>
       </c>
       <c r="H103">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I103">
         <v>2.88</v>
@@ -26240,10 +26240,10 @@
         <v>1.53</v>
       </c>
       <c r="M103">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N103">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O103">
         <v>1.53</v>
@@ -26252,13 +26252,13 @@
         <v>1.58</v>
       </c>
       <c r="Q103">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R103">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S103">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T103">
         <v>2</v>
@@ -26273,13 +26273,13 @@
         <v>1.46</v>
       </c>
       <c r="X103">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y103">
         <v>10.5</v>
       </c>
       <c r="Z103">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA103">
         <v>70</v>
@@ -26327,16 +26327,16 @@
         <v>65</v>
       </c>
       <c r="AP103">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AQ103">
         <v>7</v>
       </c>
       <c r="AR103">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="AS103">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT103">
         <v>7</v>
@@ -26351,34 +26351,34 @@
         <v>3.65</v>
       </c>
       <c r="AX103">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AY103">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AZ103">
         <v>18.5</v>
       </c>
       <c r="BA103">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BB103">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC103">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD103">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BE103">
+        <v>3.95</v>
+      </c>
+      <c r="BF103">
         <v>3.9</v>
       </c>
-      <c r="BF103">
-        <v>3.8</v>
-      </c>
       <c r="BG103">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH103">
         <v>2.88</v>
@@ -26461,7 +26461,7 @@
         <v>382</v>
       </c>
       <c r="F104">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G104">
         <v>1.47</v>
@@ -26470,7 +26470,7 @@
         <v>9.6</v>
       </c>
       <c r="I104">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J104">
         <v>4.6</v>
@@ -26491,13 +26491,13 @@
         <v>1.3</v>
       </c>
       <c r="P104">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q104">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R104">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S104">
         <v>2.68</v>
@@ -26715,7 +26715,7 @@
         <v>110</v>
       </c>
       <c r="J105">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K105">
         <v>950</v>
@@ -26727,19 +26727,19 @@
         <v>1.01</v>
       </c>
       <c r="N105">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="O105">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="P105">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q105">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R105">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S105">
         <v>1.41</v>
@@ -26751,10 +26751,10 @@
         <v>1.01</v>
       </c>
       <c r="V105">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1000</v>
@@ -26945,166 +26945,166 @@
         <v>384</v>
       </c>
       <c r="F106">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G106">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="H106">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I106">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="J106">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K106">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L106">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M106">
         <v>1.03</v>
       </c>
       <c r="N106">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O106">
         <v>1.32</v>
       </c>
       <c r="P106">
+        <v>1.95</v>
+      </c>
+      <c r="Q106">
         <v>1.94</v>
       </c>
-      <c r="Q106">
-        <v>1.88</v>
-      </c>
       <c r="R106">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S106">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T106">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U106">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V106">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W106">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="X106">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y106">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z106">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA106">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB106">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC106">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD106">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE106">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF106">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG106">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH106">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI106">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ106">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK106">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL106">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM106">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN106">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AO106">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP106">
-        <v>1.92</v>
+        <v>13</v>
       </c>
       <c r="AQ106">
-        <v>1.76</v>
+        <v>5</v>
       </c>
       <c r="AR106">
-        <v>1.76</v>
+        <v>5.9</v>
       </c>
       <c r="AS106">
-        <v>1.76</v>
+        <v>6.2</v>
       </c>
       <c r="AT106">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU106">
-        <v>1.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV106">
-        <v>1.76</v>
+        <v>5.4</v>
       </c>
       <c r="AW106">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="AX106">
-        <v>1.67</v>
+        <v>7.6</v>
       </c>
       <c r="AY106">
-        <v>1.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ106">
-        <v>1.76</v>
+        <v>5.4</v>
       </c>
       <c r="BA106">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="BB106">
-        <v>1.73</v>
+        <v>12</v>
       </c>
       <c r="BC106">
-        <v>1.92</v>
+        <v>15</v>
       </c>
       <c r="BD106">
-        <v>1.76</v>
+        <v>5.6</v>
       </c>
       <c r="BE106">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="BF106">
-        <v>1.67</v>
+        <v>7.8</v>
       </c>
       <c r="BG106">
-        <v>1.59</v>
+        <v>5.8</v>
       </c>
       <c r="BH106">
         <v>970</v>
@@ -27211,22 +27211,22 @@
         <v>1.01</v>
       </c>
       <c r="N107">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="O107">
         <v>1.12</v>
       </c>
       <c r="P107">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Q107">
         <v>1.12</v>
       </c>
       <c r="R107">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S107">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="T107">
         <v>1.01</v>
@@ -27429,22 +27429,22 @@
         <v>386</v>
       </c>
       <c r="F108">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="G108">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="H108">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I108">
         <v>4.7</v>
       </c>
       <c r="J108">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K108">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L108">
         <v>1.01</v>
@@ -27453,58 +27453,58 @@
         <v>1.1</v>
       </c>
       <c r="N108">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O108">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P108">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q108">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R108">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S108">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T108">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U108">
         <v>1.71</v>
       </c>
       <c r="V108">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W108">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="X108">
         <v>12</v>
       </c>
       <c r="Y108">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z108">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA108">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB108">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC108">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD108">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AE108">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF108">
         <v>14</v>
@@ -27516,13 +27516,13 @@
         <v>23</v>
       </c>
       <c r="AI108">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ108">
         <v>34</v>
       </c>
       <c r="AK108">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL108">
         <v>65</v>
@@ -27534,7 +27534,7 @@
         <v>30</v>
       </c>
       <c r="AO108">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP108">
         <v>1.01</v>
@@ -27695,13 +27695,13 @@
         <v>1.05</v>
       </c>
       <c r="N109">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O109">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P109">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q109">
         <v>2.06</v>
@@ -27710,7 +27710,7 @@
         <v>1.24</v>
       </c>
       <c r="S109">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T109">
         <v>1.81</v>
@@ -27755,7 +27755,7 @@
         <v>20</v>
       </c>
       <c r="AH109">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI109">
         <v>70</v>
@@ -27779,28 +27779,28 @@
         <v>40</v>
       </c>
       <c r="AP109">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AQ109">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AR109">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AS109">
+        <v>2.12</v>
+      </c>
+      <c r="AT109">
+        <v>2.16</v>
+      </c>
+      <c r="AU109">
+        <v>2.2</v>
+      </c>
+      <c r="AV109">
+        <v>1.95</v>
+      </c>
+      <c r="AW109">
         <v>2.1</v>
-      </c>
-      <c r="AT109">
-        <v>2.3</v>
-      </c>
-      <c r="AU109">
-        <v>2.12</v>
-      </c>
-      <c r="AV109">
-        <v>2.32</v>
-      </c>
-      <c r="AW109">
-        <v>2.08</v>
       </c>
       <c r="AX109">
         <v>2.04</v>
@@ -27809,13 +27809,13 @@
         <v>1.98</v>
       </c>
       <c r="AZ109">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="BA109">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BB109">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BC109">
         <v>2.12</v>
@@ -27824,7 +27824,7 @@
         <v>2.14</v>
       </c>
       <c r="BE109">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="BF109">
         <v>25</v>
@@ -27913,16 +27913,16 @@
         <v>388</v>
       </c>
       <c r="F110">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G110">
         <v>1.89</v>
       </c>
       <c r="H110">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I110">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J110">
         <v>4.3</v>
@@ -27940,43 +27940,43 @@
         <v>6.2</v>
       </c>
       <c r="O110">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P110">
         <v>2.78</v>
       </c>
       <c r="Q110">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R110">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S110">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T110">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U110">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V110">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
         <v>2.12</v>
       </c>
       <c r="X110">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y110">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Z110">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA110">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB110">
         <v>15</v>
@@ -27985,7 +27985,7 @@
         <v>11.5</v>
       </c>
       <c r="AD110">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE110">
         <v>48</v>
@@ -27997,40 +27997,40 @@
         <v>11.5</v>
       </c>
       <c r="AH110">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI110">
         <v>44</v>
       </c>
       <c r="AJ110">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK110">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL110">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM110">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN110">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO110">
         <v>32</v>
       </c>
       <c r="AP110">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ110">
         <v>20</v>
       </c>
       <c r="AR110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS110">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT110">
         <v>13</v>
@@ -28042,7 +28042,7 @@
         <v>15</v>
       </c>
       <c r="AW110">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX110">
         <v>13.5</v>
@@ -28054,25 +28054,25 @@
         <v>14</v>
       </c>
       <c r="BA110">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB110">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC110">
         <v>15</v>
       </c>
       <c r="BD110">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE110">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF110">
         <v>6.6</v>
       </c>
       <c r="BG110">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH110">
         <v>6.4</v>
